--- a/data/Master Standardisation DACCS.xlsx
+++ b/data/Master Standardisation DACCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/SAF Paper_Katrin/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Documents/GitHub/DACCSvDACCU/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6240" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2A1159F-F1F7-492B-91BE-6C943397B3D9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35709E9C-8B18-9F42-8FC9-5C3A93149941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="973" firstSheet="10" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" tabRatio="973" firstSheet="10" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3613" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="792">
   <si>
     <t>This is a sheet for standardisation of inputs for the Meta Analysis of Net Removed Cost from Direct Air Capture Transport and Storage</t>
   </si>
@@ -3374,8 +3374,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
@@ -3908,7 +3908,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3936,14 +3936,14 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3985,7 +3985,7 @@
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4073,7 +4073,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="170" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4132,7 +4132,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{93C04280-CBA5-B944-83DB-A7AAB169697E}"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -7383,9 +7383,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7399,33 +7399,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AL46"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.8984375" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.6640625" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.09765625" customWidth="1"/>
-    <col min="19" max="22" width="20.09765625" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" customWidth="1"/>
+    <col min="19" max="22" width="20.1640625" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.09765625" customWidth="1"/>
+    <col min="26" max="28" width="15.1640625" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.59765625" customWidth="1"/>
+    <col min="32" max="32" width="37.6640625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.59765625" customWidth="1"/>
+    <col min="36" max="36" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AI3" s="53"/>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AI4" s="53"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AI5" s="53"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>199</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>214</v>
       </c>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="AI12" s="53"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>223</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>230</v>
       </c>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>234</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="18" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="58" t="s">
         <v>240</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48" t="s">
         <v>251</v>
       </c>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="AH21"/>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:37" s="60" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" s="60" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -9717,7 +9717,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>278</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -9983,7 +9983,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="32" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -10235,7 +10235,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="58" t="s">
         <v>294</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>301</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>315</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A38" s="48" t="s">
         <v>319</v>
       </c>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="F38" s="48"/>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>329</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>329</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A41" s="55" t="s">
         <v>336</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A42" s="55" t="s">
         <v>342</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="55" t="s">
         <v>345</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="55" t="s">
         <v>345</v>
       </c>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AH44"/>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>348</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A46" s="48"/>
     </row>
   </sheetData>
@@ -11353,29 +11353,29 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}">
-  <sheetPr codeName="Sheet7" filterMode="1">
+  <sheetPr codeName="Sheet7">
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:W180"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="40.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.59765625" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" customWidth="1"/>
-    <col min="7" max="7" width="6.8984375" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.3984375" customWidth="1"/>
-    <col min="11" max="11" width="13.59765625" customWidth="1"/>
-    <col min="12" max="13" width="24.09765625" customWidth="1"/>
-    <col min="14" max="14" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="18.09765625" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="13" width="24.1640625" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="L1" s="144" t="s">
         <v>655</v>
       </c>
@@ -11390,7 +11390,7 @@
       <c r="Q1" s="144"/>
       <c r="R1" s="144"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>403.01854968021763</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -11552,7 +11552,7 @@
         <v>330.6742103299726</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11597,7 +11597,7 @@
         <v>512.10547184973177</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>181.25398541249336</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>118.68760404820473</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>334.73812666531126</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>'Study Parameters'!A3</f>
         <v>Young et al. 2023</v>
@@ -11780,7 +11780,7 @@
         <v>2060.169523488109</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>1488.7216799143798</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>2729.5646158724885</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>235.23063570473388</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>127.38938043426646</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>537.5569191608829</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>'Study Parameters'!A4</f>
         <v>Young et al. 2023</v>
@@ -12055,7 +12055,7 @@
         <v>1308.9151041939408</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>1185.9075603382862</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>1518.5576325147504</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>1093.6075895663253</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>970.70141969195765</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -12275,7 +12275,7 @@
         <v>1303.0811612516566</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>'Study Parameters'!A5</f>
         <v>Young et al. 2023</v>
@@ -12325,7 +12325,7 @@
         <v>484.59306078439545</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>382.81191676230259</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -12413,7 +12413,7 @@
         <v>657.89384726964306</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>422.03061084640188</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>320.26794660828392</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -12545,7 +12545,7 @@
         <v>595.300597691691</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="str">
         <f>'Study Parameters'!A6</f>
         <v>Sievert et al. 2024</v>
@@ -12594,7 +12594,7 @@
         <v>669.94069463308699</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -12638,7 +12638,7 @@
         <v>521.31303134173265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>185</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>894.39776183919753</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>341.46121706214058</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>225.6544183898213</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>544.22032736034907</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>'Study Parameters'!A7</f>
         <v>Sievert et al. 2024</v>
@@ -12860,7 +12860,7 @@
         <v>1282.314450530346</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>1180.094323057237</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>185</v>
       </c>
@@ -12946,7 +12946,7 @@
         <v>1392.3242644152151</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -12989,7 +12989,7 @@
         <v>373.55046457825102</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>280.7967580377242</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>579.4216269225069</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>'Study Parameters'!A8</f>
         <v>Sievert et al. 2024</v>
@@ -13124,7 +13124,7 @@
         <v>2481.3480043001368</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>2153.1601565847341</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>2874.3199941446942</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>371.36449627097238</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>230.08236375974619</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>834.90242160632192</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13392,7 +13392,7 @@
         <v>293.01246179996224</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13447,7 +13447,7 @@
         <v>267.3339028754757</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13502,7 +13502,7 @@
         <v>303.19697040786667</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13549,7 +13549,7 @@
         <v>278.51244114406211</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13596,7 +13596,7 @@
         <v>260.17305813012763</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13643,7 +13643,7 @@
         <v>334.02175471233329</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13690,7 +13690,7 @@
         <v>347.52430793993972</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13737,7 +13737,7 @@
         <v>431.20952014305874</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13784,7 +13784,7 @@
         <v>405.58125796275607</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13831,7 +13831,7 @@
         <v>532.88151930075014</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13882,7 +13882,7 @@
         <v>598.00725415939087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13928,7 +13928,7 @@
         <v>594.26871158968584</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13974,7 +13974,7 @@
         <v>556.61504560775791</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14020,7 +14020,7 @@
         <v>745.92213758183834</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14066,7 +14066,7 @@
         <v>863.3220713069054</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
         <f>'Study Parameters'!A11</f>
         <v>Fasihi et al. 2019</v>
@@ -14123,7 +14123,7 @@
         <v>240.77436949062533</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>240.77436949062533</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>68.353737784789558</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>214</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>88.868172166477493</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
         <f>'Study Parameters'!A12</f>
         <v>Fasihi et al. 2019</v>
@@ -14332,7 +14332,7 @@
         <v>284.73955537191881</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>214</v>
       </c>
@@ -14383,7 +14383,7 @@
         <v>284.73955537191881</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>214</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>86.276726060082211</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>214</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>103.93137796340747</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="str">
         <f>'Study Parameters'!A13</f>
         <v>Mazzotti et al. 2013</v>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="M68" s="30"/>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="M69" s="30"/>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="M70" s="30"/>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
         <f>'Study Parameters'!A14</f>
         <v>Zeman 2014</v>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="M71" s="30"/>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
         <f>'Study Parameters'!A15</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="M72" s="30"/>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>230</v>
       </c>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="M73" s="30"/>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
         <f>'Study Parameters'!A16</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14793,7 +14793,7 @@
       </c>
       <c r="M74" s="30"/>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="M75" s="30"/>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="str">
         <f>'Study Parameters'!A17</f>
         <v>Terlouw et al. 2024</v>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="M76" s="62"/>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="M77" s="62"/>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
         <f>'Study Parameters'!A18</f>
         <v>McQueen et al. 2021</v>
@@ -14963,7 +14963,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -15080,7 +15080,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -15119,7 +15119,7 @@
         <v>463.06098024892566</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>240</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>558.57147419213493</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>240</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>777.69611217374995</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>2052.1001665091567</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" t="str">
         <f>'Study Parameters'!A19</f>
         <v>Datta et al. 2023</v>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="M86" s="30"/>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" t="str">
         <f>'Study Parameters'!A20</f>
         <v>Datta et al. 2023</v>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M87" s="30"/>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="M88" s="30"/>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>255</v>
       </c>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="M89" s="30"/>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="M90" s="30"/>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="M91" s="30"/>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="M92" s="30"/>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="M93" s="30"/>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="M94" s="30"/>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>255</v>
       </c>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="M95" s="30"/>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>255</v>
       </c>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="M96" s="30"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="str">
         <f>'Study Parameters'!A22</f>
         <v>Simon et al. 2011</v>
@@ -15736,7 +15736,7 @@
         <v>304.707654655694</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>803.14143939193252</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -15816,7 +15816,7 @@
         <v>329.15418006599049</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>267</v>
       </c>
@@ -15854,7 +15854,7 @@
         <v>779.02843503778104</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>267</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>831.75510668257198</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>267</v>
       </c>
@@ -15930,7 +15930,7 @@
         <v>317.24671499539198</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>267</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>371.938416568371</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>291.241690193887</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>355.05876736764702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>267</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>267.11083137986202</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="str">
         <f>'Study Parameters'!A23</f>
         <v>Küng et al. 2023</v>
@@ -16126,7 +16126,7 @@
         <v>314.61251708631102</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>267</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>1817.71250053524</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>267</v>
       </c>
@@ -16202,7 +16202,7 @@
         <v>1990.0315112179401</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>267</v>
       </c>
@@ -16240,7 +16240,7 @@
         <v>980.75097520117902</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>267</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>1064.51188379418</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>267</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>411.65027432423102</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>488.64611354083598</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>267</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>378.55341271061599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>267</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>468.39609948070898</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>267</v>
       </c>
@@ -16468,7 +16468,7 @@
         <v>349.10367628750998</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>267</v>
       </c>
@@ -16506,7 +16506,7 @@
         <v>415.97729787873197</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>267</v>
       </c>
@@ -16544,7 +16544,7 @@
         <v>2476.9733161530498</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>267</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>2750.7170677000299</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="str">
         <f>'Study Parameters'!A24</f>
         <v>Küng et al. 2023</v>
@@ -16625,7 +16625,7 @@
         <v>183.15040372394199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>267</v>
       </c>
@@ -16663,7 +16663,7 @@
         <v>227.07677281852301</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>61.893630816227301</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -16739,7 +16739,7 @@
         <v>72.225103599114604</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>393.65606020680502</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -16815,7 +16815,7 @@
         <v>503.939346853232</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>406.913082895564</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>517.19636954199098</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>243.248532930187</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -16967,7 +16967,7 @@
         <v>305.088767461244</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -17005,7 +17005,7 @@
         <v>76.028698179975393</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>90.573508350133693</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>523.47869237559496</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>698.67329510641696</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>536.73571506435496</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -17195,7 +17195,7 @@
         <v>711.93031779517605</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" t="str">
         <f>'Study Parameters'!A25</f>
         <v>Mostafa et al. 2022</v>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="L136" s="30"/>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" t="str">
         <f>'Study Parameters'!A26</f>
         <v>Keith et al. 2018</v>
@@ -17279,7 +17279,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -17327,7 +17327,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>167.17362579080822</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -17474,7 +17474,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -17525,7 +17525,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -17576,7 +17576,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>167.17362579080822</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" t="str">
         <f>'Study Parameters'!A27</f>
         <v>Gray et al. 2024</v>
@@ -17678,7 +17678,7 @@
         <v>1422.4526421724208</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" t="str">
         <f>'Study Parameters'!A28</f>
         <v>Rosen et al. 2024</v>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="L146" s="30"/>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" t="str">
         <f>'Study Parameters'!A29</f>
         <v>Rosen et al. 2024</v>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="L147" s="30"/>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" t="str">
         <f>'Study Parameters'!A30</f>
         <v>Rosen et al. 2024</v>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="L148" s="30"/>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" t="str">
         <f>'Study Parameters'!A31</f>
         <v>Rosen et al. 2024</v>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="L149" s="30"/>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" t="str">
         <f>'Study Parameters'!A32</f>
         <v>Sabatino et al. 2020</v>
@@ -17837,7 +17837,7 @@
       </c>
       <c r="L150" s="30"/>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17879,7 +17879,7 @@
         <v>52.859259278213045</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17920,7 +17920,7 @@
         <v>174.22096158203897</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -17956,7 +17956,7 @@
         <v>45.162595126533958</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>294</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>155.30185025856494</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" t="str">
         <f>'Study Parameters'!A34</f>
         <v>Lee et al. 2023</v>
@@ -18050,7 +18050,7 @@
         <v>270.09276004403995</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" t="str">
         <f>'Study Parameters'!A35</f>
         <v>Abanades et al. 2023</v>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="L156" s="30"/>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" t="str">
         <f>'Study Parameters'!A36</f>
         <v>Abanades et al. 2020</v>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="L157" s="30"/>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" t="str">
         <f>'Study Parameters'!A37</f>
         <v>Ragipani et al. 2022</v>
@@ -18146,7 +18146,7 @@
         <v>121.14570202833102</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>315</v>
       </c>
@@ -18182,7 +18182,7 @@
         <v>140.09669470231475</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -18230,7 +18230,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>329</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" t="str">
         <f>'Study Parameters'!A39</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18378,7 +18378,7 @@
         <v>141.90647783174506</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -18426,7 +18426,7 @@
         <v>141.90647783174506</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>141.90647783174506</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" t="str">
         <f>'Study Parameters'!A40</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18527,7 +18527,7 @@
         <v>440.01216847304312</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>329</v>
       </c>
@@ -18575,7 +18575,7 @@
         <v>339.04143355290654</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>329</v>
       </c>
@@ -18623,7 +18623,7 @@
         <v>263.41019772115243</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>162.86808564420988</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" t="str">
         <f>'Study Parameters'!A41</f>
         <v>NETL/Valentine 2022a</v>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="M170" s="30"/>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="M171" s="30"/>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>336</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="M172" s="30"/>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" t="str">
         <f>'Study Parameters'!A42</f>
         <v>NETL/Valentine 2022b</v>
@@ -18840,7 +18840,7 @@
       </c>
       <c r="M173" s="30"/>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="M174" s="30"/>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>342</v>
       </c>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="M175" s="30"/>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" t="str">
         <f>'Study Parameters'!A43</f>
         <v>NASEM 2019</v>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18974,7 +18974,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19001,14 +19001,13 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
       </c>
-      <c r="B179" t="str">
-        <f>'Study Parameters'!H45</f>
-        <v>end 2008/early 2009</v>
+      <c r="B179">
+        <v>2009</v>
       </c>
       <c r="C179" t="str">
         <f>'Study Parameters'!E45</f>
@@ -19048,12 +19047,12 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>348</v>
       </c>
-      <c r="B180" t="s">
-        <v>400</v>
+      <c r="B180">
+        <v>2009</v>
       </c>
       <c r="C180" t="s">
         <v>350</v>
@@ -19089,13 +19088,7 @@
       <c r="M180" s="30"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:W180" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="2050"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:W180" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}"/>
   <mergeCells count="2">
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="L1:N1"/>
@@ -19110,14 +19103,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C0257C-D407-4235-8443-42A5A3A9A73A}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
         <v>751</v>
       </c>
@@ -19127,7 +19120,7 @@
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="64" t="s">
         <v>753</v>
       </c>
@@ -19137,7 +19130,7 @@
       <c r="J2" s="74"/>
       <c r="K2" s="74"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
       <c r="F3" s="74" t="s">
         <v>755</v>
@@ -19145,7 +19138,7 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>756</v>
       </c>
@@ -19161,7 +19154,7 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>760</v>
       </c>
@@ -19177,7 +19170,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="74"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>764</v>
       </c>
@@ -19190,7 +19183,7 @@
       <c r="J6" s="74"/>
       <c r="K6" s="74"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>766</v>
       </c>
@@ -19200,7 +19193,7 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>767</v>
       </c>
@@ -19210,7 +19203,7 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>768</v>
       </c>
@@ -19220,7 +19213,7 @@
       <c r="J9" s="74"/>
       <c r="K9" s="74"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>769</v>
       </c>
@@ -19230,7 +19223,7 @@
       <c r="J10" s="74"/>
       <c r="K10" s="74"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>770</v>
       </c>
@@ -19240,7 +19233,7 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>771</v>
       </c>
@@ -19250,7 +19243,7 @@
       <c r="J12" s="76"/>
       <c r="K12" s="77"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>772</v>
       </c>
@@ -19260,7 +19253,7 @@
       <c r="J13" s="76"/>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>773</v>
       </c>
@@ -19270,7 +19263,7 @@
       <c r="J14" s="76"/>
       <c r="K14" s="77"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>774</v>
       </c>
@@ -19280,7 +19273,7 @@
       <c r="J15" s="76"/>
       <c r="K15" s="77"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>775</v>
       </c>
@@ -19290,7 +19283,7 @@
       <c r="J16" s="76"/>
       <c r="K16" s="77"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>776</v>
       </c>
@@ -19300,7 +19293,7 @@
       <c r="J17" s="76"/>
       <c r="K17" s="77"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>777</v>
       </c>
@@ -19310,7 +19303,7 @@
       <c r="J18" s="76"/>
       <c r="K18" s="77"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>778</v>
       </c>
@@ -19320,7 +19313,7 @@
       <c r="J19" s="76"/>
       <c r="K19" s="74"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>779</v>
       </c>
@@ -19330,7 +19323,7 @@
       <c r="J20" s="76"/>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>780</v>
       </c>
@@ -19340,7 +19333,7 @@
       <c r="J21" s="76"/>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -19351,7 +19344,7 @@
       <c r="J22" s="76"/>
       <c r="K22" s="77"/>
     </row>
-    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="85" t="s">
         <v>80</v>
       </c>
@@ -19382,7 +19375,7 @@
       <c r="J23" s="76"/>
       <c r="K23" s="77"/>
     </row>
-    <row r="24" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="78" t="s">
         <v>782</v>
       </c>
@@ -19413,14 +19406,14 @@
       <c r="J24" s="76"/>
       <c r="K24" s="77"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="86" t="s">
         <v>784</v>
       </c>
       <c r="J25" s="76"/>
       <c r="K25" s="77"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>785</v>
       </c>
@@ -19434,7 +19427,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="77"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -19457,52 +19450,52 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56965C59-6106-408A-A712-D0B6552D4011}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="74" t="s">
         <v>752</v>
       </c>
       <c r="B1" s="74"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="74" t="s">
         <v>754</v>
       </c>
       <c r="B2" s="74"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="74" t="s">
         <v>755</v>
       </c>
       <c r="B3" s="74"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="74" t="s">
         <v>759</v>
       </c>
       <c r="B4" s="74"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="74" t="s">
         <v>763</v>
       </c>
       <c r="B5" s="74"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="74" t="s">
         <v>765</v>
       </c>
       <c r="B6" s="74"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="74" t="s">
         <v>788</v>
       </c>
@@ -19510,17 +19503,17 @@
         <v>789</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="74"/>
       <c r="B9" s="74"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="74" t="s">
         <v>790</v>
       </c>
       <c r="B10" s="74"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="74" t="s">
         <v>791</v>
       </c>
@@ -19528,7 +19521,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="76">
         <v>39448</v>
       </c>
@@ -19536,7 +19529,7 @@
         <v>1.4728000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="76">
         <v>39479</v>
       </c>
@@ -19544,7 +19537,7 @@
         <v>1.4759</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="76">
         <v>39508</v>
       </c>
@@ -19552,7 +19545,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="76">
         <v>39539</v>
       </c>
@@ -19560,7 +19553,7 @@
         <v>1.5753999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="76">
         <v>39569</v>
       </c>
@@ -19568,7 +19561,7 @@
         <v>1.5553999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="76">
         <v>39600</v>
       </c>
@@ -19576,7 +19569,7 @@
         <v>1.5562</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="76">
         <v>39630</v>
       </c>
@@ -19584,7 +19577,7 @@
         <v>1.5759000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="76">
         <v>39661</v>
       </c>
@@ -19592,7 +19585,7 @@
         <v>1.4955000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="76">
         <v>39692</v>
       </c>
@@ -19600,7 +19593,7 @@
         <v>1.4341999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="76">
         <v>39722</v>
       </c>
@@ -19608,7 +19601,7 @@
         <v>1.3266</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="76">
         <v>39753</v>
       </c>
@@ -19616,7 +19609,7 @@
         <v>1.2744</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="76">
         <v>39783</v>
       </c>
@@ -19624,7 +19617,7 @@
         <v>1.3511</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="76">
         <v>39814</v>
       </c>
@@ -19632,7 +19625,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="76">
         <v>39845</v>
       </c>
@@ -19640,7 +19633,7 @@
         <v>1.2797000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="76">
         <v>39873</v>
       </c>
@@ -19648,7 +19641,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="76">
         <v>39904</v>
       </c>
@@ -19656,7 +19649,7 @@
         <v>1.3199000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="76">
         <v>39934</v>
       </c>
@@ -19664,7 +19657,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="76">
         <v>39965</v>
       </c>
@@ -19672,7 +19665,7 @@
         <v>1.4014</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="76">
         <v>39995</v>
       </c>
@@ -19680,7 +19673,7 @@
         <v>1.4092</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="76">
         <v>40026</v>
       </c>
@@ -19688,7 +19681,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="76">
         <v>40057</v>
       </c>
@@ -19696,7 +19689,7 @@
         <v>1.4575</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="76">
         <v>40087</v>
       </c>
@@ -19704,7 +19697,7 @@
         <v>1.4821</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="76">
         <v>40118</v>
       </c>
@@ -19712,7 +19705,7 @@
         <v>1.4907999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="76">
         <v>40148</v>
       </c>
@@ -19720,7 +19713,7 @@
         <v>1.4579</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="76">
         <v>40179</v>
       </c>
@@ -19728,7 +19721,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="76">
         <v>40210</v>
       </c>
@@ -19736,7 +19729,7 @@
         <v>1.3680000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="76">
         <v>40238</v>
       </c>
@@ -19744,7 +19737,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="76">
         <v>40269</v>
       </c>
@@ -19752,7 +19745,7 @@
         <v>1.3416999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="76">
         <v>40299</v>
       </c>
@@ -19760,7 +19753,7 @@
         <v>1.2563</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="76">
         <v>40330</v>
       </c>
@@ -19768,7 +19761,7 @@
         <v>1.2222999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="76">
         <v>40360</v>
       </c>
@@ -19776,7 +19769,7 @@
         <v>1.2810999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="76">
         <v>40391</v>
       </c>
@@ -19784,7 +19777,7 @@
         <v>1.2903</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="76">
         <v>40422</v>
       </c>
@@ -19792,7 +19785,7 @@
         <v>1.3103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="76">
         <v>40452</v>
       </c>
@@ -19800,7 +19793,7 @@
         <v>1.3900999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="76">
         <v>40483</v>
       </c>
@@ -19808,7 +19801,7 @@
         <v>1.3653999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="76">
         <v>40513</v>
       </c>
@@ -19816,7 +19809,7 @@
         <v>1.3221000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="76">
         <v>40544</v>
       </c>
@@ -19824,7 +19817,7 @@
         <v>1.3371</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="76">
         <v>40575</v>
       </c>
@@ -19832,7 +19825,7 @@
         <v>1.3655999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="76">
         <v>40603</v>
       </c>
@@ -19840,7 +19833,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="76">
         <v>40634</v>
       </c>
@@ -19848,7 +19841,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="76">
         <v>40664</v>
       </c>
@@ -19856,7 +19849,7 @@
         <v>1.4335</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="76">
         <v>40695</v>
       </c>
@@ -19864,7 +19857,7 @@
         <v>1.4402999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="76">
         <v>40725</v>
       </c>
@@ -19872,7 +19865,7 @@
         <v>1.4275</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="76">
         <v>40756</v>
       </c>
@@ -19880,7 +19873,7 @@
         <v>1.4333</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="76">
         <v>40787</v>
       </c>
@@ -19888,7 +19881,7 @@
         <v>1.3747</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="76">
         <v>40817</v>
       </c>
@@ -19896,7 +19889,7 @@
         <v>1.3732</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="76">
         <v>40848</v>
       </c>
@@ -19904,7 +19897,7 @@
         <v>1.3557999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="76">
         <v>40878</v>
       </c>
@@ -19912,7 +19905,7 @@
         <v>1.3154999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="76">
         <v>40909</v>
       </c>
@@ -19920,7 +19913,7 @@
         <v>1.2909999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="76">
         <v>40940</v>
       </c>
@@ -19928,7 +19921,7 @@
         <v>1.3238000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="76">
         <v>40969</v>
       </c>
@@ -19936,7 +19929,7 @@
         <v>1.3208</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="76">
         <v>41000</v>
       </c>
@@ -19944,7 +19937,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="76">
         <v>41030</v>
       </c>
@@ -19952,7 +19945,7 @@
         <v>1.2806</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="76">
         <v>41061</v>
       </c>
@@ -19960,7 +19953,7 @@
         <v>1.2541</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="76">
         <v>41091</v>
       </c>
@@ -19968,7 +19961,7 @@
         <v>1.2278</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="76">
         <v>41122</v>
       </c>
@@ -19976,7 +19969,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="76">
         <v>41153</v>
       </c>
@@ -19984,7 +19977,7 @@
         <v>1.2885</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="76">
         <v>41183</v>
       </c>
@@ -19992,7 +19985,7 @@
         <v>1.2974000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="76">
         <v>41214</v>
       </c>
@@ -20000,7 +19993,7 @@
         <v>1.2837000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="76">
         <v>41244</v>
       </c>
@@ -20008,7 +20001,7 @@
         <v>1.3119000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="76">
         <v>41275</v>
       </c>
@@ -20016,7 +20009,7 @@
         <v>1.3304</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="76">
         <v>41306</v>
       </c>
@@ -20024,7 +20017,7 @@
         <v>1.3347</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="76">
         <v>41334</v>
       </c>
@@ -20032,7 +20025,7 @@
         <v>1.2952999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="76">
         <v>41365</v>
       </c>
@@ -20040,7 +20033,7 @@
         <v>1.3025</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="76">
         <v>41395</v>
       </c>
@@ -20048,7 +20041,7 @@
         <v>1.2983</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="76">
         <v>41426</v>
       </c>
@@ -20056,7 +20049,7 @@
         <v>1.3197000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="76">
         <v>41456</v>
       </c>
@@ -20064,7 +20057,7 @@
         <v>1.3088</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="76">
         <v>41487</v>
       </c>
@@ -20072,7 +20065,7 @@
         <v>1.3313999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="76">
         <v>41518</v>
       </c>
@@ -20080,7 +20073,7 @@
         <v>1.3364</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="76">
         <v>41548</v>
       </c>
@@ -20088,7 +20081,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="76">
         <v>41579</v>
       </c>
@@ -20096,7 +20089,7 @@
         <v>1.3491</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="76">
         <v>41609</v>
       </c>
@@ -20104,7 +20097,7 @@
         <v>1.3708</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="76">
         <v>41640</v>
       </c>
@@ -20112,7 +20105,7 @@
         <v>1.3617999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="76">
         <v>41671</v>
       </c>
@@ -20120,7 +20113,7 @@
         <v>1.3665</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="76">
         <v>41699</v>
       </c>
@@ -20128,7 +20121,7 @@
         <v>1.3828</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="76">
         <v>41730</v>
       </c>
@@ -20136,7 +20129,7 @@
         <v>1.381</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="76">
         <v>41760</v>
       </c>
@@ -20144,7 +20137,7 @@
         <v>1.3738999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="76">
         <v>41791</v>
       </c>
@@ -20152,7 +20145,7 @@
         <v>1.3594999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="76">
         <v>41821</v>
       </c>
@@ -20160,7 +20153,7 @@
         <v>1.3532999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="76">
         <v>41852</v>
       </c>
@@ -20168,7 +20161,7 @@
         <v>1.3314999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="76">
         <v>41883</v>
       </c>
@@ -20176,7 +20169,7 @@
         <v>1.2888999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="76">
         <v>41913</v>
       </c>
@@ -20184,7 +20177,7 @@
         <v>1.2677</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="76">
         <v>41944</v>
       </c>
@@ -20192,7 +20185,7 @@
         <v>1.2473000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="76">
         <v>41974</v>
       </c>
@@ -20200,7 +20193,7 @@
         <v>1.2329000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="76">
         <v>42005</v>
       </c>
@@ -20208,7 +20201,7 @@
         <v>1.1615</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="76">
         <v>42036</v>
       </c>
@@ -20216,7 +20209,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="76">
         <v>42064</v>
       </c>
@@ -20224,7 +20217,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="76">
         <v>42095</v>
       </c>
@@ -20232,7 +20225,7 @@
         <v>1.0822000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="76">
         <v>42125</v>
       </c>
@@ -20240,7 +20233,7 @@
         <v>1.1167</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="76">
         <v>42156</v>
       </c>
@@ -20248,7 +20241,7 @@
         <v>1.1226</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="76">
         <v>42186</v>
       </c>
@@ -20256,7 +20249,7 @@
         <v>1.0996999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="76">
         <v>42217</v>
       </c>
@@ -20264,7 +20257,7 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="76">
         <v>42248</v>
       </c>
@@ -20272,7 +20265,7 @@
         <v>1.1229</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="76">
         <v>42278</v>
       </c>
@@ -20280,7 +20273,7 @@
         <v>1.1228</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="76">
         <v>42309</v>
       </c>
@@ -20288,7 +20281,7 @@
         <v>1.0727</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="76">
         <v>42339</v>
       </c>
@@ -20296,7 +20289,7 @@
         <v>1.0889</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="76">
         <v>42370</v>
       </c>
@@ -20304,7 +20297,7 @@
         <v>1.0854999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="76">
         <v>42401</v>
       </c>
@@ -20312,7 +20305,7 @@
         <v>1.1092</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="76">
         <v>42430</v>
       </c>
@@ -20320,7 +20313,7 @@
         <v>1.1133999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="76">
         <v>42461</v>
       </c>
@@ -20328,7 +20321,7 @@
         <v>1.1346000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="76">
         <v>42491</v>
       </c>
@@ -20336,7 +20329,7 @@
         <v>1.1312</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="76">
         <v>42522</v>
       </c>
@@ -20344,7 +20337,7 @@
         <v>1.1232</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="76">
         <v>42552</v>
       </c>
@@ -20352,7 +20345,7 @@
         <v>1.1054999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="76">
         <v>42583</v>
       </c>
@@ -20360,7 +20353,7 @@
         <v>1.1207</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="76">
         <v>42614</v>
       </c>
@@ -20368,7 +20361,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="76">
         <v>42644</v>
       </c>
@@ -20376,7 +20369,7 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="76">
         <v>42675</v>
       </c>
@@ -20384,7 +20377,7 @@
         <v>1.0791999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="76">
         <v>42705</v>
       </c>
@@ -20392,7 +20385,7 @@
         <v>1.0545</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="76">
         <v>42736</v>
       </c>
@@ -20400,7 +20393,7 @@
         <v>1.0634999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="76">
         <v>42767</v>
       </c>
@@ -20408,7 +20401,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="76">
         <v>42795</v>
       </c>
@@ -20416,7 +20409,7 @@
         <v>1.0690999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="76">
         <v>42826</v>
       </c>
@@ -20424,7 +20417,7 @@
         <v>1.0713999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="76">
         <v>42856</v>
       </c>
@@ -20432,7 +20425,7 @@
         <v>1.105</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="76">
         <v>42887</v>
       </c>
@@ -20440,7 +20433,7 @@
         <v>1.1233</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="76">
         <v>42917</v>
       </c>
@@ -20448,7 +20441,7 @@
         <v>1.153</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="76">
         <v>42948</v>
       </c>
@@ -20456,7 +20449,7 @@
         <v>1.1813</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="76">
         <v>42979</v>
       </c>
@@ -20464,7 +20457,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="76">
         <v>43009</v>
       </c>
@@ -20472,7 +20465,7 @@
         <v>1.1755</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="76">
         <v>43040</v>
       </c>
@@ -20480,7 +20473,7 @@
         <v>1.1742999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="76">
         <v>43070</v>
       </c>
@@ -20488,7 +20481,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="76">
         <v>43101</v>
       </c>
@@ -20496,7 +20489,7 @@
         <v>1.2197</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="76">
         <v>43132</v>
       </c>
@@ -20504,7 +20497,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="76">
         <v>43160</v>
       </c>
@@ -20512,7 +20505,7 @@
         <v>1.2334000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="76">
         <v>43191</v>
       </c>
@@ -20520,7 +20513,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="76">
         <v>43221</v>
       </c>
@@ -20528,7 +20521,7 @@
         <v>1.1822999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="76">
         <v>43252</v>
       </c>
@@ -20536,7 +20529,7 @@
         <v>1.1678999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="76">
         <v>43282</v>
       </c>
@@ -20544,7 +20537,7 @@
         <v>1.1685000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="76">
         <v>43313</v>
       </c>
@@ -20552,7 +20545,7 @@
         <v>1.1547000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="76">
         <v>43344</v>
       </c>
@@ -20560,7 +20553,7 @@
         <v>1.1667000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="76">
         <v>43374</v>
       </c>
@@ -20568,7 +20561,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="76">
         <v>43405</v>
       </c>
@@ -20576,7 +20569,7 @@
         <v>1.1364000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="76">
         <v>43435</v>
       </c>
@@ -20584,7 +20577,7 @@
         <v>1.1379999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="76">
         <v>43466</v>
       </c>
@@ -20592,7 +20585,7 @@
         <v>1.1417999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="76">
         <v>43497</v>
       </c>
@@ -20600,7 +20593,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="76">
         <v>43525</v>
       </c>
@@ -20608,7 +20601,7 @@
         <v>1.1295999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="76">
         <v>43556</v>
       </c>
@@ -20616,7 +20609,7 @@
         <v>1.1234</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="76">
         <v>43586</v>
       </c>
@@ -20624,7 +20617,7 @@
         <v>1.1187</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="76">
         <v>43617</v>
       </c>
@@ -20632,7 +20625,7 @@
         <v>1.1294999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="76">
         <v>43647</v>
       </c>
@@ -20640,7 +20633,7 @@
         <v>1.1211</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="76">
         <v>43678</v>
       </c>
@@ -20648,7 +20641,7 @@
         <v>1.1129</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="76">
         <v>43709</v>
       </c>
@@ -20656,7 +20649,7 @@
         <v>1.1011</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="76">
         <v>43739</v>
       </c>
@@ -20664,7 +20657,7 @@
         <v>1.1057999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="76">
         <v>43770</v>
       </c>
@@ -20672,7 +20665,7 @@
         <v>1.1051</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="76">
         <v>43800</v>
       </c>
@@ -20680,7 +20673,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="76">
         <v>43831</v>
       </c>
@@ -20688,7 +20681,7 @@
         <v>1.1097999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="76">
         <v>43862</v>
       </c>
@@ -20696,7 +20689,7 @@
         <v>1.0911</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="76">
         <v>43891</v>
       </c>
@@ -20704,7 +20697,7 @@
         <v>1.1046</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="76">
         <v>43922</v>
       </c>
@@ -20712,7 +20705,7 @@
         <v>1.0871</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="76">
         <v>43952</v>
       </c>
@@ -20720,7 +20713,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="76">
         <v>43983</v>
       </c>
@@ -20728,7 +20721,7 @@
         <v>1.1258999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="76">
         <v>44013</v>
       </c>
@@ -20736,7 +20729,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="76">
         <v>44044</v>
       </c>
@@ -20744,7 +20737,7 @@
         <v>1.1831</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="76">
         <v>44075</v>
       </c>
@@ -20752,7 +20745,7 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="76">
         <v>44105</v>
       </c>
@@ -20760,7 +20753,7 @@
         <v>1.1768000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="76">
         <v>44136</v>
       </c>
@@ -20768,7 +20761,7 @@
         <v>1.1826000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="76">
         <v>44166</v>
       </c>
@@ -20776,7 +20769,7 @@
         <v>1.2168000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="76">
         <v>44197</v>
       </c>
@@ -20784,7 +20777,7 @@
         <v>1.2178</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="76">
         <v>44228</v>
       </c>
@@ -20792,7 +20785,7 @@
         <v>1.2094</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="76">
         <v>44256</v>
       </c>
@@ -20800,7 +20793,7 @@
         <v>1.1901999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="76">
         <v>44287</v>
       </c>
@@ -20808,7 +20801,7 @@
         <v>1.1964999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="76">
         <v>44317</v>
       </c>
@@ -20816,7 +20809,7 @@
         <v>1.2145999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="76">
         <v>44348</v>
       </c>
@@ -20824,7 +20817,7 @@
         <v>1.2048000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="76">
         <v>44378</v>
       </c>
@@ -20832,7 +20825,7 @@
         <v>1.1820999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="76">
         <v>44409</v>
       </c>
@@ -20840,7 +20833,7 @@
         <v>1.1767000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="76">
         <v>44440</v>
       </c>
@@ -20848,7 +20841,7 @@
         <v>1.1765000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="76">
         <v>44470</v>
       </c>
@@ -20856,7 +20849,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="76">
         <v>44501</v>
       </c>
@@ -20864,7 +20857,7 @@
         <v>1.1415999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="76">
         <v>44531</v>
       </c>
@@ -20872,7 +20865,7 @@
         <v>1.1301000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="76">
         <v>44562</v>
       </c>
@@ -20880,7 +20873,7 @@
         <v>1.1316999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="76">
         <v>44593</v>
       </c>
@@ -20888,7 +20881,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="76">
         <v>44621</v>
       </c>
@@ -20896,7 +20889,7 @@
         <v>1.1019000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" s="76">
         <v>44652</v>
       </c>
@@ -20904,7 +20897,7 @@
         <v>1.0803</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="76">
         <v>44682</v>
       </c>
@@ -20912,7 +20905,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="76">
         <v>44713</v>
       </c>
@@ -20920,7 +20913,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="76">
         <v>44743</v>
       </c>
@@ -20928,7 +20921,7 @@
         <v>1.0167999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="76">
         <v>44774</v>
       </c>
@@ -20936,7 +20929,7 @@
         <v>1.0128999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="76">
         <v>44805</v>
       </c>
@@ -20944,7 +20937,7 @@
         <v>0.9899</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="76">
         <v>44835</v>
       </c>
@@ -20952,7 +20945,7 @@
         <v>0.98529999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="76">
         <v>44866</v>
       </c>
@@ -20960,7 +20953,7 @@
         <v>1.0192000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="76">
         <v>44896</v>
       </c>
@@ -20968,7 +20961,7 @@
         <v>1.0590999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" s="76">
         <v>44927</v>
       </c>
@@ -20976,7 +20969,7 @@
         <v>1.0777000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="76">
         <v>44958</v>
       </c>
@@ -20984,7 +20977,7 @@
         <v>1.0702</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="76">
         <v>44986</v>
       </c>
@@ -20992,7 +20985,7 @@
         <v>1.0710999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="76">
         <v>45017</v>
       </c>
@@ -21000,7 +20993,7 @@
         <v>1.0962000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="76">
         <v>45047</v>
       </c>
@@ -21008,7 +21001,7 @@
         <v>1.0867</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="76">
         <v>45078</v>
       </c>
@@ -21016,7 +21009,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="76">
         <v>45108</v>
       </c>
@@ -21024,7 +21017,7 @@
         <v>1.1067</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="76">
         <v>45139</v>
       </c>
@@ -21032,7 +21025,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="76">
         <v>45170</v>
       </c>
@@ -21040,7 +21033,7 @@
         <v>1.0671999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="76">
         <v>45200</v>
       </c>
@@ -21048,7 +21041,7 @@
         <v>1.0565</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="76">
         <v>45231</v>
       </c>
@@ -21056,7 +21049,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="76">
         <v>45261</v>
       </c>
@@ -21064,7 +21057,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="76">
         <v>45292</v>
       </c>
@@ -21072,7 +21065,7 @@
         <v>1.0899000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="76">
         <v>45323</v>
       </c>
@@ -21080,7 +21073,7 @@
         <v>1.0792999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="76">
         <v>45352</v>
       </c>
@@ -21088,7 +21081,7 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="76">
         <v>45383</v>
       </c>
@@ -21096,7 +21089,7 @@
         <v>1.0724</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="76">
         <v>45413</v>
       </c>
@@ -21104,7 +21097,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="76">
         <v>45444</v>
       </c>
@@ -21112,7 +21105,7 @@
         <v>1.0763</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="76">
         <v>45474</v>
       </c>
@@ -21120,7 +21113,7 @@
         <v>1.0847</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="76">
         <v>45505</v>
       </c>
@@ -21137,7 +21130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21149,15 +21142,15 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -21171,7 +21164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -21185,12 +21178,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -21198,7 +21191,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -21207,7 +21200,7 @@
         <v>2.453282945060923E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -21215,7 +21208,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -21224,12 +21217,12 @@
         <v>0.81870109796004231</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="57" t="s">
         <v>15</v>
       </c>
@@ -21247,7 +21240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="57" t="s">
         <v>15</v>
       </c>
@@ -21265,7 +21258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="105" t="s">
         <v>19</v>
       </c>
@@ -21282,7 +21275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="105" t="s">
         <v>19</v>
       </c>
@@ -21299,7 +21292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="105" t="s">
         <v>19</v>
       </c>
@@ -21315,7 +21308,7 @@
       </c>
       <c r="E13" s="94"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="105" t="s">
         <v>19</v>
       </c>
@@ -21331,7 +21324,7 @@
       </c>
       <c r="E14" s="94"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="105" t="s">
         <v>22</v>
       </c>
@@ -21348,7 +21341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="105" t="s">
         <v>22</v>
       </c>
@@ -21365,7 +21358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="105" t="s">
         <v>22</v>
       </c>
@@ -21381,7 +21374,7 @@
       </c>
       <c r="E17" s="94"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="105" t="s">
         <v>22</v>
       </c>
@@ -21397,7 +21390,7 @@
       </c>
       <c r="E18" s="94"/>
     </row>
-    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="94" t="s">
         <v>23</v>
       </c>
@@ -21411,7 +21404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="94" t="s">
         <v>25</v>
       </c>
@@ -21425,7 +21418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="94" t="s">
         <v>26</v>
       </c>
@@ -21440,12 +21433,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -21462,7 +21455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -21479,12 +21472,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -21501,7 +21494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="57" t="s">
         <v>32</v>
       </c>
@@ -21518,7 +21511,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" s="108" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="108" t="s">
         <v>33</v>
       </c>
@@ -21546,17 +21539,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="35" max="35" width="8.59765625" style="47"/>
-    <col min="36" max="36" width="17.09765625" style="41" customWidth="1"/>
-    <col min="37" max="37" width="13.59765625" customWidth="1"/>
+    <col min="35" max="35" width="8.6640625" style="47"/>
+    <col min="36" max="36" width="17.1640625" style="41" customWidth="1"/>
+    <col min="37" max="37" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
@@ -21672,7 +21665,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
         <v>43</v>
       </c>
@@ -21789,7 +21782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>51</v>
       </c>
@@ -21896,7 +21889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
         <v>53</v>
       </c>
@@ -22003,7 +21996,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>55</v>
       </c>
@@ -22110,7 +22103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
         <v>56</v>
       </c>
@@ -22217,7 +22210,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="40" t="s">
         <v>57</v>
       </c>
@@ -22324,7 +22317,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="40" t="s">
         <v>58</v>
       </c>
@@ -22431,7 +22424,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
         <v>59</v>
       </c>
@@ -22538,7 +22531,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="40" t="s">
         <v>60</v>
       </c>
@@ -22645,7 +22638,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="40" t="s">
         <v>61</v>
       </c>
@@ -22752,7 +22745,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
@@ -22859,7 +22852,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="40" t="s">
         <v>63</v>
       </c>
@@ -22966,7 +22959,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>43</v>
       </c>
@@ -23083,7 +23076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="40" t="s">
         <v>64</v>
       </c>
@@ -23190,7 +23183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
         <v>65</v>
       </c>
@@ -23297,7 +23290,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
@@ -23404,7 +23397,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
         <v>67</v>
       </c>
@@ -23511,7 +23504,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="40" t="s">
         <v>68</v>
       </c>
@@ -23628,7 +23621,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
@@ -23735,7 +23728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="40" t="s">
         <v>53</v>
       </c>
@@ -23842,7 +23835,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="40" t="s">
         <v>55</v>
       </c>
@@ -23949,7 +23942,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="40" t="s">
         <v>56</v>
       </c>
@@ -24056,7 +24049,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="40" t="s">
         <v>57</v>
       </c>
@@ -24163,7 +24156,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" s="40" t="s">
         <v>58</v>
       </c>
@@ -24270,7 +24263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" s="40" t="s">
         <v>59</v>
       </c>
@@ -24377,7 +24370,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" s="40" t="s">
         <v>60</v>
       </c>
@@ -24484,7 +24477,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="40" t="s">
         <v>61</v>
       </c>
@@ -24591,7 +24584,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" s="40" t="s">
         <v>62</v>
       </c>
@@ -24698,7 +24691,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" s="40" t="s">
         <v>63</v>
       </c>
@@ -24805,7 +24798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34" t="s">
         <v>43</v>
       </c>
@@ -24922,7 +24915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" s="40" t="s">
         <v>64</v>
       </c>
@@ -25029,7 +25022,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A33" s="40" t="s">
         <v>65</v>
       </c>
@@ -25136,7 +25129,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A34" s="40" t="s">
         <v>66</v>
       </c>
@@ -25243,7 +25236,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A35" s="40" t="s">
         <v>67</v>
       </c>
@@ -25350,7 +25343,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A36" s="40" t="s">
         <v>68</v>
       </c>
@@ -25467,7 +25460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A37" s="40" t="s">
         <v>72</v>
       </c>
@@ -25494,7 +25487,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A38" s="40" t="s">
         <v>72</v>
       </c>
@@ -25518,7 +25511,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A39" s="40" t="s">
         <v>75</v>
       </c>
@@ -25551,7 +25544,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A40" s="40" t="s">
         <v>75</v>
       </c>
@@ -25572,14 +25565,14 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="AI42"/>
       <c r="AJ42"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A43" s="97"/>
       <c r="B43" s="98" t="s">
         <v>80</v>
@@ -25605,7 +25598,7 @@
       <c r="AI43"/>
       <c r="AJ43"/>
     </row>
-    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="99" t="s">
         <v>87</v>
       </c>
@@ -25634,7 +25627,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A45" s="97"/>
       <c r="B45" s="100" t="s">
         <v>88</v>
@@ -25663,7 +25656,7 @@
       <c r="AI45"/>
       <c r="AJ45"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A46" s="97"/>
       <c r="B46" s="100" t="s">
         <v>88</v>
@@ -25692,7 +25685,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="99" t="s">
         <v>94</v>
       </c>
@@ -25723,44 +25716,44 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>98</v>
       </c>
       <c r="AI48"/>
       <c r="AJ48"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>99</v>
       </c>
       <c r="AI49"/>
       <c r="AJ49"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>100</v>
       </c>
       <c r="AI50"/>
       <c r="AJ50"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AI51"/>
       <c r="AJ51"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AI52"/>
       <c r="AJ52"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AI53"/>
       <c r="AJ53"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AI54"/>
       <c r="AJ54"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AI55"/>
       <c r="AJ55"/>
     </row>
@@ -25782,17 +25775,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" style="10"/>
-    <col min="2" max="2" width="69.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="10"/>
+    <col min="2" max="2" width="69.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="10.59765625" style="10"/>
+    <col min="6" max="16384" width="10.6640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -25838,7 +25831,7 @@
       <c r="AQ1" s="9"/>
       <c r="AR1" s="9"/>
     </row>
-    <row r="2" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="11" t="s">
         <v>101</v>
@@ -25886,7 +25879,7 @@
       <c r="AQ2" s="9"/>
       <c r="AR2" s="9"/>
     </row>
-    <row r="3" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -25932,7 +25925,7 @@
       <c r="AQ3" s="9"/>
       <c r="AR3" s="9"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>102</v>
@@ -25982,7 +25975,7 @@
       <c r="AQ4" s="9"/>
       <c r="AR4" s="9"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
@@ -26090,7 +26083,7 @@
       <c r="AQ5" s="15"/>
       <c r="AR5" s="15"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>105</v>
@@ -26196,7 +26189,7 @@
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>106</v>
@@ -26302,7 +26295,7 @@
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="25"/>
@@ -26348,7 +26341,7 @@
       <c r="AQ8" s="25"/>
       <c r="AR8" s="25"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
         <v>107</v>
@@ -26396,7 +26389,7 @@
       <c r="AQ9" s="25"/>
       <c r="AR9" s="25"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
         <v>108</v>
@@ -26444,7 +26437,7 @@
       <c r="AQ10" s="25"/>
       <c r="AR10" s="25"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="12" t="s">
         <v>109</v>
@@ -26550,7 +26543,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
         <v>110</v>
@@ -26598,7 +26591,7 @@
       <c r="AQ12" s="25"/>
       <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
         <v>109</v>
@@ -26704,7 +26697,7 @@
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
         <v>111</v>
@@ -26752,7 +26745,7 @@
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
         <v>109</v>
@@ -26858,7 +26851,7 @@
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="25"/>
@@ -26904,7 +26897,7 @@
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -26950,7 +26943,7 @@
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
     </row>
-    <row r="18" spans="1:44" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="11" t="s">
         <v>112</v>
@@ -26998,7 +26991,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
     </row>
-    <row r="19" spans="1:44" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -27044,7 +27037,7 @@
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -27091,7 +27084,7 @@
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>112</v>
@@ -27142,7 +27135,7 @@
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -27188,7 +27181,7 @@
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -27234,7 +27227,7 @@
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -27276,7 +27269,7 @@
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -27322,7 +27315,7 @@
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -27368,7 +27361,7 @@
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -27422,20 +27415,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="144" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -27443,7 +27436,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>406</v>
       </c>
@@ -27451,7 +27444,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>358</v>
       </c>
@@ -27459,7 +27452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -27471,13 +27464,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="144" t="s">
         <v>119</v>
       </c>
       <c r="B9" s="144"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -27485,7 +27478,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -27499,7 +27492,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -27510,13 +27503,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="144" t="s">
         <v>122</v>
       </c>
       <c r="B14" s="144"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -27524,7 +27517,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -27535,7 +27528,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -27563,13 +27556,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -27588,31 +27581,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA419E9D-493B-4DCE-A933-2A9A9AF40246}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" outlineLevelCol="2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.09765625" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="8.83203125" hidden="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="7" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="11.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="6" max="6" width="16.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="7" max="8" width="8.8984375" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="9" max="9" width="10.59765625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="10" max="10" width="8.3984375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="5" max="5" width="11.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="6" max="6" width="16.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="7" max="8" width="8.83203125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="9" max="9" width="10.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="13" width="8" customWidth="1"/>
-    <col min="14" max="15" width="16.59765625" customWidth="1"/>
-    <col min="16" max="16" width="20.59765625" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" customWidth="1"/>
     <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.69921875" customWidth="1"/>
-    <col min="20" max="20" width="34.19921875" customWidth="1"/>
-    <col min="21" max="21" width="33.8984375" customWidth="1"/>
-    <col min="22" max="22" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.6640625" customWidth="1"/>
+    <col min="20" max="20" width="34.1640625" customWidth="1"/>
+    <col min="21" max="21" width="33.83203125" customWidth="1"/>
+    <col min="22" max="22" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -27696,7 +27689,7 @@
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -27752,7 +27745,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -27808,7 +27801,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -27862,7 +27855,7 @@
       </c>
       <c r="W4" s="60"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -27916,7 +27909,7 @@
       </c>
       <c r="W5" s="60"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -27970,7 +27963,7 @@
       </c>
       <c r="W6" s="60"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -28024,7 +28017,7 @@
       </c>
       <c r="W7" s="60"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -28078,7 +28071,7 @@
       </c>
       <c r="W8" s="60"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -28132,7 +28125,7 @@
       </c>
       <c r="W9" s="60"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -28186,7 +28179,7 @@
       </c>
       <c r="W10" s="60"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -28240,7 +28233,7 @@
       </c>
       <c r="W11" s="60"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -28294,7 +28287,7 @@
       </c>
       <c r="W12" s="60"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -28348,7 +28341,7 @@
       </c>
       <c r="W13" s="60"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -28402,7 +28395,7 @@
       </c>
       <c r="W14" s="60"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -28456,7 +28449,7 @@
       </c>
       <c r="W15" s="60"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -28513,7 +28506,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -28570,7 +28563,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -28612,7 +28605,7 @@
       </c>
       <c r="W18" s="60"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -28654,7 +28647,7 @@
       </c>
       <c r="W19" s="60"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -28690,7 +28683,7 @@
       </c>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -28726,7 +28719,7 @@
       </c>
       <c r="W21" s="60"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -28762,7 +28755,7 @@
       </c>
       <c r="W22" s="60"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -28798,7 +28791,7 @@
       </c>
       <c r="W23" s="60"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -28840,7 +28833,7 @@
       </c>
       <c r="W24" s="60"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -28891,7 +28884,7 @@
       </c>
       <c r="W25" s="60"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -28927,7 +28920,7 @@
       </c>
       <c r="W26" s="60"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -28963,7 +28956,7 @@
       </c>
       <c r="W27" s="60"/>
     </row>
-    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48" t="s">
         <v>150</v>
       </c>
@@ -28993,7 +28986,7 @@
       </c>
       <c r="W28" s="90"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -29029,7 +29022,7 @@
       </c>
       <c r="W29" s="60"/>
     </row>
-    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48" t="s">
         <v>260</v>
       </c>
@@ -29062,7 +29055,7 @@
       </c>
       <c r="W30" s="90"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -29098,7 +29091,7 @@
       </c>
       <c r="W31" s="60"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -29134,7 +29127,7 @@
       </c>
       <c r="W32" s="60"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -29170,7 +29163,7 @@
       </c>
       <c r="W33" s="60"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -29206,7 +29199,7 @@
       </c>
       <c r="W34" s="60"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -29257,7 +29250,7 @@
       </c>
       <c r="W35" s="60"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -29293,7 +29286,7 @@
       </c>
       <c r="W36" s="60"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -29329,7 +29322,7 @@
       </c>
       <c r="W37" s="60"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -29365,7 +29358,7 @@
       </c>
       <c r="W38" s="60"/>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -29401,7 +29394,7 @@
       </c>
       <c r="W39" s="60"/>
     </row>
-    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48" t="s">
         <v>150</v>
       </c>
@@ -29428,7 +29421,7 @@
       </c>
       <c r="W40" s="90"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -29467,7 +29460,7 @@
       </c>
       <c r="W41" s="60"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -29509,7 +29502,7 @@
       </c>
       <c r="W42" s="60"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -29542,7 +29535,7 @@
       </c>
       <c r="W43" s="60"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>150</v>
       </c>
@@ -29575,7 +29568,7 @@
       </c>
       <c r="W44" s="60"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -29608,7 +29601,7 @@
       </c>
       <c r="W45" s="60"/>
     </row>
-    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48" t="s">
         <v>150</v>
       </c>
@@ -29635,7 +29628,7 @@
       </c>
       <c r="W46" s="90"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -29669,7 +29662,7 @@
       </c>
       <c r="W47" s="60"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>260</v>
       </c>
@@ -29703,7 +29696,7 @@
       </c>
       <c r="W48" s="60"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -29751,7 +29744,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -29799,7 +29792,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -29847,7 +29840,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -29895,7 +29888,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -29937,7 +29930,7 @@
       </c>
       <c r="W53" s="60"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -29973,7 +29966,7 @@
       </c>
       <c r="W54" s="60"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -30009,7 +30002,7 @@
       </c>
       <c r="W55" s="60"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>150</v>
       </c>
@@ -30045,7 +30038,7 @@
       </c>
       <c r="W56" s="60"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>150</v>
       </c>
@@ -30102,34 +30095,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99968075-C79E-496E-8470-A0201C505FA7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="11.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.8984375" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.6640625" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.09765625" customWidth="1"/>
-    <col min="19" max="22" width="20.09765625" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" customWidth="1"/>
+    <col min="19" max="22" width="20.1640625" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.09765625" customWidth="1"/>
+    <col min="26" max="28" width="15.1640625" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.59765625" customWidth="1"/>
+    <col min="32" max="32" width="37.6640625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.59765625" customWidth="1"/>
+    <col min="36" max="36" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -30189,7 +30182,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="117" t="s">
         <v>151</v>
       </c>
@@ -30220,7 +30213,7 @@
       <c r="R2" s="118"/>
       <c r="AI2" s="119"/>
     </row>
-    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="117" t="s">
         <v>151</v>
       </c>
@@ -30252,7 +30245,7 @@
       <c r="R3" s="118"/>
       <c r="AI3" s="119"/>
     </row>
-    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="117" t="s">
         <v>151</v>
       </c>
@@ -30284,7 +30277,7 @@
       <c r="R4" s="118"/>
       <c r="AI4" s="119"/>
     </row>
-    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="117" t="s">
         <v>151</v>
       </c>
@@ -30317,7 +30310,7 @@
       <c r="AD5" s="120"/>
       <c r="AI5" s="119"/>
     </row>
-    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="117" t="s">
         <v>185</v>
       </c>
@@ -30348,7 +30341,7 @@
       </c>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="117" t="s">
         <v>185</v>
       </c>
@@ -30380,7 +30373,7 @@
       <c r="O7" s="122"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="117" t="s">
         <v>185</v>
       </c>
@@ -30412,7 +30405,7 @@
       <c r="R8" s="121"/>
       <c r="AD8" s="120"/>
     </row>
-    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -30447,7 +30440,7 @@
       <c r="W9" s="114"/>
       <c r="AF9" s="115"/>
     </row>
-    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -30484,7 +30477,7 @@
       <c r="R10" s="113"/>
       <c r="AI10" s="116"/>
     </row>
-    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="117" t="s">
         <v>214</v>
       </c>
@@ -30515,7 +30508,7 @@
       <c r="R11" s="121"/>
       <c r="AI11" s="119"/>
     </row>
-    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="117" t="s">
         <v>214</v>
       </c>
@@ -30546,7 +30539,7 @@
       <c r="R12" s="121"/>
       <c r="AI12" s="119"/>
     </row>
-    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>223</v>
       </c>
@@ -30581,7 +30574,7 @@
       <c r="AA13" s="124"/>
       <c r="AB13" s="124"/>
     </row>
-    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>227</v>
       </c>
@@ -30618,7 +30611,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
@@ -30650,7 +30643,7 @@
       <c r="AI15" s="116"/>
       <c r="AL15" s="127"/>
     </row>
-    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>230</v>
       </c>
@@ -30682,7 +30675,7 @@
       <c r="AI16" s="116"/>
       <c r="AL16" s="127"/>
     </row>
-    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>234</v>
       </c>
@@ -30713,7 +30706,7 @@
       <c r="R17" s="123"/>
       <c r="AI17" s="116"/>
     </row>
-    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="128" t="s">
         <v>240</v>
       </c>
@@ -30741,7 +30734,7 @@
       <c r="R18" s="129"/>
       <c r="W18" s="130"/>
     </row>
-    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>247</v>
       </c>
@@ -30776,7 +30769,7 @@
       <c r="R19" s="123"/>
       <c r="X19" s="123"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>247</v>
       </c>
@@ -30808,7 +30801,7 @@
       <c r="R20" s="123"/>
       <c r="X20" s="123"/>
     </row>
-    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="127" t="s">
         <v>251</v>
       </c>
@@ -30827,7 +30820,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>255</v>
       </c>
@@ -30869,7 +30862,7 @@
       <c r="AB22" s="124"/>
       <c r="AF22" s="115"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>267</v>
       </c>
@@ -30903,7 +30896,7 @@
       <c r="X23" s="123"/>
       <c r="AI23" s="116"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
@@ -30937,7 +30930,7 @@
       <c r="X24" s="123"/>
       <c r="AI24" s="116"/>
     </row>
-    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -30961,7 +30954,7 @@
       </c>
       <c r="AI25" s="93"/>
     </row>
-    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="117" t="s">
         <v>275</v>
       </c>
@@ -30991,7 +30984,7 @@
       </c>
       <c r="X26" s="138"/>
     </row>
-    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
@@ -31025,7 +31018,7 @@
       <c r="R27" s="126"/>
       <c r="X27" s="123"/>
     </row>
-    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -31053,7 +31046,7 @@
       <c r="AI28" s="53"/>
       <c r="AJ28" s="48"/>
     </row>
-    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -31081,7 +31074,7 @@
       <c r="AI29" s="53"/>
       <c r="AJ29" s="48"/>
     </row>
-    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -31109,7 +31102,7 @@
       <c r="AI30" s="53"/>
       <c r="AJ30" s="48"/>
     </row>
-    <row r="31" spans="1:36" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -31138,7 +31131,7 @@
       <c r="AI31" s="53"/>
       <c r="AJ31" s="48"/>
     </row>
-    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -31155,7 +31148,7 @@
       <c r="AH32"/>
       <c r="AI32" s="87"/>
     </row>
-    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="112" t="s">
         <v>294</v>
       </c>
@@ -31189,7 +31182,7 @@
       <c r="L33" s="41"/>
       <c r="X33" s="132"/>
     </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>301</v>
       </c>
@@ -31220,7 +31213,7 @@
       <c r="Q34" s="127"/>
       <c r="AI34" s="116"/>
     </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>307</v>
       </c>
@@ -31249,7 +31242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>311</v>
       </c>
@@ -31281,7 +31274,7 @@
       <c r="X36" s="133"/>
       <c r="AA36" s="134"/>
     </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
@@ -31308,7 +31301,7 @@
       </c>
       <c r="R37" s="126"/>
     </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="127" t="s">
         <v>319</v>
       </c>
@@ -31324,7 +31317,7 @@
       </c>
       <c r="F38" s="127"/>
     </row>
-    <row r="39" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:35" s="117" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="122" t="s">
         <v>329</v>
       </c>
@@ -31356,7 +31349,7 @@
       <c r="R39" s="141"/>
       <c r="X39" s="141"/>
     </row>
-    <row r="40" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:35" s="117" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="122" t="s">
         <v>329</v>
       </c>
@@ -31390,7 +31383,7 @@
       <c r="AE40" s="120"/>
       <c r="AF40" s="142"/>
     </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="124" t="s">
         <v>336</v>
       </c>
@@ -31422,7 +31415,7 @@
       <c r="AD41" s="135"/>
       <c r="AE41" s="43"/>
     </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="124" t="s">
         <v>342</v>
       </c>
@@ -31453,7 +31446,7 @@
       <c r="X42" s="123"/>
       <c r="AE42" s="43"/>
     </row>
-    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="124" t="s">
         <v>345</v>
       </c>
@@ -31501,7 +31494,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
     </row>
-    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="124" t="s">
         <v>345</v>
       </c>
@@ -31549,7 +31542,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
     </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
@@ -31577,10 +31570,10 @@
       <c r="R45" s="123"/>
       <c r="X45" s="123"/>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A46" s="48"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50" s="143" t="s">
         <v>35</v>
       </c>
@@ -31615,7 +31608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B51" s="143" t="s">
         <v>402</v>
       </c>
@@ -31634,7 +31627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52" s="143"/>
       <c r="C52" s="143" t="s">
         <v>404</v>
@@ -31651,7 +31644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53" s="143" t="s">
         <v>405</v>
       </c>
@@ -31670,7 +31663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54" s="143"/>
       <c r="C54" s="143" t="s">
         <v>404</v>

--- a/data/Master Standardisation DACCS.xlsx
+++ b/data/Master Standardisation DACCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Documents/GitHub/DACCSvDACCU/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/_DACCS vs Synfuels/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35709E9C-8B18-9F42-8FC9-5C3A93149941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6723" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EC0C5E-1BA4-4E65-B2EC-42F6D02F8A4B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" tabRatio="973" firstSheet="10" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="2" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,9 @@
     <externalReference r:id="rId43"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Studies current &amp;future cost'!$A$1:$AL$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Study Parameters'!$A$1:$AL$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3374,17 +3374,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="36">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3929,21 +3929,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3984,7 +3984,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4046,10 +4046,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4064,7 +4064,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -4076,13 +4076,13 @@
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -4118,7 +4118,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4193,7 +4193,7 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOJKWGB3X4BKUBCKRJQPP2RTUQZ4">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -4213,22 +4213,22 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>365.78131677587601</v>
+            <v>376.52345618890524</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>300.12129261616826</v>
+            <v>310.85768113181723</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>464.78906236439371</v>
+            <v>475.54078660638976</v>
           </cell>
         </row>
       </sheetData>
@@ -4249,16 +4249,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4579,48 +4579,48 @@
       <sheetData sheetId="3">
         <row r="31">
           <cell r="D31">
-            <v>247.78573833085827</v>
+            <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>80.835242312744612</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
-            <v>247.78573833085827</v>
+            <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>63.180590409419352</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="31">
           <cell r="D31">
-            <v>247.78573833085827</v>
+            <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>80.835242312744612</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
-            <v>247.78573833085827</v>
+            <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>63.180590409419352</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="5">
         <row r="34">
           <cell r="D34">
-            <v>284.73955537191881</v>
+            <v>292.47958561757542</v>
           </cell>
           <cell r="G34">
-            <v>103.93137796340747</v>
+            <v>107.94825932901442</v>
           </cell>
           <cell r="I34">
-            <v>284.73955537191881</v>
+            <v>292.47958561757542</v>
           </cell>
           <cell r="L34">
-            <v>86.276726060082211</v>
+            <v>90.299117899440446</v>
           </cell>
         </row>
       </sheetData>
@@ -4644,48 +4644,48 @@
       <sheetData sheetId="8">
         <row r="31">
           <cell r="D31">
-            <v>203.82055244956476</v>
+            <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>65.772036515814634</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
-            <v>203.82055244956476</v>
+            <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>45.257602134126707</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="31">
           <cell r="D31">
-            <v>203.82055244956476</v>
+            <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>65.772036515814634</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
-            <v>203.82055244956476</v>
+            <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>45.257602134126707</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="34">
           <cell r="D34">
-            <v>240.77436949062533</v>
+            <v>289.21430381427916</v>
           </cell>
           <cell r="G34">
-            <v>88.868172166477493</v>
+            <v>118.82157519411055</v>
           </cell>
           <cell r="I34">
-            <v>240.77436949062533</v>
+            <v>289.21430381427916</v>
           </cell>
           <cell r="L34">
-            <v>68.353737784789558</v>
+            <v>98.307140812422617</v>
           </cell>
         </row>
       </sheetData>
@@ -5093,7 +5093,7 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOLYN5I7UQKGEFHIRCJ7WP2AS65S">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -5113,22 +5113,22 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>164.50687321381022</v>
+            <v>170.41354109154099</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>107.72136450834213</v>
+            <v>113.7451627146863</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>303.80972003368208</v>
+            <v>311.65822312471437</v>
           </cell>
         </row>
       </sheetData>
@@ -5149,16 +5149,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5631,7 +5631,7 @@
             <v>145.45192472670769</v>
           </cell>
           <cell r="F24">
-            <v>111.86001980209357</v>
+            <v>112.66928210128302</v>
           </cell>
         </row>
       </sheetData>
@@ -5647,7 +5647,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>119.54813300102964</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5663,7 +5663,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>144.54813300102964</v>
+            <v>145.35739530021908</v>
           </cell>
         </row>
       </sheetData>
@@ -5696,7 +5696,7 @@
             <v>186.68727529198395</v>
           </cell>
           <cell r="F24">
-            <v>147.43956539237121</v>
+            <v>148.24882769156065</v>
           </cell>
         </row>
       </sheetData>
@@ -5712,7 +5712,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>119.54813300102964</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5728,7 +5728,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>144.54813300102964</v>
+            <v>145.35739530021908</v>
           </cell>
         </row>
       </sheetData>
@@ -6007,7 +6007,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>128.52160188054003</v>
+            <v>134.11219617439485</v>
           </cell>
         </row>
       </sheetData>
@@ -6019,7 +6019,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>116.90647783174505</v>
+            <v>122.49707212559984</v>
           </cell>
         </row>
       </sheetData>
@@ -6031,7 +6031,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>141.90647783174506</v>
+            <v>147.49707212559986</v>
           </cell>
         </row>
       </sheetData>
@@ -6076,7 +6076,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>138.51725671085572</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6092,7 +6092,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>138.51725671085572</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6108,7 +6108,7 @@
             <v>263.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>162.86808564420988</v>
+            <v>163.71895198084354</v>
           </cell>
         </row>
       </sheetData>
@@ -6208,7 +6208,7 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOIQCVRYCOU64NH2ZBHGEIPL4V6E">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6323,7 +6323,7 @@
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOJOYEX2SMZKTJELRPRIT43AB5AX">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6343,22 +6343,22 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>213.49630616847861</v>
+            <v>233.35148149487728</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>115.61913305350822</v>
+            <v>131.99019858880641</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>487.88890210802742</v>
+            <v>522.16362117034964</v>
           </cell>
         </row>
       </sheetData>
@@ -6379,16 +6379,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6397,7 +6397,7 @@
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOJL7NTLSCSJEBALTMVDUXJ5OMPW">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6471,7 +6471,7 @@
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOMDFFUKA7VDTVGY3W5MLNF5DTYA">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6491,22 +6491,22 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>992.56280998744671</v>
+            <v>1173.97198503103</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>881.0126575386389</v>
+            <v>1062.3247136090472</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>1182.6818974130827</v>
+            <v>1364.2529374119576</v>
           </cell>
         </row>
       </sheetData>
@@ -6527,16 +6527,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6545,7 +6545,7 @@
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOL2JCYISYZIHNDYS6YOFG2L72P7">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6619,7 +6619,7 @@
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="b!E1dk8KjZL0uvs3_bw3eO8etGqPVVx6FJnkDkPD0O-HnfSyWEjm0zT58vSaSr9wig" itemId="01ZW6MSOMEECFIBGMI2NELWYV7EXIE26F5">
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -6639,22 +6639,22 @@
       <sheetName val="Breakdown"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>383.03674279412837</v>
+            <v>416.10639561160389</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>290.67652425536556</v>
+            <v>323.72847294776523</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>540.29730560518931</v>
+            <v>573.39646529779134</v>
           </cell>
         </row>
       </sheetData>
@@ -6675,16 +6675,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6702,6 +6702,9 @@
       <sheetName val="LS_summary"/>
       <sheetName val="SS_summary"/>
       <sheetName val="CaO_summary"/>
+      <sheetName val="LS_summary_11$MWh"/>
+      <sheetName val="SS_summary_11$MWh"/>
+      <sheetName val="CaO_summary_11$MWh"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -6709,72 +6712,90 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="B2">
-            <v>894.39776183919753</v>
+            <v>827</v>
           </cell>
           <cell r="J2">
-            <v>669.94069463308699</v>
+            <v>635</v>
           </cell>
           <cell r="R2">
-            <v>521.31303134173265</v>
+            <v>527</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51">
-            <v>544.22032736034907</v>
+            <v>532</v>
           </cell>
           <cell r="J51">
-            <v>341.46121706214058</v>
+            <v>349</v>
           </cell>
           <cell r="R51">
-            <v>225.6544183898213</v>
+            <v>226</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="2">
           <cell r="B2">
-            <v>1392.3242644152151</v>
+            <v>1381</v>
           </cell>
           <cell r="J2">
-            <v>1282.314450530346</v>
+            <v>1279</v>
           </cell>
           <cell r="R2">
-            <v>1180.094323057237</v>
+            <v>1231</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51">
-            <v>579.4216269225069</v>
+            <v>702</v>
           </cell>
           <cell r="J51">
-            <v>373.55046457825102</v>
+            <v>441</v>
           </cell>
           <cell r="R51">
-            <v>280.7967580377242</v>
+            <v>308</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="2">
           <cell r="B2">
-            <v>2874.3199941446942</v>
+            <v>2849</v>
           </cell>
           <cell r="J2">
-            <v>2481.3480043001368</v>
+            <v>2352</v>
           </cell>
           <cell r="R2">
-            <v>2153.1601565847341</v>
+            <v>2155</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51">
-            <v>834.90242160632192</v>
+            <v>624</v>
           </cell>
           <cell r="J51">
-            <v>371.36449627097238</v>
+            <v>372</v>
           </cell>
           <cell r="R51">
-            <v>230.08236375974619</v>
+            <v>318</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="51">
+          <cell r="R51">
+            <v>280</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7">
+        <row r="51">
+          <cell r="B51">
+            <v>575</v>
+          </cell>
+          <cell r="R51">
+            <v>260</v>
           </cell>
         </row>
       </sheetData>
@@ -7383,9 +7404,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7397,35 +7418,35 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AL46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetPr codeName="Sheet6" filterMode="1"/>
+  <dimension ref="A1:AL47"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.6640625" customWidth="1"/>
+    <col min="11" max="11" width="6.875" customWidth="1"/>
+    <col min="12" max="12" width="26.75" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" customWidth="1"/>
-    <col min="19" max="22" width="20.1640625" customWidth="1"/>
+    <col min="18" max="18" width="18.125" customWidth="1"/>
+    <col min="19" max="22" width="20.125" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.1640625" customWidth="1"/>
+    <col min="26" max="28" width="15.125" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.6640625" customWidth="1"/>
+    <col min="32" max="32" width="37.625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.6640625" customWidth="1"/>
+    <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" s="51" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7539,7 +7560,7 @@
       </c>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7646,7 +7667,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7746,7 +7767,7 @@
       </c>
       <c r="AI3" s="53"/>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -7846,7 +7867,7 @@
       </c>
       <c r="AI4" s="53"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -7946,7 +7967,7 @@
       </c>
       <c r="AI5" s="53"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -8045,7 +8066,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -8144,7 +8165,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -8243,7 +8264,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" hidden="1">
       <c r="A9" t="s">
         <v>199</v>
       </c>
@@ -8342,7 +8363,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" hidden="1">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -8446,7 +8467,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -8535,7 +8556,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38">
       <c r="A12" t="s">
         <v>214</v>
       </c>
@@ -8619,7 +8640,7 @@
       </c>
       <c r="AI12" s="53"/>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" hidden="1">
       <c r="A13" t="s">
         <v>223</v>
       </c>
@@ -8710,7 +8731,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" hidden="1">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -8804,7 +8825,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" hidden="1">
       <c r="A15" t="s">
         <v>230</v>
       </c>
@@ -8900,7 +8921,7 @@
       </c>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" hidden="1">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -8996,7 +9017,7 @@
       </c>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:37" hidden="1">
       <c r="A17" t="s">
         <v>234</v>
       </c>
@@ -9088,7 +9109,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="18" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1">
       <c r="A18" s="58" t="s">
         <v>240</v>
       </c>
@@ -9183,7 +9204,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" hidden="1">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -9270,7 +9291,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" hidden="1">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -9357,7 +9378,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1">
       <c r="A21" s="48" t="s">
         <v>251</v>
       </c>
@@ -9381,7 +9402,7 @@
       </c>
       <c r="AH21"/>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" hidden="1">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -9480,7 +9501,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" hidden="1">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -9584,7 +9605,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" hidden="1">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -9688,7 +9709,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:37" s="60" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -9717,7 +9738,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:37">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -9806,7 +9827,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:37" hidden="1">
       <c r="A27" t="s">
         <v>278</v>
       </c>
@@ -9907,7 +9928,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" hidden="1">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -9983,7 +10004,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" hidden="1">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -10059,7 +10080,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" hidden="1">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -10135,7 +10156,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" ht="25.9" hidden="1" customHeight="1">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -10211,7 +10232,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="32" spans="1:37" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -10235,7 +10256,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:37" s="58" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1">
       <c r="A33" s="58" t="s">
         <v>294</v>
       </c>
@@ -10324,7 +10345,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" hidden="1">
       <c r="A34" t="s">
         <v>301</v>
       </c>
@@ -10410,7 +10431,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" hidden="1">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -10502,7 +10523,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:37" hidden="1">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -10594,7 +10615,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:37" hidden="1">
       <c r="A37" t="s">
         <v>315</v>
       </c>
@@ -10686,7 +10707,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" hidden="1">
       <c r="A38" s="48" t="s">
         <v>319</v>
       </c>
@@ -10700,7 +10721,7 @@
       </c>
       <c r="F38" s="48"/>
     </row>
-    <row r="39" spans="1:37" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37">
       <c r="A39" s="3" t="s">
         <v>329</v>
       </c>
@@ -10797,7 +10818,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37">
       <c r="A40" s="3" t="s">
         <v>329</v>
       </c>
@@ -10893,7 +10914,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" hidden="1">
       <c r="A41" s="55" t="s">
         <v>336</v>
       </c>
@@ -10985,7 +11006,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" hidden="1">
       <c r="A42" s="55" t="s">
         <v>342</v>
       </c>
@@ -11068,7 +11089,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1">
       <c r="A43" s="55" t="s">
         <v>345</v>
       </c>
@@ -11156,7 +11177,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:37" s="92" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1">
       <c r="A44" s="55" t="s">
         <v>345</v>
       </c>
@@ -11241,7 +11262,7 @@
       </c>
       <c r="AH44"/>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:37" hidden="1">
       <c r="A45" t="s">
         <v>348</v>
       </c>
@@ -11319,11 +11340,22 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:37" hidden="1">
       <c r="A46" s="48"/>
     </row>
+    <row r="47" spans="1:37" hidden="1"/>
   </sheetData>
-  <autoFilter ref="A1:AL47" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}"/>
+  <autoFilter ref="A1:AL47" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Fasihi et al. 2019"/>
+        <filter val="Keith et al. 2018"/>
+        <filter val="Pett-Ridge et al. 2024"/>
+        <filter val="Sievert et al. 2024"/>
+        <filter val="Young et al. 2023"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="AG1:AH1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"will exclude"</formula>
@@ -11353,29 +11385,29 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}">
-  <sheetPr codeName="Sheet7">
+  <sheetPr codeName="Sheet7" filterMode="1">
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:W180"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="40.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="13" width="24.1640625" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="18.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="13.625" customWidth="1"/>
+    <col min="12" max="13" width="24.125" customWidth="1"/>
+    <col min="14" max="14" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23">
       <c r="L1" s="144" t="s">
         <v>655</v>
       </c>
@@ -11390,7 +11422,7 @@
       <c r="Q1" s="144"/>
       <c r="R1" s="144"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11461,7 +11493,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" hidden="1">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -11504,10 +11536,10 @@
       <c r="M3" s="30"/>
       <c r="O3" s="30">
         <f>'[1]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>403.01854968021763</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+        <v>414.8542592918007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" hidden="1">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -11549,10 +11581,10 @@
       <c r="M4" s="30"/>
       <c r="O4" s="30">
         <f>'[1]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G4))</f>
-        <v>330.6742103299726</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+        <v>342.50358359189738</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" hidden="1">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11594,10 +11626,10 @@
       <c r="M5" s="30"/>
       <c r="O5" s="30">
         <f>'[1]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G5))</f>
-        <v>512.10547184973177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+        <v>523.95174204407829</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -11638,10 +11670,10 @@
       <c r="M6" s="30"/>
       <c r="O6" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>181.25398541249336</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+        <v>187.76196330078002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11682,10 +11714,10 @@
       <c r="M7" s="30"/>
       <c r="O7" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>118.68760404820473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+        <v>125.3246363550643</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -11726,10 +11758,10 @@
       <c r="M8" s="30"/>
       <c r="O8" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>334.73812666531126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+        <v>343.38562228042122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" hidden="1">
       <c r="A9" t="str">
         <f>'Study Parameters'!A3</f>
         <v>Young et al. 2023</v>
@@ -11780,7 +11812,7 @@
         <v>2060.169523488109</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" hidden="1">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -11825,7 +11857,7 @@
         <v>1488.7216799143798</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" hidden="1">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -11870,7 +11902,7 @@
         <v>2729.5646158724885</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -11912,10 +11944,10 @@
       <c r="N12" s="30"/>
       <c r="O12" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G12))</f>
-        <v>235.23063570473388</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+        <v>257.10710559724805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -11957,10 +11989,10 @@
       <c r="N13" s="30"/>
       <c r="O13" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G13))</f>
-        <v>127.38938043426646</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+        <v>145.42705154035619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -12002,10 +12034,10 @@
       <c r="N14" s="30"/>
       <c r="O14" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G14))</f>
-        <v>537.5569191608829</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+        <v>575.32086973372702</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" hidden="1">
       <c r="A15" t="str">
         <f>'Study Parameters'!A4</f>
         <v>Young et al. 2023</v>
@@ -12055,7 +12087,7 @@
         <v>1308.9151041939408</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" hidden="1">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -12099,7 +12131,7 @@
         <v>1185.9075603382862</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" hidden="1">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -12143,7 +12175,7 @@
         <v>1518.5576325147504</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -12183,11 +12215,11 @@
       </c>
       <c r="M18" s="30"/>
       <c r="O18" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G17))</f>
-        <v>1093.6075895663253</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[6]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G18))</f>
+        <v>1293.4845632433239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -12227,11 +12259,11 @@
       </c>
       <c r="M19" s="30"/>
       <c r="O19" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G17))</f>
-        <v>970.70141969195765</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[6]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G19))</f>
+        <v>1170.4713874998199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -12271,11 +12303,11 @@
       </c>
       <c r="M20" s="30"/>
       <c r="O20" s="139">
-        <f>'[6]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G17))</f>
-        <v>1303.0811612516566</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[6]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G20))</f>
+        <v>1503.1364780438823</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" hidden="1">
       <c r="A21" t="str">
         <f>'Study Parameters'!A5</f>
         <v>Young et al. 2023</v>
@@ -12325,7 +12357,7 @@
         <v>484.59306078439545</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" hidden="1">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -12369,7 +12401,7 @@
         <v>382.81191676230259</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" hidden="1">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -12413,7 +12445,7 @@
         <v>657.89384726964306</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -12454,10 +12486,10 @@
       <c r="M24" s="30"/>
       <c r="O24" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G24))</f>
-        <v>422.03061084640188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+        <v>458.46681714146951</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -12498,10 +12530,10 @@
       <c r="M25" s="30"/>
       <c r="O25" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G25))</f>
-        <v>320.26794660828392</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>356.68464646471131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -12542,10 +12574,10 @@
       <c r="M26" s="30"/>
       <c r="O26" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G26))</f>
-        <v>595.300597691691</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>631.76931471782575</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" hidden="1">
       <c r="A27" s="48" t="str">
         <f>'Study Parameters'!A6</f>
         <v>Sievert et al. 2024</v>
@@ -12587,14 +12619,14 @@
       </c>
       <c r="L27" s="30">
         <f>[9]LS_summary!$J$2* ((1+Inputs!$C$5) ^ (2022-G27))</f>
-        <v>669.94069463308699</v>
+        <v>635</v>
       </c>
       <c r="M27" s="30"/>
       <c r="O27" s="30">
         <v>669.94069463308699</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" hidden="1">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -12631,14 +12663,14 @@
       </c>
       <c r="L28" s="30">
         <f>[9]LS_summary!$R$2* ((1+Inputs!$C$5) ^ (2022-G28))</f>
-        <v>521.31303134173265</v>
+        <v>527</v>
       </c>
       <c r="M28" s="30"/>
       <c r="O28" s="30">
         <v>521.31303134173265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" hidden="1">
       <c r="A29" t="s">
         <v>185</v>
       </c>
@@ -12675,14 +12707,14 @@
       </c>
       <c r="L29" s="30">
         <f>[9]LS_summary!$B$2* ((1+Inputs!$C$5) ^ (2022-G29))</f>
-        <v>894.39776183919753</v>
+        <v>827</v>
       </c>
       <c r="M29" s="30"/>
       <c r="O29" s="30">
         <v>894.39776183919753</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -12718,14 +12750,15 @@
       </c>
       <c r="L30" s="30">
         <f>[9]LS_summary!$J$51* ((1+Inputs!$C$5) ^ (2022-G30))</f>
-        <v>341.46121706214058</v>
+        <v>349</v>
       </c>
       <c r="M30" s="30"/>
       <c r="O30" s="30">
-        <v>341.46121706214058</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]LS_summary!$J$51</f>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -12761,14 +12794,15 @@
       </c>
       <c r="L31" s="30">
         <f>[9]LS_summary!$R$51* ((1+Inputs!$C$5) ^ (2022-G31))</f>
-        <v>225.6544183898213</v>
+        <v>226</v>
       </c>
       <c r="M31" s="30"/>
       <c r="O31" s="30">
-        <v>225.6544183898213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]LS_summary!$R$51</f>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -12804,14 +12838,15 @@
       </c>
       <c r="L32" s="30">
         <f>[9]LS_summary!$B$51* ((1+Inputs!$C$5) ^ (2022-G32))</f>
-        <v>544.22032736034907</v>
+        <v>532</v>
       </c>
       <c r="M32" s="30"/>
       <c r="O32" s="30">
-        <v>544.22032736034907</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]LS_summary!$B$51</f>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" hidden="1">
       <c r="A33" t="str">
         <f>'Study Parameters'!A7</f>
         <v>Sievert et al. 2024</v>
@@ -12853,14 +12888,14 @@
       </c>
       <c r="L33" s="30">
         <f>[9]SS_summary!$J$2* ((1+Inputs!$C$5) ^ (2022-G33))</f>
-        <v>1282.314450530346</v>
+        <v>1279</v>
       </c>
       <c r="M33" s="30"/>
       <c r="O33" s="30">
         <v>1282.314450530346</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" hidden="1">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -12896,14 +12931,14 @@
       </c>
       <c r="L34" s="30">
         <f>[9]SS_summary!$R$2* ((1+Inputs!$C$5) ^ (2022-G34))</f>
-        <v>1180.094323057237</v>
+        <v>1231</v>
       </c>
       <c r="M34" s="30"/>
       <c r="O34" s="30">
         <v>1180.094323057237</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" hidden="1">
       <c r="A35" t="s">
         <v>185</v>
       </c>
@@ -12939,14 +12974,14 @@
       </c>
       <c r="L35" s="30">
         <f>[9]SS_summary!$B$2* ((1+Inputs!$C$5) ^ (2022-G35))</f>
-        <v>1392.3242644152151</v>
+        <v>1381</v>
       </c>
       <c r="M35" s="30"/>
       <c r="O35" s="30">
         <v>1392.3242644152151</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -12982,14 +13017,15 @@
       </c>
       <c r="L36" s="30">
         <f>[9]SS_summary!$J$51* ((1+Inputs!$C$5) ^ (2022-G36))</f>
-        <v>373.55046457825102</v>
+        <v>441</v>
       </c>
       <c r="M36" s="30"/>
       <c r="O36" s="30">
-        <v>373.55046457825102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]SS_summary!$J$51</f>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -13025,14 +13061,15 @@
       </c>
       <c r="L37" s="30">
         <f>[9]SS_summary!$R$51* ((1+Inputs!$C$5) ^ (2022-G37))</f>
-        <v>280.7967580377242</v>
+        <v>308</v>
       </c>
       <c r="M37" s="30"/>
       <c r="O37" s="30">
-        <v>280.7967580377242</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[9]SS_summary_11$MWh'!$R$51</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -13068,14 +13105,15 @@
       </c>
       <c r="L38" s="30">
         <f>[9]SS_summary!$B$51* ((1+Inputs!$C$5) ^ (2022-G38))</f>
-        <v>579.4216269225069</v>
+        <v>702</v>
       </c>
       <c r="M38" s="30"/>
       <c r="O38" s="30">
-        <v>579.4216269225069</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]SS_summary!$B$51</f>
+        <v>702</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" hidden="1">
       <c r="A39" t="str">
         <f>'Study Parameters'!A8</f>
         <v>Sievert et al. 2024</v>
@@ -13117,14 +13155,14 @@
       </c>
       <c r="L39" s="30">
         <f>[9]CaO_summary!$J$2* ((1+Inputs!$C$5) ^ (2022-G39))</f>
-        <v>2481.3480043001368</v>
+        <v>2352</v>
       </c>
       <c r="M39" s="30"/>
       <c r="O39" s="30">
         <v>2481.3480043001368</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" hidden="1">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -13160,14 +13198,14 @@
       </c>
       <c r="L40" s="30">
         <f>[9]CaO_summary!$R$2* ((1+Inputs!$C$5) ^ (2022-G40))</f>
-        <v>2153.1601565847341</v>
+        <v>2155</v>
       </c>
       <c r="M40" s="30"/>
       <c r="O40" s="30">
         <v>2153.1601565847341</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" hidden="1">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -13203,14 +13241,14 @@
       </c>
       <c r="L41" s="30">
         <f>[9]CaO_summary!$B$2* ((1+Inputs!$C$5) ^ (2022-G41))</f>
-        <v>2874.3199941446942</v>
+        <v>2849</v>
       </c>
       <c r="M41" s="30"/>
       <c r="O41" s="30">
         <v>2874.3199941446942</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -13246,14 +13284,15 @@
       </c>
       <c r="L42" s="30">
         <f>[9]CaO_summary!$J$51* ((1+Inputs!$C$5) ^ (2022-G42))</f>
-        <v>371.36449627097238</v>
+        <v>372</v>
       </c>
       <c r="M42" s="30"/>
       <c r="O42" s="30">
-        <v>371.36449627097238</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+        <f>[9]CaO_summary!$J$51</f>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -13289,14 +13328,15 @@
       </c>
       <c r="L43" s="30">
         <f>[9]CaO_summary!$R$51* ((1+Inputs!$C$5) ^ (2022-G43))</f>
-        <v>230.08236375974619</v>
+        <v>318</v>
       </c>
       <c r="M43" s="30"/>
       <c r="O43" s="30">
-        <v>230.08236375974619</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[9]CaO_summary_11$MWh'!$R$51</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -13332,14 +13372,15 @@
       </c>
       <c r="L44" s="30">
         <f>[9]CaO_summary!$B$51* ((1+Inputs!$C$5) ^ (2022-G44))</f>
-        <v>834.90242160632192</v>
+        <v>624</v>
       </c>
       <c r="M44" s="30"/>
       <c r="O44" s="30">
-        <v>834.90242160632192</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+        <f>'[9]CaO_summary_11$MWh'!$B$51</f>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" hidden="1">
       <c r="A45" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13392,7 +13433,7 @@
         <v>293.01246179996224</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" hidden="1">
       <c r="A46" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13447,7 +13488,7 @@
         <v>267.3339028754757</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" hidden="1">
       <c r="A47" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13502,7 +13543,7 @@
         <v>303.19697040786667</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" hidden="1">
       <c r="A48" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13549,7 +13590,7 @@
         <v>278.51244114406211</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" hidden="1">
       <c r="A49" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13596,7 +13637,7 @@
         <v>260.17305813012763</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" hidden="1">
       <c r="A50" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13643,7 +13684,7 @@
         <v>334.02175471233329</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" hidden="1">
       <c r="A51" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13690,7 +13731,7 @@
         <v>347.52430793993972</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" hidden="1">
       <c r="A52" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13737,7 +13778,7 @@
         <v>431.20952014305874</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" hidden="1">
       <c r="A53" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13784,7 +13825,7 @@
         <v>405.58125796275607</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" hidden="1">
       <c r="A54" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13831,7 +13872,7 @@
         <v>532.88151930075014</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" hidden="1">
       <c r="A55" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13882,7 +13923,7 @@
         <v>598.00725415939087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" hidden="1">
       <c r="A56" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13928,7 +13969,7 @@
         <v>594.26871158968584</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" hidden="1">
       <c r="A57" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13974,7 +14015,7 @@
         <v>556.61504560775791</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" hidden="1">
       <c r="A58" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14020,7 +14061,7 @@
         <v>745.92213758183834</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" hidden="1">
       <c r="A59" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14066,7 +14107,7 @@
         <v>863.3220713069054</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" hidden="1">
       <c r="A60" t="str">
         <f>'Study Parameters'!A11</f>
         <v>Fasihi et al. 2019</v>
@@ -14112,18 +14153,18 @@
       </c>
       <c r="M60" s="30">
         <f>'[12]Step 1 LCOE LS'!$I$31* ((1+Inputs!$C$5) ^ (2022-G60))</f>
-        <v>224.56987187668696</v>
+        <v>277.94108353342045</v>
       </c>
       <c r="N60" s="30">
         <f>'[12]Step 2 WACC LS'!$I$31</f>
-        <v>203.82055244956476</v>
+        <v>252.26048677321859</v>
       </c>
       <c r="O60" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$I$34</f>
-        <v>240.77436949062533</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+        <v>289.21430381427916</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" hidden="1">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -14163,18 +14204,18 @@
       </c>
       <c r="M61" s="30">
         <f>'[12]Step 1 LCOE LS'!$D$31* ((1+Inputs!$C$5) ^ (2022-G61))</f>
-        <v>224.56987187668696</v>
+        <v>277.94108353342045</v>
       </c>
       <c r="N61" s="30">
         <f>'[12]Step 2 WACC LS'!$D$31</f>
-        <v>203.82055244956476</v>
+        <v>252.26048677321859</v>
       </c>
       <c r="O61" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$D$34</f>
-        <v>240.77436949062533</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+        <v>289.21430381427916</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -14214,18 +14255,18 @@
       </c>
       <c r="M62" s="30">
         <f>'[12]Step 1 LCOE LS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G62))</f>
-        <v>49.86491200499448</v>
+        <v>82.867628361829105</v>
       </c>
       <c r="N62" s="30">
         <f>'[12]Step 2 WACC LS'!$L$31</f>
-        <v>45.257602134126707</v>
+        <v>75.211005161759758</v>
       </c>
       <c r="O62" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$L$34</f>
-        <v>68.353737784789558</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+        <v>98.307140812422617</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>214</v>
       </c>
@@ -14265,18 +14306,18 @@
       </c>
       <c r="M63" s="30">
         <f>'[12]Step 1 LCOE LS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G63))</f>
-        <v>72.467754776987945</v>
+        <v>105.47047113382258</v>
       </c>
       <c r="N63" s="30">
         <f>'[12]Step 2 WACC LS'!$G$31</f>
-        <v>65.772036515814634</v>
+        <v>95.725439543447692</v>
       </c>
       <c r="O63" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$G$34</f>
-        <v>88.868172166477493</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+        <v>118.82157519411055</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" hidden="1">
       <c r="A64" t="str">
         <f>'Study Parameters'!A12</f>
         <v>Fasihi et al. 2019</v>
@@ -14321,18 +14362,18 @@
       </c>
       <c r="M64" s="30">
         <f>'[12]Step 1 LCOE SS'!$I$31* ((1+Inputs!$C$5) ^ (2022-G64))</f>
-        <v>273.01079719917101</v>
+        <v>281.53877722718562</v>
       </c>
       <c r="N64" s="30">
         <f>'[12]Step 2 WACC SS'!$I$31</f>
-        <v>247.78573833085827</v>
+        <v>255.52576857651488</v>
       </c>
       <c r="O64" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$I$34</f>
-        <v>284.73955537191881</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+        <v>292.47958561757542</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" hidden="1">
       <c r="A65" t="s">
         <v>214</v>
       </c>
@@ -14372,18 +14413,18 @@
       </c>
       <c r="M65" s="30">
         <f>'[12]Step 1 LCOE SS'!$D$31* ((1+Inputs!$C$5) ^ (2022-G65))</f>
-        <v>273.01079719917101</v>
+        <v>281.53877722718562</v>
       </c>
       <c r="N65" s="30">
         <f>'[12]Step 2 WACC SS'!$D$31</f>
-        <v>247.78573833085827</v>
+        <v>255.52576857651488</v>
       </c>
       <c r="O65" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$D$34</f>
-        <v>284.73955537191881</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+        <v>292.47958561757542</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>214</v>
       </c>
@@ -14423,18 +14464,18 @@
       </c>
       <c r="M66" s="30">
         <f>'[12]Step 1 LCOE SS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G66))</f>
-        <v>69.612494534120472</v>
+        <v>74.0443735038629</v>
       </c>
       <c r="N66" s="30">
         <f>'[12]Step 2 WACC SS'!$L$31</f>
-        <v>63.180590409419352</v>
+        <v>67.202982248777587</v>
       </c>
       <c r="O66" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$L$34</f>
-        <v>86.276726060082211</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+        <v>90.299117899440446</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>214</v>
       </c>
@@ -14474,18 +14515,18 @@
       </c>
       <c r="M67" s="30">
         <f>'[12]Step 1 LCOE SS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G67))</f>
-        <v>89.064423538867544</v>
+        <v>93.490231058162834</v>
       </c>
       <c r="N67" s="30">
         <f>'[12]Step 2 WACC SS'!$G$31</f>
-        <v>80.835242312744612</v>
+        <v>84.85212367835156</v>
       </c>
       <c r="O67" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$G$34</f>
-        <v>103.93137796340747</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+        <v>107.94825932901442</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" hidden="1">
       <c r="A68" t="str">
         <f>'Study Parameters'!A13</f>
         <v>Mazzotti et al. 2013</v>
@@ -14531,7 +14572,7 @@
       </c>
       <c r="M68" s="30"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" hidden="1">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -14571,7 +14612,7 @@
       </c>
       <c r="M69" s="30"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" hidden="1">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -14611,7 +14652,7 @@
       </c>
       <c r="M70" s="30"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" hidden="1">
       <c r="A71" t="str">
         <f>'Study Parameters'!A14</f>
         <v>Zeman 2014</v>
@@ -14657,7 +14698,7 @@
       </c>
       <c r="M71" s="30"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" hidden="1">
       <c r="A72" t="str">
         <f>'Study Parameters'!A15</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14705,7 +14746,7 @@
       </c>
       <c r="M72" s="30"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" hidden="1">
       <c r="A73" t="s">
         <v>230</v>
       </c>
@@ -14746,7 +14787,7 @@
       </c>
       <c r="M73" s="30"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" hidden="1">
       <c r="A74" t="str">
         <f>'Study Parameters'!A16</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14793,7 +14834,7 @@
       </c>
       <c r="M74" s="30"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" hidden="1">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14833,7 +14874,7 @@
       </c>
       <c r="M75" s="30"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" hidden="1">
       <c r="A76" t="str">
         <f>'Study Parameters'!A17</f>
         <v>Terlouw et al. 2024</v>
@@ -14879,7 +14920,7 @@
       </c>
       <c r="M76" s="62"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" hidden="1">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -14919,7 +14960,7 @@
       </c>
       <c r="M77" s="62"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" hidden="1">
       <c r="A78" t="str">
         <f>'Study Parameters'!A18</f>
         <v>McQueen et al. 2021</v>
@@ -14963,7 +15004,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" hidden="1">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -15002,7 +15043,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" hidden="1">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -15041,7 +15082,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" hidden="1">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -15080,7 +15121,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" hidden="1">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -15119,7 +15160,7 @@
         <v>463.06098024892566</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" hidden="1">
       <c r="A83" t="s">
         <v>240</v>
       </c>
@@ -15158,7 +15199,7 @@
         <v>558.57147419213493</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" hidden="1">
       <c r="A84" t="s">
         <v>240</v>
       </c>
@@ -15197,7 +15238,7 @@
         <v>777.69611217374995</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" hidden="1">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -15236,7 +15277,7 @@
         <v>2052.1001665091567</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" hidden="1">
       <c r="A86" t="str">
         <f>'Study Parameters'!A19</f>
         <v>Datta et al. 2023</v>
@@ -15284,7 +15325,7 @@
       </c>
       <c r="M86" s="30"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" hidden="1">
       <c r="A87" t="str">
         <f>'Study Parameters'!A20</f>
         <v>Datta et al. 2023</v>
@@ -15332,7 +15373,7 @@
       </c>
       <c r="M87" s="30"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" hidden="1">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -15372,7 +15413,7 @@
       </c>
       <c r="M88" s="30"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" hidden="1">
       <c r="A89" t="s">
         <v>255</v>
       </c>
@@ -15412,7 +15453,7 @@
       </c>
       <c r="M89" s="30"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" hidden="1">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -15452,7 +15493,7 @@
       </c>
       <c r="M90" s="30"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" hidden="1">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -15492,7 +15533,7 @@
       </c>
       <c r="M91" s="30"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" hidden="1">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -15532,7 +15573,7 @@
       </c>
       <c r="M92" s="30"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" hidden="1">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -15572,7 +15613,7 @@
       </c>
       <c r="M93" s="30"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" hidden="1">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -15612,7 +15653,7 @@
       </c>
       <c r="M94" s="30"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" hidden="1">
       <c r="A95" t="s">
         <v>255</v>
       </c>
@@ -15652,7 +15693,7 @@
       </c>
       <c r="M95" s="30"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" hidden="1">
       <c r="A96" t="s">
         <v>255</v>
       </c>
@@ -15692,7 +15733,7 @@
       </c>
       <c r="M96" s="30"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" hidden="1">
       <c r="A97" t="str">
         <f>'Study Parameters'!A22</f>
         <v>Simon et al. 2011</v>
@@ -15736,7 +15777,7 @@
         <v>304.707654655694</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" hidden="1">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -15776,7 +15817,7 @@
         <v>803.14143939193252</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" hidden="1">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -15816,7 +15857,7 @@
         <v>329.15418006599049</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" hidden="1">
       <c r="A100" t="s">
         <v>267</v>
       </c>
@@ -15854,7 +15895,7 @@
         <v>779.02843503778104</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" hidden="1">
       <c r="A101" t="s">
         <v>267</v>
       </c>
@@ -15892,7 +15933,7 @@
         <v>831.75510668257198</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" hidden="1">
       <c r="A102" t="s">
         <v>267</v>
       </c>
@@ -15930,7 +15971,7 @@
         <v>317.24671499539198</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" hidden="1">
       <c r="A103" t="s">
         <v>267</v>
       </c>
@@ -15968,7 +16009,7 @@
         <v>371.938416568371</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" hidden="1">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -16006,7 +16047,7 @@
         <v>291.241690193887</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" hidden="1">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -16044,7 +16085,7 @@
         <v>355.05876736764702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" hidden="1">
       <c r="A106" t="s">
         <v>267</v>
       </c>
@@ -16082,7 +16123,7 @@
         <v>267.11083137986202</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" hidden="1">
       <c r="A107" t="str">
         <f>'Study Parameters'!A23</f>
         <v>Küng et al. 2023</v>
@@ -16126,7 +16167,7 @@
         <v>314.61251708631102</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" hidden="1">
       <c r="A108" t="s">
         <v>267</v>
       </c>
@@ -16164,7 +16205,7 @@
         <v>1817.71250053524</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" hidden="1">
       <c r="A109" t="s">
         <v>267</v>
       </c>
@@ -16202,7 +16243,7 @@
         <v>1990.0315112179401</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" hidden="1">
       <c r="A110" t="s">
         <v>267</v>
       </c>
@@ -16240,7 +16281,7 @@
         <v>980.75097520117902</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" hidden="1">
       <c r="A111" t="s">
         <v>267</v>
       </c>
@@ -16278,7 +16319,7 @@
         <v>1064.51188379418</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" hidden="1">
       <c r="A112" t="s">
         <v>267</v>
       </c>
@@ -16316,7 +16357,7 @@
         <v>411.65027432423102</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" hidden="1">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -16354,7 +16395,7 @@
         <v>488.64611354083598</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" hidden="1">
       <c r="A114" t="s">
         <v>267</v>
       </c>
@@ -16392,7 +16433,7 @@
         <v>378.55341271061599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" hidden="1">
       <c r="A115" t="s">
         <v>267</v>
       </c>
@@ -16430,7 +16471,7 @@
         <v>468.39609948070898</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" hidden="1">
       <c r="A116" t="s">
         <v>267</v>
       </c>
@@ -16468,7 +16509,7 @@
         <v>349.10367628750998</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" hidden="1">
       <c r="A117" t="s">
         <v>267</v>
       </c>
@@ -16506,7 +16547,7 @@
         <v>415.97729787873197</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" hidden="1">
       <c r="A118" t="s">
         <v>267</v>
       </c>
@@ -16544,7 +16585,7 @@
         <v>2476.9733161530498</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" hidden="1">
       <c r="A119" t="s">
         <v>267</v>
       </c>
@@ -16582,7 +16623,7 @@
         <v>2750.7170677000299</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" hidden="1">
       <c r="A120" t="str">
         <f>'Study Parameters'!A24</f>
         <v>Küng et al. 2023</v>
@@ -16625,7 +16666,7 @@
         <v>183.15040372394199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" hidden="1">
       <c r="A121" t="s">
         <v>267</v>
       </c>
@@ -16663,7 +16704,7 @@
         <v>227.07677281852301</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" hidden="1">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -16701,7 +16742,7 @@
         <v>61.893630816227301</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" hidden="1">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -16739,7 +16780,7 @@
         <v>72.225103599114604</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" hidden="1">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -16777,7 +16818,7 @@
         <v>393.65606020680502</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" hidden="1">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -16815,7 +16856,7 @@
         <v>503.939346853232</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" hidden="1">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -16853,7 +16894,7 @@
         <v>406.913082895564</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" hidden="1">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -16891,7 +16932,7 @@
         <v>517.19636954199098</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" hidden="1">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -16929,7 +16970,7 @@
         <v>243.248532930187</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" hidden="1">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -16967,7 +17008,7 @@
         <v>305.088767461244</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" hidden="1">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -17005,7 +17046,7 @@
         <v>76.028698179975393</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" hidden="1">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -17043,7 +17084,7 @@
         <v>90.573508350133693</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" hidden="1">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -17081,7 +17122,7 @@
         <v>523.47869237559496</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15" hidden="1">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -17119,7 +17160,7 @@
         <v>698.67329510641696</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:15" hidden="1">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -17157,7 +17198,7 @@
         <v>536.73571506435496</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" hidden="1">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -17195,14 +17236,13 @@
         <v>711.93031779517605</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" hidden="1">
       <c r="A136" t="str">
         <f>'Study Parameters'!A25</f>
         <v>Mostafa et al. 2022</v>
       </c>
       <c r="B136">
-        <f>'Study Parameters'!H25</f>
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="C136" t="str">
         <f>'Study Parameters'!E25</f>
@@ -17222,7 +17262,7 @@
       </c>
       <c r="L136" s="30"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15" hidden="1">
       <c r="A137" t="str">
         <f>'Study Parameters'!A26</f>
         <v>Keith et al. 2018</v>
@@ -17279,7 +17319,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:15" hidden="1">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -17327,7 +17367,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:15" hidden="1">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -17375,7 +17415,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -17412,18 +17452,18 @@
       </c>
       <c r="M140" s="30">
         <f>'[21]Step 1 LCOE - EE'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>129.36898390250661</v>
+        <v>130.30491652206067</v>
       </c>
       <c r="N140" s="30">
         <f>'[21]Step 2 WACC'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>138.26048414033502</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O140" s="30">
         <f>'[21]Step 3 T&amp;S'!$F$27*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>167.17362579080822</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+        <v>168.10955841036227</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" hidden="1">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -17474,7 +17514,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:15" hidden="1">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -17525,7 +17565,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15" hidden="1">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -17576,7 +17616,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -17613,18 +17653,18 @@
       </c>
       <c r="M144" s="30">
         <f>'[21]Step 1 LCOE - EE (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>170.5176415629532</v>
+        <v>171.45357418250728</v>
       </c>
       <c r="N144" s="30">
         <f>'[21]Step 2 WACC (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>138.26048414033502</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O144" s="30">
         <f>'[21]Step 3 T&amp;S (2)'!$F$27* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>167.17362579080822</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+        <v>168.10955841036227</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" hidden="1">
       <c r="A145" t="str">
         <f>'Study Parameters'!A27</f>
         <v>Gray et al. 2024</v>
@@ -17678,7 +17718,7 @@
         <v>1422.4526421724208</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" hidden="1">
       <c r="A146" t="str">
         <f>'Study Parameters'!A28</f>
         <v>Rosen et al. 2024</v>
@@ -17711,7 +17751,7 @@
       </c>
       <c r="L146" s="30"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" hidden="1">
       <c r="A147" t="str">
         <f>'Study Parameters'!A29</f>
         <v>Rosen et al. 2024</v>
@@ -17744,7 +17784,7 @@
       </c>
       <c r="L147" s="30"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" hidden="1">
       <c r="A148" t="str">
         <f>'Study Parameters'!A30</f>
         <v>Rosen et al. 2024</v>
@@ -17777,7 +17817,7 @@
       </c>
       <c r="L148" s="30"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" hidden="1">
       <c r="A149" t="str">
         <f>'Study Parameters'!A31</f>
         <v>Rosen et al. 2024</v>
@@ -17810,7 +17850,7 @@
       </c>
       <c r="L149" s="30"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" hidden="1">
       <c r="A150" t="str">
         <f>'Study Parameters'!A32</f>
         <v>Sabatino et al. 2020</v>
@@ -17837,7 +17877,7 @@
       </c>
       <c r="L150" s="30"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" hidden="1">
       <c r="A151" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17879,7 +17919,7 @@
         <v>52.859259278213045</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" hidden="1">
       <c r="A152" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17920,7 +17960,7 @@
         <v>174.22096158203897</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" hidden="1">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -17956,7 +17996,7 @@
         <v>45.162595126533958</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" hidden="1">
       <c r="A154" t="s">
         <v>294</v>
       </c>
@@ -17992,7 +18032,7 @@
         <v>155.30185025856494</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" hidden="1">
       <c r="A155" t="str">
         <f>'Study Parameters'!A34</f>
         <v>Lee et al. 2023</v>
@@ -18050,7 +18090,7 @@
         <v>270.09276004403995</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" hidden="1">
       <c r="A156" t="str">
         <f>'Study Parameters'!A35</f>
         <v>Abanades et al. 2023</v>
@@ -18077,7 +18117,7 @@
       </c>
       <c r="L156" s="30"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" hidden="1">
       <c r="A157" t="str">
         <f>'Study Parameters'!A36</f>
         <v>Abanades et al. 2020</v>
@@ -18104,7 +18144,7 @@
       </c>
       <c r="L157" s="30"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" hidden="1">
       <c r="A158" t="str">
         <f>'Study Parameters'!A37</f>
         <v>Ragipani et al. 2022</v>
@@ -18146,7 +18186,7 @@
         <v>121.14570202833102</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" hidden="1">
       <c r="A159" t="s">
         <v>315</v>
       </c>
@@ -18182,7 +18222,7 @@
         <v>140.09669470231475</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" hidden="1">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -18230,7 +18270,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:15" hidden="1">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -18278,7 +18318,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15" hidden="1">
       <c r="A162" t="s">
         <v>329</v>
       </c>
@@ -18326,7 +18366,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:15">
       <c r="A163" t="str">
         <f>'Study Parameters'!A39</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18367,18 +18407,18 @@
       </c>
       <c r="M163" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>128.52160188054003</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N163" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>116.90647783174505</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O163" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>141.90647783174506</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+        <v>147.49707212559986</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -18415,18 +18455,18 @@
       </c>
       <c r="M164" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>128.52160188054003</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N164" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>116.90647783174505</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O164" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>141.90647783174506</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+        <v>147.49707212559986</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -18463,18 +18503,18 @@
       </c>
       <c r="M165" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>128.52160188054003</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N165" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>116.90647783174505</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O165" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>141.90647783174506</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+        <v>147.49707212559986</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" hidden="1">
       <c r="A166" t="str">
         <f>'Study Parameters'!A40</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18527,7 +18567,7 @@
         <v>440.01216847304312</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:15" hidden="1">
       <c r="A167" t="s">
         <v>329</v>
       </c>
@@ -18575,7 +18615,7 @@
         <v>339.04143355290654</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15" hidden="1">
       <c r="A168" t="s">
         <v>329</v>
       </c>
@@ -18623,7 +18663,7 @@
         <v>263.41019772115243</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -18657,18 +18697,18 @@
       </c>
       <c r="M169" s="30">
         <f>'[27]Step 1 - LCOE + EE'!$G$23</f>
-        <v>138.51725671085572</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="N169" s="30">
         <f>'[27]Step 2 - WACC'!$G$23</f>
-        <v>138.51725671085572</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="O169" s="30">
         <f>'[27]Step 3 - T&amp;S'!$G$23</f>
-        <v>162.86808564420988</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+        <v>163.71895198084354</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" hidden="1">
       <c r="A170" t="str">
         <f>'Study Parameters'!A41</f>
         <v>NETL/Valentine 2022a</v>
@@ -18714,7 +18754,7 @@
       </c>
       <c r="M170" s="30"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" hidden="1">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -18754,7 +18794,7 @@
       </c>
       <c r="M171" s="30"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" hidden="1">
       <c r="A172" t="s">
         <v>336</v>
       </c>
@@ -18794,7 +18834,7 @@
       </c>
       <c r="M172" s="30"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" hidden="1">
       <c r="A173" t="str">
         <f>'Study Parameters'!A42</f>
         <v>NETL/Valentine 2022b</v>
@@ -18840,7 +18880,7 @@
       </c>
       <c r="M173" s="30"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" hidden="1">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -18880,7 +18920,7 @@
       </c>
       <c r="M174" s="30"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" hidden="1">
       <c r="A175" t="s">
         <v>342</v>
       </c>
@@ -18920,7 +18960,7 @@
       </c>
       <c r="M175" s="30"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" hidden="1">
       <c r="A176" t="str">
         <f>'Study Parameters'!A43</f>
         <v>NASEM 2019</v>
@@ -18947,7 +18987,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" hidden="1">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -18974,7 +19014,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" hidden="1">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19001,7 +19041,7 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" hidden="1">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
@@ -19047,7 +19087,7 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" hidden="1">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -19088,7 +19128,13 @@
       <c r="M180" s="30"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:W180" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}"/>
+  <autoFilter ref="A2:W180" xr:uid="{2D1B99AC-5C89-CE47-B699-CCA57CE6E758}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="2050"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="L1:N1"/>
@@ -19103,14 +19149,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C0257C-D407-4235-8443-42A5A3A9A73A}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" s="63" t="s">
         <v>751</v>
       </c>
@@ -19120,7 +19166,7 @@
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="64" t="s">
         <v>753</v>
       </c>
@@ -19130,7 +19176,7 @@
       <c r="J2" s="74"/>
       <c r="K2" s="74"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="64"/>
       <c r="F3" s="74" t="s">
         <v>755</v>
@@ -19138,7 +19184,7 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>756</v>
       </c>
@@ -19154,7 +19200,7 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>760</v>
       </c>
@@ -19170,7 +19216,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="74"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="B6" t="s">
         <v>764</v>
       </c>
@@ -19183,7 +19229,7 @@
       <c r="J6" s="74"/>
       <c r="K6" s="74"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="B7" t="s">
         <v>766</v>
       </c>
@@ -19193,7 +19239,7 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="B8" t="s">
         <v>767</v>
       </c>
@@ -19203,7 +19249,7 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="B9" t="s">
         <v>768</v>
       </c>
@@ -19213,7 +19259,7 @@
       <c r="J9" s="74"/>
       <c r="K9" s="74"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="B10" t="s">
         <v>769</v>
       </c>
@@ -19223,7 +19269,7 @@
       <c r="J10" s="74"/>
       <c r="K10" s="74"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="B11" t="s">
         <v>770</v>
       </c>
@@ -19233,7 +19279,7 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="B12" t="s">
         <v>771</v>
       </c>
@@ -19243,7 +19289,7 @@
       <c r="J12" s="76"/>
       <c r="K12" s="77"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="B13" t="s">
         <v>772</v>
       </c>
@@ -19253,7 +19299,7 @@
       <c r="J13" s="76"/>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="B14" t="s">
         <v>773</v>
       </c>
@@ -19263,7 +19309,7 @@
       <c r="J14" s="76"/>
       <c r="K14" s="77"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="B15" t="s">
         <v>774</v>
       </c>
@@ -19273,7 +19319,7 @@
       <c r="J15" s="76"/>
       <c r="K15" s="77"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="B16" t="s">
         <v>775</v>
       </c>
@@ -19283,7 +19329,7 @@
       <c r="J16" s="76"/>
       <c r="K16" s="77"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="B17" t="s">
         <v>776</v>
       </c>
@@ -19293,7 +19339,7 @@
       <c r="J17" s="76"/>
       <c r="K17" s="77"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="B18" t="s">
         <v>777</v>
       </c>
@@ -19303,7 +19349,7 @@
       <c r="J18" s="76"/>
       <c r="K18" s="77"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="B19" t="s">
         <v>778</v>
       </c>
@@ -19313,7 +19359,7 @@
       <c r="J19" s="76"/>
       <c r="K19" s="74"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="B20" t="s">
         <v>779</v>
       </c>
@@ -19323,7 +19369,7 @@
       <c r="J20" s="76"/>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="B21" t="s">
         <v>780</v>
       </c>
@@ -19333,7 +19379,7 @@
       <c r="J21" s="76"/>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="16.149999999999999" thickBot="1">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -19344,7 +19390,7 @@
       <c r="J22" s="76"/>
       <c r="K22" s="77"/>
     </row>
-    <row r="23" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1">
       <c r="A23" s="85" t="s">
         <v>80</v>
       </c>
@@ -19375,7 +19421,7 @@
       <c r="J23" s="76"/>
       <c r="K23" s="77"/>
     </row>
-    <row r="24" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="16.149999999999999" thickBot="1">
       <c r="A24" s="78" t="s">
         <v>782</v>
       </c>
@@ -19406,14 +19452,14 @@
       <c r="J24" s="76"/>
       <c r="K24" s="77"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="86" t="s">
         <v>784</v>
       </c>
       <c r="J25" s="76"/>
       <c r="K25" s="77"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>785</v>
       </c>
@@ -19427,7 +19473,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="77"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -19450,52 +19496,52 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56965C59-6106-408A-A712-D0B6552D4011}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="74" t="s">
         <v>752</v>
       </c>
       <c r="B1" s="74"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="74" t="s">
         <v>754</v>
       </c>
       <c r="B2" s="74"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="74" t="s">
         <v>755</v>
       </c>
       <c r="B3" s="74"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="74" t="s">
         <v>759</v>
       </c>
       <c r="B4" s="74"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="74" t="s">
         <v>763</v>
       </c>
       <c r="B5" s="74"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="74" t="s">
         <v>765</v>
       </c>
       <c r="B6" s="74"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="74" t="s">
         <v>788</v>
       </c>
@@ -19503,17 +19549,17 @@
         <v>789</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="74"/>
       <c r="B9" s="74"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="74" t="s">
         <v>790</v>
       </c>
       <c r="B10" s="74"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="74" t="s">
         <v>791</v>
       </c>
@@ -19521,7 +19567,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="76">
         <v>39448</v>
       </c>
@@ -19529,7 +19575,7 @@
         <v>1.4728000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="76">
         <v>39479</v>
       </c>
@@ -19537,7 +19583,7 @@
         <v>1.4759</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="76">
         <v>39508</v>
       </c>
@@ -19545,7 +19591,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="76">
         <v>39539</v>
       </c>
@@ -19553,7 +19599,7 @@
         <v>1.5753999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" s="76">
         <v>39569</v>
       </c>
@@ -19561,7 +19607,7 @@
         <v>1.5553999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="76">
         <v>39600</v>
       </c>
@@ -19569,7 +19615,7 @@
         <v>1.5562</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="76">
         <v>39630</v>
       </c>
@@ -19577,7 +19623,7 @@
         <v>1.5759000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="76">
         <v>39661</v>
       </c>
@@ -19585,7 +19631,7 @@
         <v>1.4955000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="76">
         <v>39692</v>
       </c>
@@ -19593,7 +19639,7 @@
         <v>1.4341999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="76">
         <v>39722</v>
       </c>
@@ -19601,7 +19647,7 @@
         <v>1.3266</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="76">
         <v>39753</v>
       </c>
@@ -19609,7 +19655,7 @@
         <v>1.2744</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="76">
         <v>39783</v>
       </c>
@@ -19617,7 +19663,7 @@
         <v>1.3511</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="76">
         <v>39814</v>
       </c>
@@ -19625,7 +19671,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="76">
         <v>39845</v>
       </c>
@@ -19633,7 +19679,7 @@
         <v>1.2797000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="76">
         <v>39873</v>
       </c>
@@ -19641,7 +19687,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="76">
         <v>39904</v>
       </c>
@@ -19649,7 +19695,7 @@
         <v>1.3199000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="76">
         <v>39934</v>
       </c>
@@ -19657,7 +19703,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="76">
         <v>39965</v>
       </c>
@@ -19665,7 +19711,7 @@
         <v>1.4014</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="76">
         <v>39995</v>
       </c>
@@ -19673,7 +19719,7 @@
         <v>1.4092</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="76">
         <v>40026</v>
       </c>
@@ -19681,7 +19727,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="76">
         <v>40057</v>
       </c>
@@ -19689,7 +19735,7 @@
         <v>1.4575</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="76">
         <v>40087</v>
       </c>
@@ -19697,7 +19743,7 @@
         <v>1.4821</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="76">
         <v>40118</v>
       </c>
@@ -19705,7 +19751,7 @@
         <v>1.4907999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="76">
         <v>40148</v>
       </c>
@@ -19713,7 +19759,7 @@
         <v>1.4579</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="76">
         <v>40179</v>
       </c>
@@ -19721,7 +19767,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="76">
         <v>40210</v>
       </c>
@@ -19729,7 +19775,7 @@
         <v>1.3680000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="76">
         <v>40238</v>
       </c>
@@ -19737,7 +19783,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="76">
         <v>40269</v>
       </c>
@@ -19745,7 +19791,7 @@
         <v>1.3416999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="76">
         <v>40299</v>
       </c>
@@ -19753,7 +19799,7 @@
         <v>1.2563</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="76">
         <v>40330</v>
       </c>
@@ -19761,7 +19807,7 @@
         <v>1.2222999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="76">
         <v>40360</v>
       </c>
@@ -19769,7 +19815,7 @@
         <v>1.2810999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="76">
         <v>40391</v>
       </c>
@@ -19777,7 +19823,7 @@
         <v>1.2903</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="76">
         <v>40422</v>
       </c>
@@ -19785,7 +19831,7 @@
         <v>1.3103</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" s="76">
         <v>40452</v>
       </c>
@@ -19793,7 +19839,7 @@
         <v>1.3900999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" s="76">
         <v>40483</v>
       </c>
@@ -19801,7 +19847,7 @@
         <v>1.3653999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2">
       <c r="A47" s="76">
         <v>40513</v>
       </c>
@@ -19809,7 +19855,7 @@
         <v>1.3221000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2">
       <c r="A48" s="76">
         <v>40544</v>
       </c>
@@ -19817,7 +19863,7 @@
         <v>1.3371</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2">
       <c r="A49" s="76">
         <v>40575</v>
       </c>
@@ -19825,7 +19871,7 @@
         <v>1.3655999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2">
       <c r="A50" s="76">
         <v>40603</v>
       </c>
@@ -19833,7 +19879,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2">
       <c r="A51" s="76">
         <v>40634</v>
       </c>
@@ -19841,7 +19887,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2">
       <c r="A52" s="76">
         <v>40664</v>
       </c>
@@ -19849,7 +19895,7 @@
         <v>1.4335</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2">
       <c r="A53" s="76">
         <v>40695</v>
       </c>
@@ -19857,7 +19903,7 @@
         <v>1.4402999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2">
       <c r="A54" s="76">
         <v>40725</v>
       </c>
@@ -19865,7 +19911,7 @@
         <v>1.4275</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2">
       <c r="A55" s="76">
         <v>40756</v>
       </c>
@@ -19873,7 +19919,7 @@
         <v>1.4333</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2">
       <c r="A56" s="76">
         <v>40787</v>
       </c>
@@ -19881,7 +19927,7 @@
         <v>1.3747</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2">
       <c r="A57" s="76">
         <v>40817</v>
       </c>
@@ -19889,7 +19935,7 @@
         <v>1.3732</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2">
       <c r="A58" s="76">
         <v>40848</v>
       </c>
@@ -19897,7 +19943,7 @@
         <v>1.3557999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2">
       <c r="A59" s="76">
         <v>40878</v>
       </c>
@@ -19905,7 +19951,7 @@
         <v>1.3154999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2">
       <c r="A60" s="76">
         <v>40909</v>
       </c>
@@ -19913,7 +19959,7 @@
         <v>1.2909999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2">
       <c r="A61" s="76">
         <v>40940</v>
       </c>
@@ -19921,7 +19967,7 @@
         <v>1.3238000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2">
       <c r="A62" s="76">
         <v>40969</v>
       </c>
@@ -19929,7 +19975,7 @@
         <v>1.3208</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2">
       <c r="A63" s="76">
         <v>41000</v>
       </c>
@@ -19937,7 +19983,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2">
       <c r="A64" s="76">
         <v>41030</v>
       </c>
@@ -19945,7 +19991,7 @@
         <v>1.2806</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2">
       <c r="A65" s="76">
         <v>41061</v>
       </c>
@@ -19953,7 +19999,7 @@
         <v>1.2541</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2">
       <c r="A66" s="76">
         <v>41091</v>
       </c>
@@ -19961,7 +20007,7 @@
         <v>1.2278</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2">
       <c r="A67" s="76">
         <v>41122</v>
       </c>
@@ -19969,7 +20015,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2">
       <c r="A68" s="76">
         <v>41153</v>
       </c>
@@ -19977,7 +20023,7 @@
         <v>1.2885</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2">
       <c r="A69" s="76">
         <v>41183</v>
       </c>
@@ -19985,7 +20031,7 @@
         <v>1.2974000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2">
       <c r="A70" s="76">
         <v>41214</v>
       </c>
@@ -19993,7 +20039,7 @@
         <v>1.2837000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2">
       <c r="A71" s="76">
         <v>41244</v>
       </c>
@@ -20001,7 +20047,7 @@
         <v>1.3119000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2">
       <c r="A72" s="76">
         <v>41275</v>
       </c>
@@ -20009,7 +20055,7 @@
         <v>1.3304</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2">
       <c r="A73" s="76">
         <v>41306</v>
       </c>
@@ -20017,7 +20063,7 @@
         <v>1.3347</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2">
       <c r="A74" s="76">
         <v>41334</v>
       </c>
@@ -20025,7 +20071,7 @@
         <v>1.2952999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2">
       <c r="A75" s="76">
         <v>41365</v>
       </c>
@@ -20033,7 +20079,7 @@
         <v>1.3025</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2">
       <c r="A76" s="76">
         <v>41395</v>
       </c>
@@ -20041,7 +20087,7 @@
         <v>1.2983</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2">
       <c r="A77" s="76">
         <v>41426</v>
       </c>
@@ -20049,7 +20095,7 @@
         <v>1.3197000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2">
       <c r="A78" s="76">
         <v>41456</v>
       </c>
@@ -20057,7 +20103,7 @@
         <v>1.3088</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2">
       <c r="A79" s="76">
         <v>41487</v>
       </c>
@@ -20065,7 +20111,7 @@
         <v>1.3313999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2">
       <c r="A80" s="76">
         <v>41518</v>
       </c>
@@ -20073,7 +20119,7 @@
         <v>1.3364</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2">
       <c r="A81" s="76">
         <v>41548</v>
       </c>
@@ -20081,7 +20127,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2">
       <c r="A82" s="76">
         <v>41579</v>
       </c>
@@ -20089,7 +20135,7 @@
         <v>1.3491</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2">
       <c r="A83" s="76">
         <v>41609</v>
       </c>
@@ -20097,7 +20143,7 @@
         <v>1.3708</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2">
       <c r="A84" s="76">
         <v>41640</v>
       </c>
@@ -20105,7 +20151,7 @@
         <v>1.3617999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2">
       <c r="A85" s="76">
         <v>41671</v>
       </c>
@@ -20113,7 +20159,7 @@
         <v>1.3665</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2">
       <c r="A86" s="76">
         <v>41699</v>
       </c>
@@ -20121,7 +20167,7 @@
         <v>1.3828</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2">
       <c r="A87" s="76">
         <v>41730</v>
       </c>
@@ -20129,7 +20175,7 @@
         <v>1.381</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2">
       <c r="A88" s="76">
         <v>41760</v>
       </c>
@@ -20137,7 +20183,7 @@
         <v>1.3738999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2">
       <c r="A89" s="76">
         <v>41791</v>
       </c>
@@ -20145,7 +20191,7 @@
         <v>1.3594999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2">
       <c r="A90" s="76">
         <v>41821</v>
       </c>
@@ -20153,7 +20199,7 @@
         <v>1.3532999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2">
       <c r="A91" s="76">
         <v>41852</v>
       </c>
@@ -20161,7 +20207,7 @@
         <v>1.3314999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2">
       <c r="A92" s="76">
         <v>41883</v>
       </c>
@@ -20169,7 +20215,7 @@
         <v>1.2888999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2">
       <c r="A93" s="76">
         <v>41913</v>
       </c>
@@ -20177,7 +20223,7 @@
         <v>1.2677</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2">
       <c r="A94" s="76">
         <v>41944</v>
       </c>
@@ -20185,7 +20231,7 @@
         <v>1.2473000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2">
       <c r="A95" s="76">
         <v>41974</v>
       </c>
@@ -20193,7 +20239,7 @@
         <v>1.2329000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2">
       <c r="A96" s="76">
         <v>42005</v>
       </c>
@@ -20201,7 +20247,7 @@
         <v>1.1615</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2">
       <c r="A97" s="76">
         <v>42036</v>
       </c>
@@ -20209,7 +20255,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2">
       <c r="A98" s="76">
         <v>42064</v>
       </c>
@@ -20217,7 +20263,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2">
       <c r="A99" s="76">
         <v>42095</v>
       </c>
@@ -20225,7 +20271,7 @@
         <v>1.0822000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2">
       <c r="A100" s="76">
         <v>42125</v>
       </c>
@@ -20233,7 +20279,7 @@
         <v>1.1167</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2">
       <c r="A101" s="76">
         <v>42156</v>
       </c>
@@ -20241,7 +20287,7 @@
         <v>1.1226</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2">
       <c r="A102" s="76">
         <v>42186</v>
       </c>
@@ -20249,7 +20295,7 @@
         <v>1.0996999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2">
       <c r="A103" s="76">
         <v>42217</v>
       </c>
@@ -20257,7 +20303,7 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2">
       <c r="A104" s="76">
         <v>42248</v>
       </c>
@@ -20265,7 +20311,7 @@
         <v>1.1229</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2">
       <c r="A105" s="76">
         <v>42278</v>
       </c>
@@ -20273,7 +20319,7 @@
         <v>1.1228</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2">
       <c r="A106" s="76">
         <v>42309</v>
       </c>
@@ -20281,7 +20327,7 @@
         <v>1.0727</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2">
       <c r="A107" s="76">
         <v>42339</v>
       </c>
@@ -20289,7 +20335,7 @@
         <v>1.0889</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2">
       <c r="A108" s="76">
         <v>42370</v>
       </c>
@@ -20297,7 +20343,7 @@
         <v>1.0854999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2">
       <c r="A109" s="76">
         <v>42401</v>
       </c>
@@ -20305,7 +20351,7 @@
         <v>1.1092</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2">
       <c r="A110" s="76">
         <v>42430</v>
       </c>
@@ -20313,7 +20359,7 @@
         <v>1.1133999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2">
       <c r="A111" s="76">
         <v>42461</v>
       </c>
@@ -20321,7 +20367,7 @@
         <v>1.1346000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2">
       <c r="A112" s="76">
         <v>42491</v>
       </c>
@@ -20329,7 +20375,7 @@
         <v>1.1312</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2">
       <c r="A113" s="76">
         <v>42522</v>
       </c>
@@ -20337,7 +20383,7 @@
         <v>1.1232</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2">
       <c r="A114" s="76">
         <v>42552</v>
       </c>
@@ -20345,7 +20391,7 @@
         <v>1.1054999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2">
       <c r="A115" s="76">
         <v>42583</v>
       </c>
@@ -20353,7 +20399,7 @@
         <v>1.1207</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2">
       <c r="A116" s="76">
         <v>42614</v>
       </c>
@@ -20361,7 +20407,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2">
       <c r="A117" s="76">
         <v>42644</v>
       </c>
@@ -20369,7 +20415,7 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2">
       <c r="A118" s="76">
         <v>42675</v>
       </c>
@@ -20377,7 +20423,7 @@
         <v>1.0791999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2">
       <c r="A119" s="76">
         <v>42705</v>
       </c>
@@ -20385,7 +20431,7 @@
         <v>1.0545</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2">
       <c r="A120" s="76">
         <v>42736</v>
       </c>
@@ -20393,7 +20439,7 @@
         <v>1.0634999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2">
       <c r="A121" s="76">
         <v>42767</v>
       </c>
@@ -20401,7 +20447,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2">
       <c r="A122" s="76">
         <v>42795</v>
       </c>
@@ -20409,7 +20455,7 @@
         <v>1.0690999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2">
       <c r="A123" s="76">
         <v>42826</v>
       </c>
@@ -20417,7 +20463,7 @@
         <v>1.0713999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2">
       <c r="A124" s="76">
         <v>42856</v>
       </c>
@@ -20425,7 +20471,7 @@
         <v>1.105</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2">
       <c r="A125" s="76">
         <v>42887</v>
       </c>
@@ -20433,7 +20479,7 @@
         <v>1.1233</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2">
       <c r="A126" s="76">
         <v>42917</v>
       </c>
@@ -20441,7 +20487,7 @@
         <v>1.153</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2">
       <c r="A127" s="76">
         <v>42948</v>
       </c>
@@ -20449,7 +20495,7 @@
         <v>1.1813</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2">
       <c r="A128" s="76">
         <v>42979</v>
       </c>
@@ -20457,7 +20503,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2">
       <c r="A129" s="76">
         <v>43009</v>
       </c>
@@ -20465,7 +20511,7 @@
         <v>1.1755</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2">
       <c r="A130" s="76">
         <v>43040</v>
       </c>
@@ -20473,7 +20519,7 @@
         <v>1.1742999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2">
       <c r="A131" s="76">
         <v>43070</v>
       </c>
@@ -20481,7 +20527,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2">
       <c r="A132" s="76">
         <v>43101</v>
       </c>
@@ -20489,7 +20535,7 @@
         <v>1.2197</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2">
       <c r="A133" s="76">
         <v>43132</v>
       </c>
@@ -20497,7 +20543,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2">
       <c r="A134" s="76">
         <v>43160</v>
       </c>
@@ -20505,7 +20551,7 @@
         <v>1.2334000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2">
       <c r="A135" s="76">
         <v>43191</v>
       </c>
@@ -20513,7 +20559,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2">
       <c r="A136" s="76">
         <v>43221</v>
       </c>
@@ -20521,7 +20567,7 @@
         <v>1.1822999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2">
       <c r="A137" s="76">
         <v>43252</v>
       </c>
@@ -20529,7 +20575,7 @@
         <v>1.1678999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2">
       <c r="A138" s="76">
         <v>43282</v>
       </c>
@@ -20537,7 +20583,7 @@
         <v>1.1685000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2">
       <c r="A139" s="76">
         <v>43313</v>
       </c>
@@ -20545,7 +20591,7 @@
         <v>1.1547000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2">
       <c r="A140" s="76">
         <v>43344</v>
       </c>
@@ -20553,7 +20599,7 @@
         <v>1.1667000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2">
       <c r="A141" s="76">
         <v>43374</v>
       </c>
@@ -20561,7 +20607,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2">
       <c r="A142" s="76">
         <v>43405</v>
       </c>
@@ -20569,7 +20615,7 @@
         <v>1.1364000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2">
       <c r="A143" s="76">
         <v>43435</v>
       </c>
@@ -20577,7 +20623,7 @@
         <v>1.1379999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2">
       <c r="A144" s="76">
         <v>43466</v>
       </c>
@@ -20585,7 +20631,7 @@
         <v>1.1417999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2">
       <c r="A145" s="76">
         <v>43497</v>
       </c>
@@ -20593,7 +20639,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2">
       <c r="A146" s="76">
         <v>43525</v>
       </c>
@@ -20601,7 +20647,7 @@
         <v>1.1295999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2">
       <c r="A147" s="76">
         <v>43556</v>
       </c>
@@ -20609,7 +20655,7 @@
         <v>1.1234</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2">
       <c r="A148" s="76">
         <v>43586</v>
       </c>
@@ -20617,7 +20663,7 @@
         <v>1.1187</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2">
       <c r="A149" s="76">
         <v>43617</v>
       </c>
@@ -20625,7 +20671,7 @@
         <v>1.1294999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2">
       <c r="A150" s="76">
         <v>43647</v>
       </c>
@@ -20633,7 +20679,7 @@
         <v>1.1211</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2">
       <c r="A151" s="76">
         <v>43678</v>
       </c>
@@ -20641,7 +20687,7 @@
         <v>1.1129</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2">
       <c r="A152" s="76">
         <v>43709</v>
       </c>
@@ -20649,7 +20695,7 @@
         <v>1.1011</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2">
       <c r="A153" s="76">
         <v>43739</v>
       </c>
@@ -20657,7 +20703,7 @@
         <v>1.1057999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2">
       <c r="A154" s="76">
         <v>43770</v>
       </c>
@@ -20665,7 +20711,7 @@
         <v>1.1051</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2">
       <c r="A155" s="76">
         <v>43800</v>
       </c>
@@ -20673,7 +20719,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2">
       <c r="A156" s="76">
         <v>43831</v>
       </c>
@@ -20681,7 +20727,7 @@
         <v>1.1097999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2">
       <c r="A157" s="76">
         <v>43862</v>
       </c>
@@ -20689,7 +20735,7 @@
         <v>1.0911</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2">
       <c r="A158" s="76">
         <v>43891</v>
       </c>
@@ -20697,7 +20743,7 @@
         <v>1.1046</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2">
       <c r="A159" s="76">
         <v>43922</v>
       </c>
@@ -20705,7 +20751,7 @@
         <v>1.0871</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2">
       <c r="A160" s="76">
         <v>43952</v>
       </c>
@@ -20713,7 +20759,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2">
       <c r="A161" s="76">
         <v>43983</v>
       </c>
@@ -20721,7 +20767,7 @@
         <v>1.1258999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2">
       <c r="A162" s="76">
         <v>44013</v>
       </c>
@@ -20729,7 +20775,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2">
       <c r="A163" s="76">
         <v>44044</v>
       </c>
@@ -20737,7 +20783,7 @@
         <v>1.1831</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2">
       <c r="A164" s="76">
         <v>44075</v>
       </c>
@@ -20745,7 +20791,7 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2">
       <c r="A165" s="76">
         <v>44105</v>
       </c>
@@ -20753,7 +20799,7 @@
         <v>1.1768000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2">
       <c r="A166" s="76">
         <v>44136</v>
       </c>
@@ -20761,7 +20807,7 @@
         <v>1.1826000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2">
       <c r="A167" s="76">
         <v>44166</v>
       </c>
@@ -20769,7 +20815,7 @@
         <v>1.2168000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2">
       <c r="A168" s="76">
         <v>44197</v>
       </c>
@@ -20777,7 +20823,7 @@
         <v>1.2178</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2">
       <c r="A169" s="76">
         <v>44228</v>
       </c>
@@ -20785,7 +20831,7 @@
         <v>1.2094</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2">
       <c r="A170" s="76">
         <v>44256</v>
       </c>
@@ -20793,7 +20839,7 @@
         <v>1.1901999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2">
       <c r="A171" s="76">
         <v>44287</v>
       </c>
@@ -20801,7 +20847,7 @@
         <v>1.1964999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2">
       <c r="A172" s="76">
         <v>44317</v>
       </c>
@@ -20809,7 +20855,7 @@
         <v>1.2145999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2">
       <c r="A173" s="76">
         <v>44348</v>
       </c>
@@ -20817,7 +20863,7 @@
         <v>1.2048000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2">
       <c r="A174" s="76">
         <v>44378</v>
       </c>
@@ -20825,7 +20871,7 @@
         <v>1.1820999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2">
       <c r="A175" s="76">
         <v>44409</v>
       </c>
@@ -20833,7 +20879,7 @@
         <v>1.1767000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2">
       <c r="A176" s="76">
         <v>44440</v>
       </c>
@@ -20841,7 +20887,7 @@
         <v>1.1765000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2">
       <c r="A177" s="76">
         <v>44470</v>
       </c>
@@ -20849,7 +20895,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2">
       <c r="A178" s="76">
         <v>44501</v>
       </c>
@@ -20857,7 +20903,7 @@
         <v>1.1415999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2">
       <c r="A179" s="76">
         <v>44531</v>
       </c>
@@ -20865,7 +20911,7 @@
         <v>1.1301000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2">
       <c r="A180" s="76">
         <v>44562</v>
       </c>
@@ -20873,7 +20919,7 @@
         <v>1.1316999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2">
       <c r="A181" s="76">
         <v>44593</v>
       </c>
@@ -20881,7 +20927,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2">
       <c r="A182" s="76">
         <v>44621</v>
       </c>
@@ -20889,7 +20935,7 @@
         <v>1.1019000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2">
       <c r="A183" s="76">
         <v>44652</v>
       </c>
@@ -20897,7 +20943,7 @@
         <v>1.0803</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2">
       <c r="A184" s="76">
         <v>44682</v>
       </c>
@@ -20905,7 +20951,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2">
       <c r="A185" s="76">
         <v>44713</v>
       </c>
@@ -20913,7 +20959,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2">
       <c r="A186" s="76">
         <v>44743</v>
       </c>
@@ -20921,7 +20967,7 @@
         <v>1.0167999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2">
       <c r="A187" s="76">
         <v>44774</v>
       </c>
@@ -20929,7 +20975,7 @@
         <v>1.0128999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2">
       <c r="A188" s="76">
         <v>44805</v>
       </c>
@@ -20937,7 +20983,7 @@
         <v>0.9899</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2">
       <c r="A189" s="76">
         <v>44835</v>
       </c>
@@ -20945,7 +20991,7 @@
         <v>0.98529999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2">
       <c r="A190" s="76">
         <v>44866</v>
       </c>
@@ -20953,7 +20999,7 @@
         <v>1.0192000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2">
       <c r="A191" s="76">
         <v>44896</v>
       </c>
@@ -20961,7 +21007,7 @@
         <v>1.0590999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2">
       <c r="A192" s="76">
         <v>44927</v>
       </c>
@@ -20969,7 +21015,7 @@
         <v>1.0777000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2">
       <c r="A193" s="76">
         <v>44958</v>
       </c>
@@ -20977,7 +21023,7 @@
         <v>1.0702</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2">
       <c r="A194" s="76">
         <v>44986</v>
       </c>
@@ -20985,7 +21031,7 @@
         <v>1.0710999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2">
       <c r="A195" s="76">
         <v>45017</v>
       </c>
@@ -20993,7 +21039,7 @@
         <v>1.0962000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2">
       <c r="A196" s="76">
         <v>45047</v>
       </c>
@@ -21001,7 +21047,7 @@
         <v>1.0867</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2">
       <c r="A197" s="76">
         <v>45078</v>
       </c>
@@ -21009,7 +21055,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2">
       <c r="A198" s="76">
         <v>45108</v>
       </c>
@@ -21017,7 +21063,7 @@
         <v>1.1067</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2">
       <c r="A199" s="76">
         <v>45139</v>
       </c>
@@ -21025,7 +21071,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2">
       <c r="A200" s="76">
         <v>45170</v>
       </c>
@@ -21033,7 +21079,7 @@
         <v>1.0671999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2">
       <c r="A201" s="76">
         <v>45200</v>
       </c>
@@ -21041,7 +21087,7 @@
         <v>1.0565</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2">
       <c r="A202" s="76">
         <v>45231</v>
       </c>
@@ -21049,7 +21095,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2">
       <c r="A203" s="76">
         <v>45261</v>
       </c>
@@ -21057,7 +21103,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2">
       <c r="A204" s="76">
         <v>45292</v>
       </c>
@@ -21065,7 +21111,7 @@
         <v>1.0899000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2">
       <c r="A205" s="76">
         <v>45323</v>
       </c>
@@ -21073,7 +21119,7 @@
         <v>1.0792999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2">
       <c r="A206" s="76">
         <v>45352</v>
       </c>
@@ -21081,7 +21127,7 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2">
       <c r="A207" s="76">
         <v>45383</v>
       </c>
@@ -21089,7 +21135,7 @@
         <v>1.0724</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2">
       <c r="A208" s="76">
         <v>45413</v>
       </c>
@@ -21097,7 +21143,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2">
       <c r="A209" s="76">
         <v>45444</v>
       </c>
@@ -21105,7 +21151,7 @@
         <v>1.0763</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2">
       <c r="A210" s="76">
         <v>45474</v>
       </c>
@@ -21113,7 +21159,7 @@
         <v>1.0847</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2">
       <c r="A211" s="76">
         <v>45505</v>
       </c>
@@ -21130,7 +21176,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21142,15 +21188,15 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -21164,7 +21210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -21178,12 +21224,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" s="8" customFormat="1">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -21191,7 +21237,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -21200,7 +21246,7 @@
         <v>2.453282945060923E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -21208,7 +21254,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -21217,12 +21263,12 @@
         <v>0.81870109796004231</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" s="8" customFormat="1">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="57" t="s">
         <v>15</v>
       </c>
@@ -21240,16 +21286,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="57" t="s">
         <v>15</v>
       </c>
       <c r="B10">
         <v>2050</v>
       </c>
-      <c r="C10" cm="1">
-        <f t="array" ref="C10">_xlfn.IFS($D$1 = "Low Electricity and CO2", 'Energy_Carbon intensity'!AF30, $D$1 = "Reference",'Standard Input Calculations'!AE13, $D$1="High Electricity and CO2",'Energy_Carbon intensity'!AF34)</f>
-        <v>29</v>
+      <c r="C10">
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -21258,7 +21303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="105" t="s">
         <v>19</v>
       </c>
@@ -21275,7 +21320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="105" t="s">
         <v>19</v>
       </c>
@@ -21292,7 +21337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="105" t="s">
         <v>19</v>
       </c>
@@ -21308,7 +21353,7 @@
       </c>
       <c r="E13" s="94"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="105" t="s">
         <v>19</v>
       </c>
@@ -21324,7 +21369,7 @@
       </c>
       <c r="E14" s="94"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="105" t="s">
         <v>22</v>
       </c>
@@ -21341,7 +21386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="105" t="s">
         <v>22</v>
       </c>
@@ -21358,7 +21403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="105" t="s">
         <v>22</v>
       </c>
@@ -21374,7 +21419,7 @@
       </c>
       <c r="E17" s="94"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="105" t="s">
         <v>22</v>
       </c>
@@ -21390,7 +21435,7 @@
       </c>
       <c r="E18" s="94"/>
     </row>
-    <row r="19" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.45">
       <c r="A19" s="94" t="s">
         <v>23</v>
       </c>
@@ -21404,7 +21449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.45">
       <c r="A20" s="94" t="s">
         <v>25</v>
       </c>
@@ -21418,7 +21463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.45">
       <c r="A21" s="94" t="s">
         <v>26</v>
       </c>
@@ -21433,12 +21478,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" s="8" customFormat="1">
       <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -21455,7 +21500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -21472,12 +21517,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" s="8" customFormat="1">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -21494,7 +21539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" s="57" t="s">
         <v>32</v>
       </c>
@@ -21511,7 +21556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="108" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.45">
       <c r="A29" s="108" t="s">
         <v>33</v>
       </c>
@@ -21539,17 +21584,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="35" max="35" width="8.6640625" style="47"/>
-    <col min="36" max="36" width="17.1640625" style="41" customWidth="1"/>
-    <col min="37" max="37" width="13.6640625" customWidth="1"/>
+    <col min="35" max="35" width="8.625" style="47"/>
+    <col min="36" max="36" width="17.125" style="41" customWidth="1"/>
+    <col min="37" max="37" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38">
       <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
@@ -21665,7 +21710,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38">
       <c r="A2" s="34" t="s">
         <v>43</v>
       </c>
@@ -21782,7 +21827,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38">
       <c r="A3" s="40" t="s">
         <v>51</v>
       </c>
@@ -21889,7 +21934,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38">
       <c r="A4" s="40" t="s">
         <v>53</v>
       </c>
@@ -21996,7 +22041,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38">
       <c r="A5" s="40" t="s">
         <v>55</v>
       </c>
@@ -22103,7 +22148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38">
       <c r="A6" s="40" t="s">
         <v>56</v>
       </c>
@@ -22210,7 +22255,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38">
       <c r="A7" s="40" t="s">
         <v>57</v>
       </c>
@@ -22317,7 +22362,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38">
       <c r="A8" s="40" t="s">
         <v>58</v>
       </c>
@@ -22424,7 +22469,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38">
       <c r="A9" s="40" t="s">
         <v>59</v>
       </c>
@@ -22531,7 +22576,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38">
       <c r="A10" s="40" t="s">
         <v>60</v>
       </c>
@@ -22638,7 +22683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38">
       <c r="A11" s="40" t="s">
         <v>61</v>
       </c>
@@ -22745,7 +22790,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38">
       <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
@@ -22852,7 +22897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38">
       <c r="A13" s="40" t="s">
         <v>63</v>
       </c>
@@ -22959,7 +23004,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38">
       <c r="A14" s="34" t="s">
         <v>43</v>
       </c>
@@ -23076,7 +23121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38">
       <c r="A15" s="40" t="s">
         <v>64</v>
       </c>
@@ -23183,7 +23228,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38">
       <c r="A16" s="40" t="s">
         <v>65</v>
       </c>
@@ -23290,7 +23335,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38">
       <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
@@ -23397,7 +23442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38">
       <c r="A18" s="40" t="s">
         <v>67</v>
       </c>
@@ -23504,7 +23549,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38">
       <c r="A19" s="40" t="s">
         <v>68</v>
       </c>
@@ -23621,7 +23666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38">
       <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
@@ -23728,7 +23773,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38">
       <c r="A21" s="40" t="s">
         <v>53</v>
       </c>
@@ -23835,7 +23880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38">
       <c r="A22" s="40" t="s">
         <v>55</v>
       </c>
@@ -23942,7 +23987,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38">
       <c r="A23" s="40" t="s">
         <v>56</v>
       </c>
@@ -24049,7 +24094,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38">
       <c r="A24" s="40" t="s">
         <v>57</v>
       </c>
@@ -24156,7 +24201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38">
       <c r="A25" s="40" t="s">
         <v>58</v>
       </c>
@@ -24263,7 +24308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:38">
       <c r="A26" s="40" t="s">
         <v>59</v>
       </c>
@@ -24370,7 +24415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38">
       <c r="A27" s="40" t="s">
         <v>60</v>
       </c>
@@ -24477,7 +24522,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38">
       <c r="A28" s="40" t="s">
         <v>61</v>
       </c>
@@ -24584,7 +24629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38">
       <c r="A29" s="40" t="s">
         <v>62</v>
       </c>
@@ -24691,7 +24736,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38">
       <c r="A30" s="40" t="s">
         <v>63</v>
       </c>
@@ -24798,7 +24843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" s="2" customFormat="1">
       <c r="A31" s="34" t="s">
         <v>43</v>
       </c>
@@ -24915,7 +24960,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:38">
       <c r="A32" s="40" t="s">
         <v>64</v>
       </c>
@@ -25022,7 +25067,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:40">
       <c r="A33" s="40" t="s">
         <v>65</v>
       </c>
@@ -25129,7 +25174,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:40">
       <c r="A34" s="40" t="s">
         <v>66</v>
       </c>
@@ -25236,7 +25281,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:40">
       <c r="A35" s="40" t="s">
         <v>67</v>
       </c>
@@ -25343,7 +25388,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:40">
       <c r="A36" s="40" t="s">
         <v>68</v>
       </c>
@@ -25460,7 +25505,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:40">
       <c r="A37" s="40" t="s">
         <v>72</v>
       </c>
@@ -25487,7 +25532,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:40">
       <c r="A38" s="40" t="s">
         <v>72</v>
       </c>
@@ -25511,7 +25556,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:40">
       <c r="A39" s="40" t="s">
         <v>75</v>
       </c>
@@ -25544,7 +25589,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:40">
       <c r="A40" s="40" t="s">
         <v>75</v>
       </c>
@@ -25565,14 +25610,14 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:40">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="AI42"/>
       <c r="AJ42"/>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:40">
       <c r="A43" s="97"/>
       <c r="B43" s="98" t="s">
         <v>80</v>
@@ -25598,7 +25643,7 @@
       <c r="AI43"/>
       <c r="AJ43"/>
     </row>
-    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:40" s="1" customFormat="1">
       <c r="A44" s="99" t="s">
         <v>87</v>
       </c>
@@ -25627,7 +25672,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:40">
       <c r="A45" s="97"/>
       <c r="B45" s="100" t="s">
         <v>88</v>
@@ -25656,7 +25701,7 @@
       <c r="AI45"/>
       <c r="AJ45"/>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:40">
       <c r="A46" s="97"/>
       <c r="B46" s="100" t="s">
         <v>88</v>
@@ -25685,7 +25730,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:40" s="1" customFormat="1">
       <c r="A47" s="99" t="s">
         <v>94</v>
       </c>
@@ -25716,44 +25761,44 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:40">
       <c r="A48" t="s">
         <v>98</v>
       </c>
       <c r="AI48"/>
       <c r="AJ48"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36">
       <c r="A49" t="s">
         <v>99</v>
       </c>
       <c r="AI49"/>
       <c r="AJ49"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36">
       <c r="A50" t="s">
         <v>100</v>
       </c>
       <c r="AI50"/>
       <c r="AJ50"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36">
       <c r="AI51"/>
       <c r="AJ51"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36">
       <c r="AI52"/>
       <c r="AJ52"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36">
       <c r="AI53"/>
       <c r="AJ53"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36">
       <c r="AI54"/>
       <c r="AJ54"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36">
       <c r="AI55"/>
       <c r="AJ55"/>
     </row>
@@ -25775,17 +25820,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="10"/>
-    <col min="2" max="2" width="69.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="10"/>
+    <col min="2" max="2" width="69.625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="10.6640625" style="10"/>
+    <col min="6" max="16384" width="10.625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -25831,7 +25876,7 @@
       <c r="AQ1" s="9"/>
       <c r="AR1" s="9"/>
     </row>
-    <row r="2" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="20.45" thickBot="1">
       <c r="A2" s="9"/>
       <c r="B2" s="11" t="s">
         <v>101</v>
@@ -25879,7 +25924,7 @@
       <c r="AQ2" s="9"/>
       <c r="AR2" s="9"/>
     </row>
-    <row r="3" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="16.149999999999999" thickTop="1">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -25925,7 +25970,7 @@
       <c r="AQ3" s="9"/>
       <c r="AR3" s="9"/>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>102</v>
@@ -25975,7 +26020,7 @@
       <c r="AQ4" s="9"/>
       <c r="AR4" s="9"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
@@ -26083,7 +26128,7 @@
       <c r="AQ5" s="15"/>
       <c r="AR5" s="15"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>105</v>
@@ -26189,7 +26234,7 @@
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>106</v>
@@ -26295,7 +26340,7 @@
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="25"/>
@@ -26341,7 +26386,7 @@
       <c r="AQ8" s="25"/>
       <c r="AR8" s="25"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
         <v>107</v>
@@ -26389,7 +26434,7 @@
       <c r="AQ9" s="25"/>
       <c r="AR9" s="25"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
         <v>108</v>
@@ -26437,7 +26482,7 @@
       <c r="AQ10" s="25"/>
       <c r="AR10" s="25"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44">
       <c r="A11" s="12"/>
       <c r="B11" s="12" t="s">
         <v>109</v>
@@ -26543,7 +26588,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
         <v>110</v>
@@ -26591,7 +26636,7 @@
       <c r="AQ12" s="25"/>
       <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
         <v>109</v>
@@ -26697,7 +26742,7 @@
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
         <v>111</v>
@@ -26745,7 +26790,7 @@
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
         <v>109</v>
@@ -26851,7 +26896,7 @@
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="25"/>
@@ -26897,7 +26942,7 @@
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -26943,7 +26988,7 @@
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
     </row>
-    <row r="18" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" ht="20.45" thickBot="1">
       <c r="A18" s="9"/>
       <c r="B18" s="11" t="s">
         <v>112</v>
@@ -26991,7 +27036,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
     </row>
-    <row r="19" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="16.149999999999999" thickTop="1">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -27037,7 +27082,7 @@
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:44">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -27084,7 +27129,7 @@
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:44">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>112</v>
@@ -27135,7 +27180,7 @@
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:44">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -27181,7 +27226,7 @@
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:44">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -27227,7 +27272,7 @@
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44">
       <c r="A24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -27269,7 +27314,7 @@
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -27315,7 +27360,7 @@
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -27361,7 +27406,7 @@
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -27415,20 +27460,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="144" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -27436,7 +27481,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>406</v>
       </c>
@@ -27444,7 +27489,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>358</v>
       </c>
@@ -27452,7 +27497,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -27464,13 +27509,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="144" t="s">
         <v>119</v>
       </c>
       <c r="B9" s="144"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -27478,7 +27523,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -27492,7 +27537,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -27503,13 +27548,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="144" t="s">
         <v>122</v>
       </c>
       <c r="B14" s="144"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -27517,7 +27562,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -27528,7 +27573,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -27556,13 +27601,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -27581,31 +27626,31 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA419E9D-493B-4DCE-A933-2A9A9AF40246}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" outlineLevelCol="2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.1640625" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.83203125" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.125" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
     <col min="4" max="4" width="7" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="5" max="5" width="11.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="6" max="6" width="16.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="7" max="8" width="8.83203125" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="9" max="9" width="10.6640625" hidden="1" customWidth="1" outlineLevel="2"/>
-    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="5" max="5" width="11.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="6" max="6" width="16.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="7" max="8" width="8.875" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="9" max="9" width="10.625" hidden="1" customWidth="1" outlineLevel="2"/>
+    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="13" width="8" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="20.6640625" customWidth="1"/>
+    <col min="14" max="15" width="16.625" customWidth="1"/>
+    <col min="16" max="16" width="20.625" customWidth="1"/>
     <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="37.6640625" customWidth="1"/>
-    <col min="20" max="20" width="34.1640625" customWidth="1"/>
-    <col min="21" max="21" width="33.83203125" customWidth="1"/>
-    <col min="22" max="22" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.75" customWidth="1"/>
+    <col min="20" max="20" width="34.25" customWidth="1"/>
+    <col min="21" max="21" width="33.875" customWidth="1"/>
+    <col min="22" max="22" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="30" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -27689,7 +27734,7 @@
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -27745,7 +27790,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -27801,7 +27846,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -27855,7 +27900,7 @@
       </c>
       <c r="W4" s="60"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -27909,7 +27954,7 @@
       </c>
       <c r="W5" s="60"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -27963,7 +28008,7 @@
       </c>
       <c r="W6" s="60"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -28017,7 +28062,7 @@
       </c>
       <c r="W7" s="60"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -28071,7 +28116,7 @@
       </c>
       <c r="W8" s="60"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -28125,7 +28170,7 @@
       </c>
       <c r="W9" s="60"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -28179,7 +28224,7 @@
       </c>
       <c r="W10" s="60"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -28233,7 +28278,7 @@
       </c>
       <c r="W11" s="60"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -28287,7 +28332,7 @@
       </c>
       <c r="W12" s="60"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -28341,7 +28386,7 @@
       </c>
       <c r="W13" s="60"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -28395,7 +28440,7 @@
       </c>
       <c r="W14" s="60"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -28449,7 +28494,7 @@
       </c>
       <c r="W15" s="60"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -28506,7 +28551,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -28563,7 +28608,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -28605,7 +28650,7 @@
       </c>
       <c r="W18" s="60"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -28647,7 +28692,7 @@
       </c>
       <c r="W19" s="60"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -28683,7 +28728,7 @@
       </c>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -28719,7 +28764,7 @@
       </c>
       <c r="W21" s="60"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -28755,7 +28800,7 @@
       </c>
       <c r="W22" s="60"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -28791,7 +28836,7 @@
       </c>
       <c r="W23" s="60"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -28833,7 +28878,7 @@
       </c>
       <c r="W24" s="60"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -28884,7 +28929,7 @@
       </c>
       <c r="W25" s="60"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -28920,7 +28965,7 @@
       </c>
       <c r="W26" s="60"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -28956,7 +29001,7 @@
       </c>
       <c r="W27" s="60"/>
     </row>
-    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" s="48" customFormat="1">
       <c r="A28" s="48" t="s">
         <v>150</v>
       </c>
@@ -28986,7 +29031,7 @@
       </c>
       <c r="W28" s="90"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -29022,7 +29067,7 @@
       </c>
       <c r="W29" s="60"/>
     </row>
-    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" s="48" customFormat="1">
       <c r="A30" s="48" t="s">
         <v>260</v>
       </c>
@@ -29055,7 +29100,7 @@
       </c>
       <c r="W30" s="90"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -29091,7 +29136,7 @@
       </c>
       <c r="W31" s="60"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -29127,7 +29172,7 @@
       </c>
       <c r="W32" s="60"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -29163,7 +29208,7 @@
       </c>
       <c r="W33" s="60"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -29199,7 +29244,7 @@
       </c>
       <c r="W34" s="60"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -29250,7 +29295,7 @@
       </c>
       <c r="W35" s="60"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -29286,7 +29331,7 @@
       </c>
       <c r="W36" s="60"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -29322,7 +29367,7 @@
       </c>
       <c r="W37" s="60"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -29358,7 +29403,7 @@
       </c>
       <c r="W38" s="60"/>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -29394,7 +29439,7 @@
       </c>
       <c r="W39" s="60"/>
     </row>
-    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" s="48" customFormat="1">
       <c r="A40" s="48" t="s">
         <v>150</v>
       </c>
@@ -29421,7 +29466,7 @@
       </c>
       <c r="W40" s="90"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -29460,7 +29505,7 @@
       </c>
       <c r="W41" s="60"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -29502,7 +29547,7 @@
       </c>
       <c r="W42" s="60"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -29535,7 +29580,7 @@
       </c>
       <c r="W43" s="60"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23">
       <c r="A44" t="s">
         <v>150</v>
       </c>
@@ -29568,7 +29613,7 @@
       </c>
       <c r="W44" s="60"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -29601,7 +29646,7 @@
       </c>
       <c r="W45" s="60"/>
     </row>
-    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" s="48" customFormat="1">
       <c r="A46" s="48" t="s">
         <v>150</v>
       </c>
@@ -29628,7 +29673,7 @@
       </c>
       <c r="W46" s="90"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -29662,7 +29707,7 @@
       </c>
       <c r="W47" s="60"/>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23">
       <c r="A48" t="s">
         <v>260</v>
       </c>
@@ -29696,7 +29741,7 @@
       </c>
       <c r="W48" s="60"/>
     </row>
-    <row r="49" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -29744,7 +29789,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -29792,7 +29837,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -29840,7 +29885,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -29888,7 +29933,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -29930,7 +29975,7 @@
       </c>
       <c r="W53" s="60"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -29966,7 +30011,7 @@
       </c>
       <c r="W54" s="60"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -30002,7 +30047,7 @@
       </c>
       <c r="W55" s="60"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26">
       <c r="A56" t="s">
         <v>150</v>
       </c>
@@ -30038,7 +30083,7 @@
       </c>
       <c r="W56" s="60"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26">
       <c r="A57" t="s">
         <v>150</v>
       </c>
@@ -30095,34 +30140,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99968075-C79E-496E-8470-A0201C505FA7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="23.1640625" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.6640625" customWidth="1"/>
+    <col min="11" max="11" width="30.875" customWidth="1"/>
+    <col min="12" max="12" width="26.75" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="18.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" customWidth="1"/>
-    <col min="19" max="22" width="20.1640625" customWidth="1"/>
+    <col min="18" max="18" width="18.125" customWidth="1"/>
+    <col min="19" max="22" width="20.125" customWidth="1"/>
     <col min="24" max="25" width="17.5" customWidth="1"/>
-    <col min="26" max="28" width="15.1640625" customWidth="1"/>
+    <col min="26" max="28" width="15.125" customWidth="1"/>
     <col min="29" max="29" width="22.5" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="22.5" customWidth="1"/>
-    <col min="32" max="32" width="37.6640625" customWidth="1"/>
+    <col min="32" max="32" width="37.625" customWidth="1"/>
     <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19" customWidth="1"/>
-    <col min="36" max="36" width="33.6640625" customWidth="1"/>
+    <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" s="51" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -30182,7 +30227,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" s="117" customFormat="1">
       <c r="A2" s="117" t="s">
         <v>151</v>
       </c>
@@ -30213,7 +30258,7 @@
       <c r="R2" s="118"/>
       <c r="AI2" s="119"/>
     </row>
-    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" s="117" customFormat="1">
       <c r="A3" s="117" t="s">
         <v>151</v>
       </c>
@@ -30245,7 +30290,7 @@
       <c r="R3" s="118"/>
       <c r="AI3" s="119"/>
     </row>
-    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" s="117" customFormat="1">
       <c r="A4" s="117" t="s">
         <v>151</v>
       </c>
@@ -30277,7 +30322,7 @@
       <c r="R4" s="118"/>
       <c r="AI4" s="119"/>
     </row>
-    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" s="117" customFormat="1">
       <c r="A5" s="117" t="s">
         <v>151</v>
       </c>
@@ -30310,7 +30355,7 @@
       <c r="AD5" s="120"/>
       <c r="AI5" s="119"/>
     </row>
-    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" s="117" customFormat="1">
       <c r="A6" s="117" t="s">
         <v>185</v>
       </c>
@@ -30341,7 +30386,7 @@
       </c>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" s="117" customFormat="1">
       <c r="A7" s="117" t="s">
         <v>185</v>
       </c>
@@ -30373,7 +30418,7 @@
       <c r="O7" s="122"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" s="117" customFormat="1">
       <c r="A8" s="117" t="s">
         <v>185</v>
       </c>
@@ -30405,7 +30450,7 @@
       <c r="R8" s="121"/>
       <c r="AD8" s="120"/>
     </row>
-    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -30440,7 +30485,7 @@
       <c r="W9" s="114"/>
       <c r="AF9" s="115"/>
     </row>
-    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -30477,7 +30522,7 @@
       <c r="R10" s="113"/>
       <c r="AI10" s="116"/>
     </row>
-    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" s="117" customFormat="1">
       <c r="A11" s="117" t="s">
         <v>214</v>
       </c>
@@ -30508,7 +30553,7 @@
       <c r="R11" s="121"/>
       <c r="AI11" s="119"/>
     </row>
-    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" s="117" customFormat="1">
       <c r="A12" s="117" t="s">
         <v>214</v>
       </c>
@@ -30539,7 +30584,7 @@
       <c r="R12" s="121"/>
       <c r="AI12" s="119"/>
     </row>
-    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A13" s="2" t="s">
         <v>223</v>
       </c>
@@ -30574,7 +30619,7 @@
       <c r="AA13" s="124"/>
       <c r="AB13" s="124"/>
     </row>
-    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A14" s="2" t="s">
         <v>227</v>
       </c>
@@ -30611,7 +30656,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
@@ -30643,7 +30688,7 @@
       <c r="AI15" s="116"/>
       <c r="AL15" s="127"/>
     </row>
-    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1">
       <c r="A16" s="2" t="s">
         <v>230</v>
       </c>
@@ -30675,7 +30720,7 @@
       <c r="AI16" s="116"/>
       <c r="AL16" s="127"/>
     </row>
-    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A17" s="2" t="s">
         <v>234</v>
       </c>
@@ -30706,7 +30751,7 @@
       <c r="R17" s="123"/>
       <c r="AI17" s="116"/>
     </row>
-    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1">
       <c r="A18" s="128" t="s">
         <v>240</v>
       </c>
@@ -30734,7 +30779,7 @@
       <c r="R18" s="129"/>
       <c r="W18" s="130"/>
     </row>
-    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A19" s="2" t="s">
         <v>247</v>
       </c>
@@ -30769,7 +30814,7 @@
       <c r="R19" s="123"/>
       <c r="X19" s="123"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A20" s="2" t="s">
         <v>247</v>
       </c>
@@ -30801,7 +30846,7 @@
       <c r="R20" s="123"/>
       <c r="X20" s="123"/>
     </row>
-    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1">
       <c r="A21" s="127" t="s">
         <v>251</v>
       </c>
@@ -30820,7 +30865,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A22" s="2" t="s">
         <v>255</v>
       </c>
@@ -30862,7 +30907,7 @@
       <c r="AB22" s="124"/>
       <c r="AF22" s="115"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A23" s="2" t="s">
         <v>267</v>
       </c>
@@ -30896,7 +30941,7 @@
       <c r="X23" s="123"/>
       <c r="AI23" s="116"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
@@ -30930,7 +30975,7 @@
       <c r="X24" s="123"/>
       <c r="AI24" s="116"/>
     </row>
-    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -30954,7 +30999,7 @@
       </c>
       <c r="AI25" s="93"/>
     </row>
-    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" s="117" customFormat="1">
       <c r="A26" s="117" t="s">
         <v>275</v>
       </c>
@@ -30984,7 +31029,7 @@
       </c>
       <c r="X26" s="138"/>
     </row>
-    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
@@ -31018,7 +31063,7 @@
       <c r="R27" s="126"/>
       <c r="X27" s="123"/>
     </row>
-    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" hidden="1">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -31046,7 +31091,7 @@
       <c r="AI28" s="53"/>
       <c r="AJ28" s="48"/>
     </row>
-    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" hidden="1">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -31074,7 +31119,7 @@
       <c r="AI29" s="53"/>
       <c r="AJ29" s="48"/>
     </row>
-    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" hidden="1">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -31102,7 +31147,7 @@
       <c r="AI30" s="53"/>
       <c r="AJ30" s="48"/>
     </row>
-    <row r="31" spans="1:36" ht="26" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" ht="25.9" hidden="1" customHeight="1">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -31131,7 +31176,7 @@
       <c r="AI31" s="53"/>
       <c r="AJ31" s="48"/>
     </row>
-    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -31148,7 +31193,7 @@
       <c r="AH32"/>
       <c r="AI32" s="87"/>
     </row>
-    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1">
       <c r="A33" s="112" t="s">
         <v>294</v>
       </c>
@@ -31182,7 +31227,7 @@
       <c r="L33" s="41"/>
       <c r="X33" s="132"/>
     </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A34" s="2" t="s">
         <v>301</v>
       </c>
@@ -31213,7 +31258,7 @@
       <c r="Q34" s="127"/>
       <c r="AI34" s="116"/>
     </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A35" s="2" t="s">
         <v>307</v>
       </c>
@@ -31242,7 +31287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A36" s="2" t="s">
         <v>311</v>
       </c>
@@ -31274,7 +31319,7 @@
       <c r="X36" s="133"/>
       <c r="AA36" s="134"/>
     </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
@@ -31301,7 +31346,7 @@
       </c>
       <c r="R37" s="126"/>
     </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A38" s="127" t="s">
         <v>319</v>
       </c>
@@ -31317,7 +31362,7 @@
       </c>
       <c r="F38" s="127"/>
     </row>
-    <row r="39" spans="1:35" s="117" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" s="117" customFormat="1">
       <c r="A39" s="122" t="s">
         <v>329</v>
       </c>
@@ -31349,7 +31394,7 @@
       <c r="R39" s="141"/>
       <c r="X39" s="141"/>
     </row>
-    <row r="40" spans="1:35" s="117" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" s="117" customFormat="1">
       <c r="A40" s="122" t="s">
         <v>329</v>
       </c>
@@ -31383,7 +31428,7 @@
       <c r="AE40" s="120"/>
       <c r="AF40" s="142"/>
     </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A41" s="124" t="s">
         <v>336</v>
       </c>
@@ -31415,7 +31460,7 @@
       <c r="AD41" s="135"/>
       <c r="AE41" s="43"/>
     </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A42" s="124" t="s">
         <v>342</v>
       </c>
@@ -31446,7 +31491,7 @@
       <c r="X42" s="123"/>
       <c r="AE42" s="43"/>
     </row>
-    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1">
       <c r="A43" s="124" t="s">
         <v>345</v>
       </c>
@@ -31494,7 +31539,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
     </row>
-    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1">
       <c r="A44" s="124" t="s">
         <v>345</v>
       </c>
@@ -31542,7 +31587,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
     </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
@@ -31570,10 +31615,10 @@
       <c r="R45" s="123"/>
       <c r="X45" s="123"/>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35">
       <c r="A46" s="48"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:12">
       <c r="B50" s="143" t="s">
         <v>35</v>
       </c>
@@ -31608,7 +31653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:12">
       <c r="B51" s="143" t="s">
         <v>402</v>
       </c>
@@ -31627,7 +31672,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:12">
       <c r="B52" s="143"/>
       <c r="C52" s="143" t="s">
         <v>404</v>
@@ -31644,7 +31689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:12">
       <c r="B53" s="143" t="s">
         <v>405</v>
       </c>
@@ -31663,7 +31708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:12">
       <c r="B54" s="143"/>
       <c r="C54" s="143" t="s">
         <v>404</v>
@@ -31718,9 +31763,5 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}"/>
 </file>
--- a/data/Master Standardisation DACCS.xlsx
+++ b/data/Master Standardisation DACCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28803"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/_DACCS vs Synfuels/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6723" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EC0C5E-1BA4-4E65-B2EC-42F6D02F8A4B}"/>
+  <xr:revisionPtr revIDLastSave="6766" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8995197C-C705-47D3-A39C-A2D6721E81DA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="2" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -4132,7 +4132,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{93C04280-CBA5-B944-83DB-A7AAB169697E}"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -4582,13 +4582,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>84.85212367835156</v>
+            <v>78.932509034299216</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>67.202982248777587</v>
+            <v>61.275246906565449</v>
           </cell>
         </row>
       </sheetData>
@@ -4598,13 +4598,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>84.85212367835156</v>
+            <v>78.932509034299216</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>67.202982248777587</v>
+            <v>61.275246906565449</v>
           </cell>
         </row>
       </sheetData>
@@ -4614,13 +4614,13 @@
             <v>292.47958561757542</v>
           </cell>
           <cell r="G34">
-            <v>107.94825932901442</v>
+            <v>102.02864468496207</v>
           </cell>
           <cell r="I34">
             <v>292.47958561757542</v>
           </cell>
           <cell r="L34">
-            <v>90.299117899440446</v>
+            <v>84.371382557228301</v>
           </cell>
         </row>
       </sheetData>
@@ -4647,13 +4647,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>95.725439543447692</v>
+            <v>51.583582450093708</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>75.211005161759758</v>
+            <v>31.069148068405784</v>
           </cell>
         </row>
       </sheetData>
@@ -4663,13 +4663,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>95.725439543447692</v>
+            <v>51.583582450093708</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>75.211005161759758</v>
+            <v>31.069148068405784</v>
           </cell>
         </row>
       </sheetData>
@@ -4679,13 +4679,13 @@
             <v>289.21430381427916</v>
           </cell>
           <cell r="G34">
-            <v>118.82157519411055</v>
+            <v>74.67971810075656</v>
           </cell>
           <cell r="I34">
             <v>289.21430381427916</v>
           </cell>
           <cell r="L34">
-            <v>98.307140812422617</v>
+            <v>54.16528371906864</v>
           </cell>
         </row>
       </sheetData>
@@ -5118,17 +5118,17 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>170.41354109154099</v>
+            <v>161.70897790330613</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>113.7451627146863</v>
+            <v>104.86798641060018</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>311.65822312471437</v>
+            <v>300.09200804319312</v>
           </cell>
         </row>
       </sheetData>
@@ -5631,7 +5631,7 @@
             <v>145.45192472670769</v>
           </cell>
           <cell r="F24">
-            <v>112.66928210128302</v>
+            <v>110.40334766355258</v>
           </cell>
         </row>
       </sheetData>
@@ -5647,7 +5647,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>120.35739530021907</v>
+            <v>118.09146086248863</v>
           </cell>
         </row>
       </sheetData>
@@ -5663,7 +5663,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>145.35739530021908</v>
+            <v>143.09146086248865</v>
           </cell>
         </row>
       </sheetData>
@@ -5696,7 +5696,7 @@
             <v>186.68727529198395</v>
           </cell>
           <cell r="F24">
-            <v>148.24882769156065</v>
+            <v>145.98289325383018</v>
           </cell>
         </row>
       </sheetData>
@@ -5712,7 +5712,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>120.35739530021907</v>
+            <v>118.09146086248863</v>
           </cell>
         </row>
       </sheetData>
@@ -5728,7 +5728,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>145.35739530021908</v>
+            <v>143.09146086248865</v>
           </cell>
         </row>
       </sheetData>
@@ -6007,7 +6007,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>134.11219617439485</v>
+            <v>118.45853215160149</v>
           </cell>
         </row>
       </sheetData>
@@ -6019,7 +6019,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>122.49707212559984</v>
+            <v>106.84340810280642</v>
           </cell>
         </row>
       </sheetData>
@@ -6031,7 +6031,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>147.49707212559986</v>
+            <v>131.84340810280642</v>
           </cell>
         </row>
       </sheetData>
@@ -6076,7 +6076,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>139.37212947003994</v>
+            <v>136.97848574432413</v>
           </cell>
         </row>
       </sheetData>
@@ -6092,7 +6092,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>139.37212947003994</v>
+            <v>136.97848574432413</v>
           </cell>
         </row>
       </sheetData>
@@ -6108,7 +6108,7 @@
             <v>263.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>163.71895198084354</v>
+            <v>161.3365262382693</v>
           </cell>
         </row>
       </sheetData>
@@ -6348,17 +6348,17 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>233.35148149487728</v>
+            <v>204.09122311913183</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>131.99019858880641</v>
+            <v>107.86441779994588</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>522.16362117034964</v>
+            <v>471.65350886798007</v>
           </cell>
         </row>
       </sheetData>
@@ -6496,17 +6496,17 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>1173.97198503103</v>
+            <v>906.63214812469676</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>1062.3247136090472</v>
+            <v>795.12799940002435</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>1364.2529374119576</v>
+            <v>1096.6745626767736</v>
           </cell>
         </row>
       </sheetData>
@@ -6644,17 +6644,17 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>416.10639561160389</v>
+            <v>367.37217040690308</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>323.72847294776523</v>
+            <v>275.02033803264993</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>573.39646529779134</v>
+            <v>524.6187562771147</v>
           </cell>
         </row>
       </sheetData>
@@ -11670,7 +11670,7 @@
       <c r="M6" s="30"/>
       <c r="O6" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>187.76196330078002</v>
+        <v>178.17125904435753</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -11714,7 +11714,7 @@
       <c r="M7" s="30"/>
       <c r="O7" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>125.3246363550643</v>
+        <v>115.54374663969233</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -11758,7 +11758,7 @@
       <c r="M8" s="30"/>
       <c r="O8" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>343.38562228042122</v>
+        <v>330.64194453183813</v>
       </c>
     </row>
     <row r="9" spans="1:23" hidden="1">
@@ -11944,7 +11944,7 @@
       <c r="N12" s="30"/>
       <c r="O12" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G12))</f>
-        <v>257.10710559724805</v>
+        <v>224.86809733459555</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -11989,7 +11989,7 @@
       <c r="N13" s="30"/>
       <c r="O13" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G13))</f>
-        <v>145.42705154035619</v>
+        <v>118.84522043664496</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -12034,7 +12034,7 @@
       <c r="N14" s="30"/>
       <c r="O14" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G14))</f>
-        <v>575.32086973372702</v>
+        <v>519.66873204743047</v>
       </c>
     </row>
     <row r="15" spans="1:23" hidden="1">
@@ -12216,7 +12216,7 @@
       <c r="M18" s="30"/>
       <c r="O18" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G18))</f>
-        <v>1293.4845632433239</v>
+        <v>998.92902308774705</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -12260,7 +12260,7 @@
       <c r="M19" s="30"/>
       <c r="O19" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G19))</f>
-        <v>1170.4713874998199</v>
+        <v>876.07354020402272</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -12304,7 +12304,7 @@
       <c r="M20" s="30"/>
       <c r="O20" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G20))</f>
-        <v>1503.1364780438823</v>
+        <v>1208.3181164553391</v>
       </c>
     </row>
     <row r="21" spans="1:15" hidden="1">
@@ -12486,7 +12486,7 @@
       <c r="M24" s="30"/>
       <c r="O24" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G24))</f>
-        <v>458.46681714146951</v>
+        <v>404.77135523294874</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -12530,7 +12530,7 @@
       <c r="M25" s="30"/>
       <c r="O25" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G25))</f>
-        <v>356.68464646471131</v>
+        <v>303.01793088681831</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -12574,7 +12574,7 @@
       <c r="M26" s="30"/>
       <c r="O26" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G26))</f>
-        <v>631.76931471782575</v>
+        <v>578.02594225825874</v>
       </c>
     </row>
     <row r="27" spans="1:15" hidden="1">
@@ -14255,15 +14255,15 @@
       </c>
       <c r="M62" s="30">
         <f>'[12]Step 1 LCOE LS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G62))</f>
-        <v>82.867628361829105</v>
+        <v>34.232046362283334</v>
       </c>
       <c r="N62" s="30">
         <f>'[12]Step 2 WACC LS'!$L$31</f>
-        <v>75.211005161759758</v>
+        <v>31.069148068405784</v>
       </c>
       <c r="O62" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$L$34</f>
-        <v>98.307140812422617</v>
+        <v>54.16528371906864</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -14306,15 +14306,15 @@
       </c>
       <c r="M63" s="30">
         <f>'[12]Step 1 LCOE LS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G63))</f>
-        <v>105.47047113382258</v>
+        <v>56.8348891342768</v>
       </c>
       <c r="N63" s="30">
         <f>'[12]Step 2 WACC LS'!$G$31</f>
-        <v>95.725439543447692</v>
+        <v>51.583582450093708</v>
       </c>
       <c r="O63" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$G$34</f>
-        <v>118.82157519411055</v>
+        <v>74.67971810075656</v>
       </c>
     </row>
     <row r="64" spans="1:15" hidden="1">
@@ -14464,15 +14464,15 @@
       </c>
       <c r="M66" s="30">
         <f>'[12]Step 1 LCOE SS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G66))</f>
-        <v>74.0443735038629</v>
+        <v>67.513183443189845</v>
       </c>
       <c r="N66" s="30">
         <f>'[12]Step 2 WACC SS'!$L$31</f>
-        <v>67.202982248777587</v>
+        <v>61.275246906565449</v>
       </c>
       <c r="O66" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$L$34</f>
-        <v>90.299117899440446</v>
+        <v>84.371382557228301</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -14515,15 +14515,15 @@
       </c>
       <c r="M67" s="30">
         <f>'[12]Step 1 LCOE SS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G67))</f>
-        <v>93.490231058162834</v>
+        <v>86.967988398148719</v>
       </c>
       <c r="N67" s="30">
         <f>'[12]Step 2 WACC SS'!$G$31</f>
-        <v>84.85212367835156</v>
+        <v>78.932509034299216</v>
       </c>
       <c r="O67" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$G$34</f>
-        <v>107.94825932901442</v>
+        <v>102.02864468496207</v>
       </c>
     </row>
     <row r="68" spans="1:15" hidden="1">
@@ -17452,15 +17452,15 @@
       </c>
       <c r="M140" s="30">
         <f>'[21]Step 1 LCOE - EE'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>130.30491652206067</v>
+        <v>127.68430518730926</v>
       </c>
       <c r="N140" s="30">
         <f>'[21]Step 2 WACC'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>139.1964167598891</v>
+        <v>136.57580542513767</v>
       </c>
       <c r="O140" s="30">
         <f>'[21]Step 3 T&amp;S'!$F$27*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>168.10955841036227</v>
+        <v>165.48894707561087</v>
       </c>
     </row>
     <row r="141" spans="1:15" hidden="1">
@@ -17653,15 +17653,15 @@
       </c>
       <c r="M144" s="30">
         <f>'[21]Step 1 LCOE - EE (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>171.45357418250728</v>
+        <v>168.83296284775582</v>
       </c>
       <c r="N144" s="30">
         <f>'[21]Step 2 WACC (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>139.1964167598891</v>
+        <v>136.57580542513767</v>
       </c>
       <c r="O144" s="30">
         <f>'[21]Step 3 T&amp;S (2)'!$F$27* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>168.10955841036227</v>
+        <v>165.48894707561087</v>
       </c>
     </row>
     <row r="145" spans="1:15" hidden="1">
@@ -18407,15 +18407,15 @@
       </c>
       <c r="M163" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>134.11219617439485</v>
+        <v>118.45853215160149</v>
       </c>
       <c r="N163" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>122.49707212559984</v>
+        <v>106.84340810280642</v>
       </c>
       <c r="O163" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>147.49707212559986</v>
+        <v>131.84340810280642</v>
       </c>
     </row>
     <row r="164" spans="1:15">
@@ -18455,15 +18455,15 @@
       </c>
       <c r="M164" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>134.11219617439485</v>
+        <v>118.45853215160149</v>
       </c>
       <c r="N164" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>122.49707212559984</v>
+        <v>106.84340810280642</v>
       </c>
       <c r="O164" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>147.49707212559986</v>
+        <v>131.84340810280642</v>
       </c>
     </row>
     <row r="165" spans="1:15">
@@ -18503,15 +18503,15 @@
       </c>
       <c r="M165" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>134.11219617439485</v>
+        <v>118.45853215160149</v>
       </c>
       <c r="N165" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>122.49707212559984</v>
+        <v>106.84340810280642</v>
       </c>
       <c r="O165" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>147.49707212559986</v>
+        <v>131.84340810280642</v>
       </c>
     </row>
     <row r="166" spans="1:15" hidden="1">
@@ -18697,15 +18697,15 @@
       </c>
       <c r="M169" s="30">
         <f>'[27]Step 1 - LCOE + EE'!$G$23</f>
-        <v>139.37212947003994</v>
+        <v>136.97848574432413</v>
       </c>
       <c r="N169" s="30">
         <f>'[27]Step 2 - WACC'!$G$23</f>
-        <v>139.37212947003994</v>
+        <v>136.97848574432413</v>
       </c>
       <c r="O169" s="30">
         <f>'[27]Step 3 - T&amp;S'!$G$23</f>
-        <v>163.71895198084354</v>
+        <v>161.3365262382693</v>
       </c>
     </row>
     <row r="170" spans="1:15" hidden="1">
@@ -21294,7 +21294,7 @@
         <v>2050</v>
       </c>
       <c r="C10">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>

--- a/data/Master Standardisation DACCS.xlsx
+++ b/data/Master Standardisation DACCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/_DACCS vs Synfuels/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6766" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8995197C-C705-47D3-A39C-A2D6721E81DA}"/>
+  <xr:revisionPtr revIDLastSave="6723" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EC0C5E-1BA4-4E65-B2EC-42F6D02F8A4B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="10" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="2" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -4132,7 +4132,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{93C04280-CBA5-B944-83DB-A7AAB169697E}"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -4582,13 +4582,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>78.932509034299216</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>61.275246906565449</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
@@ -4598,13 +4598,13 @@
             <v>255.52576857651488</v>
           </cell>
           <cell r="G31">
-            <v>78.932509034299216</v>
+            <v>84.85212367835156</v>
           </cell>
           <cell r="I31">
             <v>255.52576857651488</v>
           </cell>
           <cell r="L31">
-            <v>61.275246906565449</v>
+            <v>67.202982248777587</v>
           </cell>
         </row>
       </sheetData>
@@ -4614,13 +4614,13 @@
             <v>292.47958561757542</v>
           </cell>
           <cell r="G34">
-            <v>102.02864468496207</v>
+            <v>107.94825932901442</v>
           </cell>
           <cell r="I34">
             <v>292.47958561757542</v>
           </cell>
           <cell r="L34">
-            <v>84.371382557228301</v>
+            <v>90.299117899440446</v>
           </cell>
         </row>
       </sheetData>
@@ -4647,13 +4647,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>51.583582450093708</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>31.069148068405784</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
@@ -4663,13 +4663,13 @@
             <v>252.26048677321859</v>
           </cell>
           <cell r="G31">
-            <v>51.583582450093708</v>
+            <v>95.725439543447692</v>
           </cell>
           <cell r="I31">
             <v>252.26048677321859</v>
           </cell>
           <cell r="L31">
-            <v>31.069148068405784</v>
+            <v>75.211005161759758</v>
           </cell>
         </row>
       </sheetData>
@@ -4679,13 +4679,13 @@
             <v>289.21430381427916</v>
           </cell>
           <cell r="G34">
-            <v>74.67971810075656</v>
+            <v>118.82157519411055</v>
           </cell>
           <cell r="I34">
             <v>289.21430381427916</v>
           </cell>
           <cell r="L34">
-            <v>54.16528371906864</v>
+            <v>98.307140812422617</v>
           </cell>
         </row>
       </sheetData>
@@ -5118,17 +5118,17 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>161.70897790330613</v>
+            <v>170.41354109154099</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>104.86798641060018</v>
+            <v>113.7451627146863</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>300.09200804319312</v>
+            <v>311.65822312471437</v>
           </cell>
         </row>
       </sheetData>
@@ -5631,7 +5631,7 @@
             <v>145.45192472670769</v>
           </cell>
           <cell r="F24">
-            <v>110.40334766355258</v>
+            <v>112.66928210128302</v>
           </cell>
         </row>
       </sheetData>
@@ -5647,7 +5647,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>118.09146086248863</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5663,7 +5663,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>143.09146086248865</v>
+            <v>145.35739530021908</v>
           </cell>
         </row>
       </sheetData>
@@ -5696,7 +5696,7 @@
             <v>186.68727529198395</v>
           </cell>
           <cell r="F24">
-            <v>145.98289325383018</v>
+            <v>148.24882769156065</v>
           </cell>
         </row>
       </sheetData>
@@ -5712,7 +5712,7 @@
             <v>154.3621577744924</v>
           </cell>
           <cell r="F24">
-            <v>118.09146086248863</v>
+            <v>120.35739530021907</v>
           </cell>
         </row>
       </sheetData>
@@ -5728,7 +5728,7 @@
             <v>194.3621577744924</v>
           </cell>
           <cell r="F27">
-            <v>143.09146086248865</v>
+            <v>145.35739530021908</v>
           </cell>
         </row>
       </sheetData>
@@ -6007,7 +6007,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>118.45853215160149</v>
+            <v>134.11219617439485</v>
           </cell>
         </row>
       </sheetData>
@@ -6019,7 +6019,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>106.84340810280642</v>
+            <v>122.49707212559984</v>
           </cell>
         </row>
       </sheetData>
@@ -6031,7 +6031,7 @@
         </row>
         <row r="21">
           <cell r="B21">
-            <v>131.84340810280642</v>
+            <v>147.49707212559986</v>
           </cell>
         </row>
       </sheetData>
@@ -6076,7 +6076,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>136.97848574432413</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6092,7 +6092,7 @@
             <v>223.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>136.97848574432413</v>
+            <v>139.37212947003994</v>
           </cell>
         </row>
       </sheetData>
@@ -6108,7 +6108,7 @@
             <v>263.41019772115243</v>
           </cell>
           <cell r="G23">
-            <v>161.3365262382693</v>
+            <v>163.71895198084354</v>
           </cell>
         </row>
       </sheetData>
@@ -6348,17 +6348,17 @@
       <sheetData sheetId="2">
         <row r="15">
           <cell r="I15">
-            <v>204.09122311913183</v>
+            <v>233.35148149487728</v>
           </cell>
         </row>
         <row r="16">
           <cell r="I16">
-            <v>107.86441779994588</v>
+            <v>131.99019858880641</v>
           </cell>
         </row>
         <row r="17">
           <cell r="I17">
-            <v>471.65350886798007</v>
+            <v>522.16362117034964</v>
           </cell>
         </row>
       </sheetData>
@@ -6496,17 +6496,17 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>906.63214812469676</v>
+            <v>1173.97198503103</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>795.12799940002435</v>
+            <v>1062.3247136090472</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>1096.6745626767736</v>
+            <v>1364.2529374119576</v>
           </cell>
         </row>
       </sheetData>
@@ -6644,17 +6644,17 @@
       <sheetData sheetId="2">
         <row r="2">
           <cell r="I2">
-            <v>367.37217040690308</v>
+            <v>416.10639561160389</v>
           </cell>
         </row>
         <row r="3">
           <cell r="I3">
-            <v>275.02033803264993</v>
+            <v>323.72847294776523</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>524.6187562771147</v>
+            <v>573.39646529779134</v>
           </cell>
         </row>
       </sheetData>
@@ -11670,7 +11670,7 @@
       <c r="M6" s="30"/>
       <c r="O6" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>178.17125904435753</v>
+        <v>187.76196330078002</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -11714,7 +11714,7 @@
       <c r="M7" s="30"/>
       <c r="O7" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>115.54374663969233</v>
+        <v>125.3246363550643</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -11758,7 +11758,7 @@
       <c r="M8" s="30"/>
       <c r="O8" s="30">
         <f>'[2]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G3))</f>
-        <v>330.64194453183813</v>
+        <v>343.38562228042122</v>
       </c>
     </row>
     <row r="9" spans="1:23" hidden="1">
@@ -11944,7 +11944,7 @@
       <c r="N12" s="30"/>
       <c r="O12" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$15* ((1+Inputs!$C$5) ^ (2023-G12))</f>
-        <v>224.86809733459555</v>
+        <v>257.10710559724805</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -11989,7 +11989,7 @@
       <c r="N13" s="30"/>
       <c r="O13" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$16* ((1+Inputs!$C$5) ^ (2023-G13))</f>
-        <v>118.84522043664496</v>
+        <v>145.42705154035619</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -12034,7 +12034,7 @@
       <c r="N14" s="30"/>
       <c r="O14" s="30">
         <f>'[4]Inputs and TEA calculations'!$I$17* ((1+Inputs!$C$5) ^ (2023-G14))</f>
-        <v>519.66873204743047</v>
+        <v>575.32086973372702</v>
       </c>
     </row>
     <row r="15" spans="1:23" hidden="1">
@@ -12216,7 +12216,7 @@
       <c r="M18" s="30"/>
       <c r="O18" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G18))</f>
-        <v>998.92902308774705</v>
+        <v>1293.4845632433239</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -12260,7 +12260,7 @@
       <c r="M19" s="30"/>
       <c r="O19" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G19))</f>
-        <v>876.07354020402272</v>
+        <v>1170.4713874998199</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -12304,7 +12304,7 @@
       <c r="M20" s="30"/>
       <c r="O20" s="139">
         <f>'[6]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G20))</f>
-        <v>1208.3181164553391</v>
+        <v>1503.1364780438823</v>
       </c>
     </row>
     <row r="21" spans="1:15" hidden="1">
@@ -12486,7 +12486,7 @@
       <c r="M24" s="30"/>
       <c r="O24" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$2* ((1+Inputs!$C$5) ^ (2023-G24))</f>
-        <v>404.77135523294874</v>
+        <v>458.46681714146951</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -12530,7 +12530,7 @@
       <c r="M25" s="30"/>
       <c r="O25" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$3* ((1+Inputs!$C$5) ^ (2023-G25))</f>
-        <v>303.01793088681831</v>
+        <v>356.68464646471131</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -12574,7 +12574,7 @@
       <c r="M26" s="30"/>
       <c r="O26" s="139">
         <f>'[8]Inputs and TEA calculations'!$I$4* ((1+Inputs!$C$5) ^ (2023-G26))</f>
-        <v>578.02594225825874</v>
+        <v>631.76931471782575</v>
       </c>
     </row>
     <row r="27" spans="1:15" hidden="1">
@@ -14255,15 +14255,15 @@
       </c>
       <c r="M62" s="30">
         <f>'[12]Step 1 LCOE LS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G62))</f>
-        <v>34.232046362283334</v>
+        <v>82.867628361829105</v>
       </c>
       <c r="N62" s="30">
         <f>'[12]Step 2 WACC LS'!$L$31</f>
-        <v>31.069148068405784</v>
+        <v>75.211005161759758</v>
       </c>
       <c r="O62" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$L$34</f>
-        <v>54.16528371906864</v>
+        <v>98.307140812422617</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -14306,15 +14306,15 @@
       </c>
       <c r="M63" s="30">
         <f>'[12]Step 1 LCOE LS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G63))</f>
-        <v>56.8348891342768</v>
+        <v>105.47047113382258</v>
       </c>
       <c r="N63" s="30">
         <f>'[12]Step 2 WACC LS'!$G$31</f>
-        <v>51.583582450093708</v>
+        <v>95.725439543447692</v>
       </c>
       <c r="O63" s="30">
         <f>'[12]Step 3 T&amp;S LS'!$G$34</f>
-        <v>74.67971810075656</v>
+        <v>118.82157519411055</v>
       </c>
     </row>
     <row r="64" spans="1:15" hidden="1">
@@ -14464,15 +14464,15 @@
       </c>
       <c r="M66" s="30">
         <f>'[12]Step 1 LCOE SS'!$L$31* ((1+Inputs!$C$5) ^ (2022-G66))</f>
-        <v>67.513183443189845</v>
+        <v>74.0443735038629</v>
       </c>
       <c r="N66" s="30">
         <f>'[12]Step 2 WACC SS'!$L$31</f>
-        <v>61.275246906565449</v>
+        <v>67.202982248777587</v>
       </c>
       <c r="O66" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$L$34</f>
-        <v>84.371382557228301</v>
+        <v>90.299117899440446</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -14515,15 +14515,15 @@
       </c>
       <c r="M67" s="30">
         <f>'[12]Step 1 LCOE SS'!$G$31* ((1+Inputs!$C$5) ^ (2022-G67))</f>
-        <v>86.967988398148719</v>
+        <v>93.490231058162834</v>
       </c>
       <c r="N67" s="30">
         <f>'[12]Step 2 WACC SS'!$G$31</f>
-        <v>78.932509034299216</v>
+        <v>84.85212367835156</v>
       </c>
       <c r="O67" s="30">
         <f>'[12]Step 3 T&amp;S SS'!$G$34</f>
-        <v>102.02864468496207</v>
+        <v>107.94825932901442</v>
       </c>
     </row>
     <row r="68" spans="1:15" hidden="1">
@@ -17452,15 +17452,15 @@
       </c>
       <c r="M140" s="30">
         <f>'[21]Step 1 LCOE - EE'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>127.68430518730926</v>
+        <v>130.30491652206067</v>
       </c>
       <c r="N140" s="30">
         <f>'[21]Step 2 WACC'!$F$24*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>136.57580542513767</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O140" s="30">
         <f>'[21]Step 3 T&amp;S'!$F$27*((1+Inputs!$C$5)^(2022-G140))</f>
-        <v>165.48894707561087</v>
+        <v>168.10955841036227</v>
       </c>
     </row>
     <row r="141" spans="1:15" hidden="1">
@@ -17653,15 +17653,15 @@
       </c>
       <c r="M144" s="30">
         <f>'[21]Step 1 LCOE - EE (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>168.83296284775582</v>
+        <v>171.45357418250728</v>
       </c>
       <c r="N144" s="30">
         <f>'[21]Step 2 WACC (2)'!$F$24* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>136.57580542513767</v>
+        <v>139.1964167598891</v>
       </c>
       <c r="O144" s="30">
         <f>'[21]Step 3 T&amp;S (2)'!$F$27* ((1+Inputs!$C$5) ^ (2022-G144))</f>
-        <v>165.48894707561087</v>
+        <v>168.10955841036227</v>
       </c>
     </row>
     <row r="145" spans="1:15" hidden="1">
@@ -18407,15 +18407,15 @@
       </c>
       <c r="M163" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N163" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O163" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
+        <v>147.49707212559986</v>
       </c>
     </row>
     <row r="164" spans="1:15">
@@ -18455,15 +18455,15 @@
       </c>
       <c r="M164" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N164" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O164" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
+        <v>147.49707212559986</v>
       </c>
     </row>
     <row r="165" spans="1:15">
@@ -18503,15 +18503,15 @@
       </c>
       <c r="M165" s="30">
         <f>'[26]Step 1 LCOE + EE'!$B$21</f>
-        <v>118.45853215160149</v>
+        <v>134.11219617439485</v>
       </c>
       <c r="N165" s="30">
         <f>'[26]Step 2 WACC'!$B$21</f>
-        <v>106.84340810280642</v>
+        <v>122.49707212559984</v>
       </c>
       <c r="O165" s="30">
         <f>'[26]Step 3 T&amp;S'!$B$21</f>
-        <v>131.84340810280642</v>
+        <v>147.49707212559986</v>
       </c>
     </row>
     <row r="166" spans="1:15" hidden="1">
@@ -18697,15 +18697,15 @@
       </c>
       <c r="M169" s="30">
         <f>'[27]Step 1 - LCOE + EE'!$G$23</f>
-        <v>136.97848574432413</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="N169" s="30">
         <f>'[27]Step 2 - WACC'!$G$23</f>
-        <v>136.97848574432413</v>
+        <v>139.37212947003994</v>
       </c>
       <c r="O169" s="30">
         <f>'[27]Step 3 - T&amp;S'!$G$23</f>
-        <v>161.3365262382693</v>
+        <v>163.71895198084354</v>
       </c>
     </row>
     <row r="170" spans="1:15" hidden="1">
@@ -21294,7 +21294,7 @@
         <v>2050</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>

--- a/data/Master Standardisation DACCS.xlsx
+++ b/data/Master Standardisation DACCS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28723"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/_DACCS vs Synfuels/Meta Analysis_DACCS/4 Harmonization/Harmonization Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ydubey_ethz_ch/Documents/Documents/GitHub/DACCSvDACCU/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6723" documentId="8_{427C1CD8-7ECB-4B05-A7A1-DCEB31902E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EC0C5E-1BA4-4E65-B2EC-42F6D02F8A4B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="973" firstSheet="2" activeTab="2" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15345" tabRatio="973" firstSheet="2" activeTab="2" xr2:uid="{10A797D3-143E-48A4-A3E1-9D6BC7B2CBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,9 @@
     <externalReference r:id="rId43"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Studies current &amp;future cost'!$A$1:$AL$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Study Parameters'!$A$1:$AL$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Standardization Results'!$A$2:$W$180</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3374,17 +3374,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.00000_ ;_ * \-#,##0.00000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3908,7 +3908,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3929,21 +3929,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -3984,8 +3984,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4046,10 +4046,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="33" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4064,7 +4064,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -4073,16 +4073,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -4118,7 +4118,7 @@
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="10" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4132,7 +4132,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{93C04280-CBA5-B944-83DB-A7AAB169697E}"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -7404,9 +7404,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7420,7 +7420,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
   <sheetPr codeName="Sheet6" filterMode="1"/>
   <dimension ref="A1:AL47"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -7446,7 +7446,7 @@
     <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="AI3" s="53"/>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AI4" s="53"/>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="AI5" s="53"/>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:38" hidden="1">
+    <row r="9" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>199</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:38" hidden="1">
+    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>208</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>214</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>214</v>
       </c>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AI12" s="53"/>
     </row>
-    <row r="13" spans="1:38" hidden="1">
+    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>223</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:38" hidden="1">
+    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>227</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" hidden="1">
+    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>230</v>
       </c>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="AL15" s="48"/>
     </row>
-    <row r="16" spans="1:38" hidden="1">
+    <row r="16" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>230</v>
       </c>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AL16" s="48"/>
     </row>
-    <row r="17" spans="1:37" hidden="1">
+    <row r="17" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>234</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1">
+    <row r="18" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58" t="s">
         <v>240</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:37" hidden="1">
+    <row r="19" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>247</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:37" hidden="1">
+    <row r="20" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1">
+    <row r="21" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>251</v>
       </c>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AH21"/>
     </row>
-    <row r="22" spans="1:37" hidden="1">
+    <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>255</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="23" spans="1:37" hidden="1">
+    <row r="23" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>267</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="24" spans="1:37" hidden="1">
+    <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1">
+    <row r="25" spans="1:37" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>275</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:37" hidden="1">
+    <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>278</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:37" hidden="1">
+    <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -10004,7 +10004,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="29" spans="1:37" hidden="1">
+    <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:37" hidden="1">
+    <row r="30" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="25.9" hidden="1" customHeight="1">
+    <row r="31" spans="1:37" ht="25.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1">
+    <row r="32" spans="1:37" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1">
+    <row r="33" spans="1:37" s="58" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58" t="s">
         <v>294</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:37" hidden="1">
+    <row r="34" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>301</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="35" spans="1:37" hidden="1">
+    <row r="35" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="36" spans="1:37" hidden="1">
+    <row r="36" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -10615,7 +10615,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="37" spans="1:37" hidden="1">
+    <row r="37" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>315</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="38" spans="1:37" hidden="1">
+    <row r="38" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="48" t="s">
         <v>319</v>
       </c>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="F38" s="48"/>
     </row>
-    <row r="39" spans="1:37">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>329</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="40" spans="1:37">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>329</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="1:37" hidden="1">
+    <row r="41" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="55" t="s">
         <v>336</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="42" spans="1:37" hidden="1">
+    <row r="42" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55" t="s">
         <v>342</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1">
+    <row r="43" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="55" t="s">
         <v>345</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1">
+    <row r="44" spans="1:37" s="92" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="55" t="s">
         <v>345</v>
       </c>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="AH44"/>
     </row>
-    <row r="45" spans="1:37" hidden="1">
+    <row r="45" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>348</v>
       </c>
@@ -11340,10 +11340,10 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="1:37" hidden="1">
+    <row r="46" spans="1:37" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
     </row>
-    <row r="47" spans="1:37" hidden="1"/>
+    <row r="47" spans="1:37" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:AL47" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
     <filterColumn colId="0">
@@ -11389,7 +11389,7 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:W180"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
@@ -11407,7 +11407,7 @@
     <col min="16" max="22" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="L1" s="144" t="s">
         <v>655</v>
       </c>
@@ -11422,7 +11422,7 @@
       <c r="Q1" s="144"/>
       <c r="R1" s="144"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>414.8542592918007</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>342.50358359189738</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>151</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>523.95174204407829</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>187.76196330078002</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>125.3246363550643</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>343.38562228042122</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>'Study Parameters'!A3</f>
         <v>Young et al. 2023</v>
@@ -11812,7 +11812,7 @@
         <v>2060.169523488109</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -11857,7 +11857,7 @@
         <v>1488.7216799143798</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>151</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>2729.5646158724885</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>151</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>257.10710559724805</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>151</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>145.42705154035619</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>151</v>
       </c>
@@ -12037,7 +12037,7 @@
         <v>575.32086973372702</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>'Study Parameters'!A4</f>
         <v>Young et al. 2023</v>
@@ -12087,7 +12087,7 @@
         <v>1308.9151041939408</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>1185.9075603382862</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>151</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>1518.5576325147504</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>151</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>1293.4845632433239</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>1170.4713874998199</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>151</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>1503.1364780438823</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>'Study Parameters'!A5</f>
         <v>Young et al. 2023</v>
@@ -12357,7 +12357,7 @@
         <v>484.59306078439545</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -12401,7 +12401,7 @@
         <v>382.81191676230259</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>151</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>657.89384726964306</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>151</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>458.46681714146951</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -12533,7 +12533,7 @@
         <v>356.68464646471131</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>151</v>
       </c>
@@ -12577,7 +12577,7 @@
         <v>631.76931471782575</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="48" t="str">
         <f>'Study Parameters'!A6</f>
         <v>Sievert et al. 2024</v>
@@ -12626,7 +12626,7 @@
         <v>669.94069463308699</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>521.31303134173265</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>185</v>
       </c>
@@ -12714,7 +12714,7 @@
         <v>894.39776183919753</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>'Study Parameters'!A7</f>
         <v>Sievert et al. 2024</v>
@@ -12895,7 +12895,7 @@
         <v>1282.314450530346</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -12938,7 +12938,7 @@
         <v>1180.094323057237</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>185</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>1392.3242644152151</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>185</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>185</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>'Study Parameters'!A8</f>
         <v>Sievert et al. 2024</v>
@@ -13162,7 +13162,7 @@
         <v>2481.3480043001368</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>2153.1601565847341</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>185</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>2874.3199941446942</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13433,7 +13433,7 @@
         <v>293.01246179996224</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13488,7 +13488,7 @@
         <v>267.3339028754757</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>'Study Parameters'!A9</f>
         <v>McQueen et al. 2020a</v>
@@ -13543,7 +13543,7 @@
         <v>303.19697040786667</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13590,7 +13590,7 @@
         <v>278.51244114406211</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13637,7 +13637,7 @@
         <v>260.17305813012763</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13684,7 +13684,7 @@
         <v>334.02175471233329</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13731,7 +13731,7 @@
         <v>347.52430793993972</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13778,7 +13778,7 @@
         <v>431.20952014305874</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13825,7 +13825,7 @@
         <v>405.58125796275607</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13872,7 +13872,7 @@
         <v>532.88151930075014</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13923,7 +13923,7 @@
         <v>598.00725415939087</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -13969,7 +13969,7 @@
         <v>594.26871158968584</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14015,7 +14015,7 @@
         <v>556.61504560775791</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14061,7 +14061,7 @@
         <v>745.92213758183834</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>'Study Parameters'!$A$10</f>
         <v>Sendi et al. 2022</v>
@@ -14107,7 +14107,7 @@
         <v>863.3220713069054</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>'Study Parameters'!A11</f>
         <v>Fasihi et al. 2019</v>
@@ -14164,7 +14164,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>289.21430381427916</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>98.307140812422617</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>214</v>
       </c>
@@ -14317,7 +14317,7 @@
         <v>118.82157519411055</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>'Study Parameters'!A12</f>
         <v>Fasihi et al. 2019</v>
@@ -14373,7 +14373,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>214</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>292.47958561757542</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>214</v>
       </c>
@@ -14475,7 +14475,7 @@
         <v>90.299117899440446</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>214</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>107.94825932901442</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>'Study Parameters'!A13</f>
         <v>Mazzotti et al. 2013</v>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="M68" s="30"/>
     </row>
-    <row r="69" spans="1:15" hidden="1">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>223</v>
       </c>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="M69" s="30"/>
     </row>
-    <row r="70" spans="1:15" hidden="1">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>223</v>
       </c>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="M70" s="30"/>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>'Study Parameters'!A14</f>
         <v>Zeman 2014</v>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="M71" s="30"/>
     </row>
-    <row r="72" spans="1:15" hidden="1">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>'Study Parameters'!A15</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="M72" s="30"/>
     </row>
-    <row r="73" spans="1:15" hidden="1">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>230</v>
       </c>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="M73" s="30"/>
     </row>
-    <row r="74" spans="1:15" hidden="1">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>'Study Parameters'!A16</f>
         <v>Prats-Salvado et al. 2024</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="M74" s="30"/>
     </row>
-    <row r="75" spans="1:15" hidden="1">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>230</v>
       </c>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M75" s="30"/>
     </row>
-    <row r="76" spans="1:15" hidden="1">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>'Study Parameters'!A17</f>
         <v>Terlouw et al. 2024</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="M76" s="62"/>
     </row>
-    <row r="77" spans="1:15" hidden="1">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>234</v>
       </c>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="M77" s="62"/>
     </row>
-    <row r="78" spans="1:15" hidden="1">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>'Study Parameters'!A18</f>
         <v>McQueen et al. 2021</v>
@@ -15004,7 +15004,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>240</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>400.60217261536002</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -15121,7 +15121,7 @@
         <v>881.5737078159442</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>240</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>463.06098024892566</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>240</v>
       </c>
@@ -15199,7 +15199,7 @@
         <v>558.57147419213493</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>240</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>777.69611217374995</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>2052.1001665091567</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f>'Study Parameters'!A19</f>
         <v>Datta et al. 2023</v>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="M86" s="30"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="str">
         <f>'Study Parameters'!A20</f>
         <v>Datta et al. 2023</v>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="M87" s="30"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="M88" s="30"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>255</v>
       </c>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="M89" s="30"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="M90" s="30"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>255</v>
       </c>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="M91" s="30"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="M92" s="30"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="M93" s="30"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>255</v>
       </c>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="M94" s="30"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>255</v>
       </c>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="M95" s="30"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>255</v>
       </c>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="M96" s="30"/>
     </row>
-    <row r="97" spans="1:12" hidden="1">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f>'Study Parameters'!A22</f>
         <v>Simon et al. 2011</v>
@@ -15777,7 +15777,7 @@
         <v>304.707654655694</v>
       </c>
     </row>
-    <row r="98" spans="1:12" hidden="1">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>255</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>803.14143939193252</v>
       </c>
     </row>
-    <row r="99" spans="1:12" hidden="1">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -15857,7 +15857,7 @@
         <v>329.15418006599049</v>
       </c>
     </row>
-    <row r="100" spans="1:12" hidden="1">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>267</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>779.02843503778104</v>
       </c>
     </row>
-    <row r="101" spans="1:12" hidden="1">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>267</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>831.75510668257198</v>
       </c>
     </row>
-    <row r="102" spans="1:12" hidden="1">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>267</v>
       </c>
@@ -15971,7 +15971,7 @@
         <v>317.24671499539198</v>
       </c>
     </row>
-    <row r="103" spans="1:12" hidden="1">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>267</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>371.938416568371</v>
       </c>
     </row>
-    <row r="104" spans="1:12" hidden="1">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>267</v>
       </c>
@@ -16047,7 +16047,7 @@
         <v>291.241690193887</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>267</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>355.05876736764702</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>267</v>
       </c>
@@ -16123,7 +16123,7 @@
         <v>267.11083137986202</v>
       </c>
     </row>
-    <row r="107" spans="1:12" hidden="1">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f>'Study Parameters'!A23</f>
         <v>Küng et al. 2023</v>
@@ -16167,7 +16167,7 @@
         <v>314.61251708631102</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>267</v>
       </c>
@@ -16205,7 +16205,7 @@
         <v>1817.71250053524</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>267</v>
       </c>
@@ -16243,7 +16243,7 @@
         <v>1990.0315112179401</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>267</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>980.75097520117902</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>267</v>
       </c>
@@ -16319,7 +16319,7 @@
         <v>1064.51188379418</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>267</v>
       </c>
@@ -16357,7 +16357,7 @@
         <v>411.65027432423102</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>267</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>488.64611354083598</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>267</v>
       </c>
@@ -16433,7 +16433,7 @@
         <v>378.55341271061599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>267</v>
       </c>
@@ -16471,7 +16471,7 @@
         <v>468.39609948070898</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>267</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>349.10367628750998</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>267</v>
       </c>
@@ -16547,7 +16547,7 @@
         <v>415.97729787873197</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>267</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>2476.9733161530498</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>267</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>2750.7170677000299</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f>'Study Parameters'!A24</f>
         <v>Küng et al. 2023</v>
@@ -16666,7 +16666,7 @@
         <v>183.15040372394199</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>267</v>
       </c>
@@ -16704,7 +16704,7 @@
         <v>227.07677281852301</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>61.893630816227301</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>72.225103599114604</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>393.65606020680502</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -16856,7 +16856,7 @@
         <v>503.939346853232</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -16894,7 +16894,7 @@
         <v>406.913082895564</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>517.19636954199098</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -16970,7 +16970,7 @@
         <v>243.248532930187</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -17008,7 +17008,7 @@
         <v>305.088767461244</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -17046,7 +17046,7 @@
         <v>76.028698179975393</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -17084,7 +17084,7 @@
         <v>90.573508350133693</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -17122,7 +17122,7 @@
         <v>523.47869237559496</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>698.67329510641696</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -17198,7 +17198,7 @@
         <v>536.73571506435496</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>711.93031779517605</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f>'Study Parameters'!A25</f>
         <v>Mostafa et al. 2022</v>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="L136" s="30"/>
     </row>
-    <row r="137" spans="1:15" hidden="1">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f>'Study Parameters'!A26</f>
         <v>Keith et al. 2018</v>
@@ -17319,7 +17319,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>275</v>
       </c>
@@ -17415,7 +17415,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>168.10955841036227</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>275</v>
       </c>
@@ -17514,7 +17514,7 @@
         <v>295.67151321600323</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>275</v>
       </c>
@@ -17565,7 +17565,7 @@
         <v>238.63022727495593</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>275</v>
       </c>
@@ -17616,7 +17616,7 @@
         <v>224.78482396902055</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>275</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>168.10955841036227</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f>'Study Parameters'!A27</f>
         <v>Gray et al. 2024</v>
@@ -17718,7 +17718,7 @@
         <v>1422.4526421724208</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f>'Study Parameters'!A28</f>
         <v>Rosen et al. 2024</v>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="L146" s="30"/>
     </row>
-    <row r="147" spans="1:15" hidden="1">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f>'Study Parameters'!A29</f>
         <v>Rosen et al. 2024</v>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="L147" s="30"/>
     </row>
-    <row r="148" spans="1:15" hidden="1">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f>'Study Parameters'!A30</f>
         <v>Rosen et al. 2024</v>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="L148" s="30"/>
     </row>
-    <row r="149" spans="1:15" hidden="1">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f>'Study Parameters'!A31</f>
         <v>Rosen et al. 2024</v>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="L149" s="30"/>
     </row>
-    <row r="150" spans="1:15" hidden="1">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f>'Study Parameters'!A32</f>
         <v>Sabatino et al. 2020</v>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="L150" s="30"/>
     </row>
-    <row r="151" spans="1:15" hidden="1">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17919,7 +17919,7 @@
         <v>52.859259278213045</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="str">
         <f>'Study Parameters'!A33</f>
         <v>McQueen et al. 2020c</v>
@@ -17960,7 +17960,7 @@
         <v>174.22096158203897</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -17996,7 +17996,7 @@
         <v>45.162595126533958</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>294</v>
       </c>
@@ -18032,7 +18032,7 @@
         <v>155.30185025856494</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="str">
         <f>'Study Parameters'!A34</f>
         <v>Lee et al. 2023</v>
@@ -18090,7 +18090,7 @@
         <v>270.09276004403995</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="str">
         <f>'Study Parameters'!A35</f>
         <v>Abanades et al. 2023</v>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="L156" s="30"/>
     </row>
-    <row r="157" spans="1:15" hidden="1">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <f>'Study Parameters'!A36</f>
         <v>Abanades et al. 2020</v>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="L157" s="30"/>
     </row>
-    <row r="158" spans="1:15" hidden="1">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <f>'Study Parameters'!A37</f>
         <v>Ragipani et al. 2022</v>
@@ -18186,7 +18186,7 @@
         <v>121.14570202833102</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>315</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>140.09669470231475</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -18270,7 +18270,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>329</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>329</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>295.30442580438057</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" t="str">
         <f>'Study Parameters'!A39</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18418,7 +18418,7 @@
         <v>147.49707212559986</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -18466,7 +18466,7 @@
         <v>147.49707212559986</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>329</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>147.49707212559986</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="str">
         <f>'Study Parameters'!A40</f>
         <v>Pett-Ridge et al. 2024</v>
@@ -18567,7 +18567,7 @@
         <v>440.01216847304312</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>329</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>339.04143355290654</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>329</v>
       </c>
@@ -18663,7 +18663,7 @@
         <v>263.41019772115243</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>163.71895198084354</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="str">
         <f>'Study Parameters'!A41</f>
         <v>NETL/Valentine 2022a</v>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="M170" s="30"/>
     </row>
-    <row r="171" spans="1:15" hidden="1">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="M171" s="30"/>
     </row>
-    <row r="172" spans="1:15" hidden="1">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>336</v>
       </c>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="M172" s="30"/>
     </row>
-    <row r="173" spans="1:15" hidden="1">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="str">
         <f>'Study Parameters'!A42</f>
         <v>NETL/Valentine 2022b</v>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="M173" s="30"/>
     </row>
-    <row r="174" spans="1:15" hidden="1">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="M174" s="30"/>
     </row>
-    <row r="175" spans="1:15" hidden="1">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>342</v>
       </c>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="M175" s="30"/>
     </row>
-    <row r="176" spans="1:15" hidden="1">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="str">
         <f>'Study Parameters'!A43</f>
         <v>NASEM 2019</v>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="L176" s="30"/>
     </row>
-    <row r="177" spans="1:13" hidden="1">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="L177" s="30"/>
     </row>
-    <row r="178" spans="1:13" hidden="1">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f>'Study Parameters'!A44</f>
         <v>NASEM 2019</v>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L178" s="30"/>
     </row>
-    <row r="179" spans="1:13" hidden="1">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f>'Study Parameters'!A45</f>
         <v>APS 2011</v>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="M179" s="30"/>
     </row>
-    <row r="180" spans="1:13" hidden="1">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>348</v>
       </c>
@@ -19149,14 +19149,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C0257C-D407-4235-8443-42A5A3A9A73A}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="63" t="s">
         <v>751</v>
       </c>
@@ -19166,7 +19166,7 @@
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>753</v>
       </c>
@@ -19176,7 +19176,7 @@
       <c r="J2" s="74"/>
       <c r="K2" s="74"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="64"/>
       <c r="F3" s="74" t="s">
         <v>755</v>
@@ -19184,7 +19184,7 @@
       <c r="J3" s="74"/>
       <c r="K3" s="74"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>756</v>
       </c>
@@ -19200,7 +19200,7 @@
       <c r="J4" s="74"/>
       <c r="K4" s="74"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>760</v>
       </c>
@@ -19216,7 +19216,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="74"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>764</v>
       </c>
@@ -19229,7 +19229,7 @@
       <c r="J6" s="74"/>
       <c r="K6" s="74"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>766</v>
       </c>
@@ -19239,7 +19239,7 @@
       <c r="J7" s="74"/>
       <c r="K7" s="74"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>767</v>
       </c>
@@ -19249,7 +19249,7 @@
       <c r="J8" s="74"/>
       <c r="K8" s="74"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>768</v>
       </c>
@@ -19259,7 +19259,7 @@
       <c r="J9" s="74"/>
       <c r="K9" s="74"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>769</v>
       </c>
@@ -19269,7 +19269,7 @@
       <c r="J10" s="74"/>
       <c r="K10" s="74"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>770</v>
       </c>
@@ -19279,7 +19279,7 @@
       <c r="J11" s="74"/>
       <c r="K11" s="74"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>771</v>
       </c>
@@ -19289,7 +19289,7 @@
       <c r="J12" s="76"/>
       <c r="K12" s="77"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>772</v>
       </c>
@@ -19299,7 +19299,7 @@
       <c r="J13" s="76"/>
       <c r="K13" s="75"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>773</v>
       </c>
@@ -19309,7 +19309,7 @@
       <c r="J14" s="76"/>
       <c r="K14" s="77"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>774</v>
       </c>
@@ -19319,7 +19319,7 @@
       <c r="J15" s="76"/>
       <c r="K15" s="77"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>775</v>
       </c>
@@ -19329,7 +19329,7 @@
       <c r="J16" s="76"/>
       <c r="K16" s="77"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>776</v>
       </c>
@@ -19339,7 +19339,7 @@
       <c r="J17" s="76"/>
       <c r="K17" s="77"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>777</v>
       </c>
@@ -19349,7 +19349,7 @@
       <c r="J18" s="76"/>
       <c r="K18" s="77"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>778</v>
       </c>
@@ -19359,7 +19359,7 @@
       <c r="J19" s="76"/>
       <c r="K19" s="74"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>779</v>
       </c>
@@ -19369,7 +19369,7 @@
       <c r="J20" s="76"/>
       <c r="K20" s="77"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>780</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="J21" s="76"/>
       <c r="K21" s="77"/>
     </row>
-    <row r="22" spans="1:11" ht="16.149999999999999" thickBot="1">
+    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>96</v>
       </c>
@@ -19390,7 +19390,7 @@
       <c r="J22" s="76"/>
       <c r="K22" s="77"/>
     </row>
-    <row r="23" spans="1:11" ht="18.600000000000001" thickBot="1">
+    <row r="23" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="85" t="s">
         <v>80</v>
       </c>
@@ -19421,7 +19421,7 @@
       <c r="J23" s="76"/>
       <c r="K23" s="77"/>
     </row>
-    <row r="24" spans="1:11" ht="16.149999999999999" thickBot="1">
+    <row r="24" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="78" t="s">
         <v>782</v>
       </c>
@@ -19452,14 +19452,14 @@
       <c r="J24" s="76"/>
       <c r="K24" s="77"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="86" t="s">
         <v>784</v>
       </c>
       <c r="J25" s="76"/>
       <c r="K25" s="77"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>785</v>
       </c>
@@ -19473,7 +19473,7 @@
       <c r="J26" s="76"/>
       <c r="K26" s="77"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -19496,52 +19496,52 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56965C59-6106-408A-A712-D0B6552D4011}">
   <dimension ref="A1:B211"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
         <v>752</v>
       </c>
       <c r="B1" s="74"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
         <v>754</v>
       </c>
       <c r="B2" s="74"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
         <v>755</v>
       </c>
       <c r="B3" s="74"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
         <v>759</v>
       </c>
       <c r="B4" s="74"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="74" t="s">
         <v>763</v>
       </c>
       <c r="B5" s="74"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
         <v>765</v>
       </c>
       <c r="B6" s="74"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="74"/>
       <c r="B7" s="74"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
         <v>788</v>
       </c>
@@ -19549,17 +19549,17 @@
         <v>789</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="74"/>
       <c r="B9" s="74"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="74" t="s">
         <v>790</v>
       </c>
       <c r="B10" s="74"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>791</v>
       </c>
@@ -19567,7 +19567,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="76">
         <v>39448</v>
       </c>
@@ -19575,7 +19575,7 @@
         <v>1.4728000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="76">
         <v>39479</v>
       </c>
@@ -19583,7 +19583,7 @@
         <v>1.4759</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="76">
         <v>39508</v>
       </c>
@@ -19591,7 +19591,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="76">
         <v>39539</v>
       </c>
@@ -19599,7 +19599,7 @@
         <v>1.5753999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="76">
         <v>39569</v>
       </c>
@@ -19607,7 +19607,7 @@
         <v>1.5553999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="76">
         <v>39600</v>
       </c>
@@ -19615,7 +19615,7 @@
         <v>1.5562</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="76">
         <v>39630</v>
       </c>
@@ -19623,7 +19623,7 @@
         <v>1.5759000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="76">
         <v>39661</v>
       </c>
@@ -19631,7 +19631,7 @@
         <v>1.4955000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="76">
         <v>39692</v>
       </c>
@@ -19639,7 +19639,7 @@
         <v>1.4341999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="76">
         <v>39722</v>
       </c>
@@ -19647,7 +19647,7 @@
         <v>1.3266</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="76">
         <v>39753</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>1.2744</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="76">
         <v>39783</v>
       </c>
@@ -19663,7 +19663,7 @@
         <v>1.3511</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="76">
         <v>39814</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>1.3244</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="76">
         <v>39845</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>1.2797000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="76">
         <v>39873</v>
       </c>
@@ -19687,7 +19687,7 @@
         <v>1.3049999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="76">
         <v>39904</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>1.3199000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="76">
         <v>39934</v>
       </c>
@@ -19703,7 +19703,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="76">
         <v>39965</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>1.4014</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="76">
         <v>39995</v>
       </c>
@@ -19719,7 +19719,7 @@
         <v>1.4092</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="76">
         <v>40026</v>
       </c>
@@ -19727,7 +19727,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="76">
         <v>40057</v>
       </c>
@@ -19735,7 +19735,7 @@
         <v>1.4575</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="76">
         <v>40087</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>1.4821</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="76">
         <v>40118</v>
       </c>
@@ -19751,7 +19751,7 @@
         <v>1.4907999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="76">
         <v>40148</v>
       </c>
@@ -19759,7 +19759,7 @@
         <v>1.4579</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="76">
         <v>40179</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>1.4266000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="76">
         <v>40210</v>
       </c>
@@ -19775,7 +19775,7 @@
         <v>1.3680000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="76">
         <v>40238</v>
       </c>
@@ -19783,7 +19783,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="76">
         <v>40269</v>
       </c>
@@ -19791,7 +19791,7 @@
         <v>1.3416999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="76">
         <v>40299</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>1.2563</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="76">
         <v>40330</v>
       </c>
@@ -19807,7 +19807,7 @@
         <v>1.2222999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="76">
         <v>40360</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>1.2810999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="76">
         <v>40391</v>
       </c>
@@ -19823,7 +19823,7 @@
         <v>1.2903</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="76">
         <v>40422</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>1.3103</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="76">
         <v>40452</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>1.3900999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="76">
         <v>40483</v>
       </c>
@@ -19847,7 +19847,7 @@
         <v>1.3653999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="76">
         <v>40513</v>
       </c>
@@ -19855,7 +19855,7 @@
         <v>1.3221000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="76">
         <v>40544</v>
       </c>
@@ -19863,7 +19863,7 @@
         <v>1.3371</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="76">
         <v>40575</v>
       </c>
@@ -19871,7 +19871,7 @@
         <v>1.3655999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="76">
         <v>40603</v>
       </c>
@@ -19879,7 +19879,7 @@
         <v>1.4019999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="76">
         <v>40634</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>1.446</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="76">
         <v>40664</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>1.4335</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="76">
         <v>40695</v>
       </c>
@@ -19903,7 +19903,7 @@
         <v>1.4402999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="76">
         <v>40725</v>
       </c>
@@ -19911,7 +19911,7 @@
         <v>1.4275</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="76">
         <v>40756</v>
       </c>
@@ -19919,7 +19919,7 @@
         <v>1.4333</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="76">
         <v>40787</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>1.3747</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="76">
         <v>40817</v>
       </c>
@@ -19935,7 +19935,7 @@
         <v>1.3732</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="76">
         <v>40848</v>
       </c>
@@ -19943,7 +19943,7 @@
         <v>1.3557999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="76">
         <v>40878</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>1.3154999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="76">
         <v>40909</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>1.2909999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="76">
         <v>40940</v>
       </c>
@@ -19967,7 +19967,7 @@
         <v>1.3238000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="76">
         <v>40969</v>
       </c>
@@ -19975,7 +19975,7 @@
         <v>1.3208</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="76">
         <v>41000</v>
       </c>
@@ -19983,7 +19983,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="76">
         <v>41030</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>1.2806</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="76">
         <v>41061</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>1.2541</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="76">
         <v>41091</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>1.2278</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="76">
         <v>41122</v>
       </c>
@@ -20015,7 +20015,7 @@
         <v>1.2405999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="76">
         <v>41153</v>
       </c>
@@ -20023,7 +20023,7 @@
         <v>1.2885</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="76">
         <v>41183</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>1.2974000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="76">
         <v>41214</v>
       </c>
@@ -20039,7 +20039,7 @@
         <v>1.2837000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="76">
         <v>41244</v>
       </c>
@@ -20047,7 +20047,7 @@
         <v>1.3119000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="76">
         <v>41275</v>
       </c>
@@ -20055,7 +20055,7 @@
         <v>1.3304</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="76">
         <v>41306</v>
       </c>
@@ -20063,7 +20063,7 @@
         <v>1.3347</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="76">
         <v>41334</v>
       </c>
@@ -20071,7 +20071,7 @@
         <v>1.2952999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="76">
         <v>41365</v>
       </c>
@@ -20079,7 +20079,7 @@
         <v>1.3025</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="76">
         <v>41395</v>
       </c>
@@ -20087,7 +20087,7 @@
         <v>1.2983</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="76">
         <v>41426</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>1.3197000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="76">
         <v>41456</v>
       </c>
@@ -20103,7 +20103,7 @@
         <v>1.3088</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="76">
         <v>41487</v>
       </c>
@@ -20111,7 +20111,7 @@
         <v>1.3313999999999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="76">
         <v>41518</v>
       </c>
@@ -20119,7 +20119,7 @@
         <v>1.3364</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="76">
         <v>41548</v>
       </c>
@@ -20127,7 +20127,7 @@
         <v>1.3646</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="76">
         <v>41579</v>
       </c>
@@ -20135,7 +20135,7 @@
         <v>1.3491</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="76">
         <v>41609</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>1.3708</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="76">
         <v>41640</v>
       </c>
@@ -20151,7 +20151,7 @@
         <v>1.3617999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="76">
         <v>41671</v>
       </c>
@@ -20159,7 +20159,7 @@
         <v>1.3665</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="76">
         <v>41699</v>
       </c>
@@ -20167,7 +20167,7 @@
         <v>1.3828</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="76">
         <v>41730</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>1.381</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="76">
         <v>41760</v>
       </c>
@@ -20183,7 +20183,7 @@
         <v>1.3738999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="76">
         <v>41791</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>1.3594999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="76">
         <v>41821</v>
       </c>
@@ -20199,7 +20199,7 @@
         <v>1.3532999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="76">
         <v>41852</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>1.3314999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="76">
         <v>41883</v>
       </c>
@@ -20215,7 +20215,7 @@
         <v>1.2888999999999999</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="76">
         <v>41913</v>
       </c>
@@ -20223,7 +20223,7 @@
         <v>1.2677</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="76">
         <v>41944</v>
       </c>
@@ -20231,7 +20231,7 @@
         <v>1.2473000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="76">
         <v>41974</v>
       </c>
@@ -20239,7 +20239,7 @@
         <v>1.2329000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="76">
         <v>42005</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>1.1615</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="76">
         <v>42036</v>
       </c>
@@ -20255,7 +20255,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="76">
         <v>42064</v>
       </c>
@@ -20263,7 +20263,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="76">
         <v>42095</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>1.0822000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="76">
         <v>42125</v>
       </c>
@@ -20279,7 +20279,7 @@
         <v>1.1167</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="76">
         <v>42156</v>
       </c>
@@ -20287,7 +20287,7 @@
         <v>1.1226</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="76">
         <v>42186</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>1.0996999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="76">
         <v>42217</v>
       </c>
@@ -20303,7 +20303,7 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="76">
         <v>42248</v>
       </c>
@@ -20311,7 +20311,7 @@
         <v>1.1229</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="76">
         <v>42278</v>
       </c>
@@ -20319,7 +20319,7 @@
         <v>1.1228</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="76">
         <v>42309</v>
       </c>
@@ -20327,7 +20327,7 @@
         <v>1.0727</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="76">
         <v>42339</v>
       </c>
@@ -20335,7 +20335,7 @@
         <v>1.0889</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="76">
         <v>42370</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>1.0854999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="76">
         <v>42401</v>
       </c>
@@ -20351,7 +20351,7 @@
         <v>1.1092</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="76">
         <v>42430</v>
       </c>
@@ -20359,7 +20359,7 @@
         <v>1.1133999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="76">
         <v>42461</v>
       </c>
@@ -20367,7 +20367,7 @@
         <v>1.1346000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="76">
         <v>42491</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>1.1312</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="76">
         <v>42522</v>
       </c>
@@ -20383,7 +20383,7 @@
         <v>1.1232</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="76">
         <v>42552</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>1.1054999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="76">
         <v>42583</v>
       </c>
@@ -20399,7 +20399,7 @@
         <v>1.1207</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="76">
         <v>42614</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>1.1217999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="76">
         <v>42644</v>
       </c>
@@ -20415,7 +20415,7 @@
         <v>1.1013999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="76">
         <v>42675</v>
       </c>
@@ -20423,7 +20423,7 @@
         <v>1.0791999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="76">
         <v>42705</v>
       </c>
@@ -20431,7 +20431,7 @@
         <v>1.0545</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="76">
         <v>42736</v>
       </c>
@@ -20439,7 +20439,7 @@
         <v>1.0634999999999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="76">
         <v>42767</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="76">
         <v>42795</v>
       </c>
@@ -20455,7 +20455,7 @@
         <v>1.0690999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="76">
         <v>42826</v>
       </c>
@@ -20463,7 +20463,7 @@
         <v>1.0713999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="76">
         <v>42856</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>1.105</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="76">
         <v>42887</v>
       </c>
@@ -20479,7 +20479,7 @@
         <v>1.1233</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="76">
         <v>42917</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>1.153</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="76">
         <v>42948</v>
       </c>
@@ -20495,7 +20495,7 @@
         <v>1.1813</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="76">
         <v>42979</v>
       </c>
@@ -20503,7 +20503,7 @@
         <v>1.1913</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="76">
         <v>43009</v>
       </c>
@@ -20511,7 +20511,7 @@
         <v>1.1755</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="76">
         <v>43040</v>
       </c>
@@ -20519,7 +20519,7 @@
         <v>1.1742999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="76">
         <v>43070</v>
       </c>
@@ -20527,7 +20527,7 @@
         <v>1.1836</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="76">
         <v>43101</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>1.2197</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="76">
         <v>43132</v>
       </c>
@@ -20543,7 +20543,7 @@
         <v>1.234</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="76">
         <v>43160</v>
       </c>
@@ -20551,7 +20551,7 @@
         <v>1.2334000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="76">
         <v>43191</v>
       </c>
@@ -20559,7 +20559,7 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="76">
         <v>43221</v>
       </c>
@@ -20567,7 +20567,7 @@
         <v>1.1822999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="76">
         <v>43252</v>
       </c>
@@ -20575,7 +20575,7 @@
         <v>1.1678999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="76">
         <v>43282</v>
       </c>
@@ -20583,7 +20583,7 @@
         <v>1.1685000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="76">
         <v>43313</v>
       </c>
@@ -20591,7 +20591,7 @@
         <v>1.1547000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="76">
         <v>43344</v>
       </c>
@@ -20599,7 +20599,7 @@
         <v>1.1667000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="76">
         <v>43374</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="76">
         <v>43405</v>
       </c>
@@ -20615,7 +20615,7 @@
         <v>1.1364000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="76">
         <v>43435</v>
       </c>
@@ -20623,7 +20623,7 @@
         <v>1.1379999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="76">
         <v>43466</v>
       </c>
@@ -20631,7 +20631,7 @@
         <v>1.1417999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="76">
         <v>43497</v>
       </c>
@@ -20639,7 +20639,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="76">
         <v>43525</v>
       </c>
@@ -20647,7 +20647,7 @@
         <v>1.1295999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="76">
         <v>43556</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>1.1234</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="76">
         <v>43586</v>
       </c>
@@ -20663,7 +20663,7 @@
         <v>1.1187</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="76">
         <v>43617</v>
       </c>
@@ -20671,7 +20671,7 @@
         <v>1.1294999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="76">
         <v>43647</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>1.1211</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="76">
         <v>43678</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>1.1129</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="76">
         <v>43709</v>
       </c>
@@ -20695,7 +20695,7 @@
         <v>1.1011</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="76">
         <v>43739</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>1.1057999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="76">
         <v>43770</v>
       </c>
@@ -20711,7 +20711,7 @@
         <v>1.1051</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="76">
         <v>43800</v>
       </c>
@@ -20719,7 +20719,7 @@
         <v>1.1113999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="76">
         <v>43831</v>
       </c>
@@ -20727,7 +20727,7 @@
         <v>1.1097999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="76">
         <v>43862</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>1.0911</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="76">
         <v>43891</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>1.1046</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="76">
         <v>43922</v>
       </c>
@@ -20751,7 +20751,7 @@
         <v>1.0871</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="76">
         <v>43952</v>
       </c>
@@ -20759,7 +20759,7 @@
         <v>1.0907</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="76">
         <v>43983</v>
       </c>
@@ -20767,7 +20767,7 @@
         <v>1.1258999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="76">
         <v>44013</v>
       </c>
@@ -20775,7 +20775,7 @@
         <v>1.1488</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="76">
         <v>44044</v>
       </c>
@@ -20783,7 +20783,7 @@
         <v>1.1831</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="76">
         <v>44075</v>
       </c>
@@ -20791,7 +20791,7 @@
         <v>1.1785000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="76">
         <v>44105</v>
       </c>
@@ -20799,7 +20799,7 @@
         <v>1.1768000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="76">
         <v>44136</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>1.1826000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="76">
         <v>44166</v>
       </c>
@@ -20815,7 +20815,7 @@
         <v>1.2168000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="76">
         <v>44197</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>1.2178</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="76">
         <v>44228</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>1.2094</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="76">
         <v>44256</v>
       </c>
@@ -20839,7 +20839,7 @@
         <v>1.1901999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="76">
         <v>44287</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>1.1964999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="76">
         <v>44317</v>
       </c>
@@ -20855,7 +20855,7 @@
         <v>1.2145999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="76">
         <v>44348</v>
       </c>
@@ -20863,7 +20863,7 @@
         <v>1.2048000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="76">
         <v>44378</v>
       </c>
@@ -20871,7 +20871,7 @@
         <v>1.1820999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="76">
         <v>44409</v>
       </c>
@@ -20879,7 +20879,7 @@
         <v>1.1767000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="76">
         <v>44440</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>1.1765000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="76">
         <v>44470</v>
       </c>
@@ -20895,7 +20895,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="76">
         <v>44501</v>
       </c>
@@ -20903,7 +20903,7 @@
         <v>1.1415999999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="76">
         <v>44531</v>
       </c>
@@ -20911,7 +20911,7 @@
         <v>1.1301000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="76">
         <v>44562</v>
       </c>
@@ -20919,7 +20919,7 @@
         <v>1.1316999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="76">
         <v>44593</v>
       </c>
@@ -20927,7 +20927,7 @@
         <v>1.1349</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="76">
         <v>44621</v>
       </c>
@@ -20935,7 +20935,7 @@
         <v>1.1019000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="76">
         <v>44652</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>1.0803</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="76">
         <v>44682</v>
       </c>
@@ -20951,7 +20951,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="76">
         <v>44713</v>
       </c>
@@ -20959,7 +20959,7 @@
         <v>1.0567</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="76">
         <v>44743</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>1.0167999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="76">
         <v>44774</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>1.0128999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="76">
         <v>44805</v>
       </c>
@@ -20983,7 +20983,7 @@
         <v>0.9899</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="76">
         <v>44835</v>
       </c>
@@ -20991,7 +20991,7 @@
         <v>0.98529999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="76">
         <v>44866</v>
       </c>
@@ -20999,7 +20999,7 @@
         <v>1.0192000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="76">
         <v>44896</v>
       </c>
@@ -21007,7 +21007,7 @@
         <v>1.0590999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="76">
         <v>44927</v>
       </c>
@@ -21015,7 +21015,7 @@
         <v>1.0777000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="76">
         <v>44958</v>
       </c>
@@ -21023,7 +21023,7 @@
         <v>1.0702</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="76">
         <v>44986</v>
       </c>
@@ -21031,7 +21031,7 @@
         <v>1.0710999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="76">
         <v>45017</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>1.0962000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="76">
         <v>45047</v>
       </c>
@@ -21047,7 +21047,7 @@
         <v>1.0867</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="76">
         <v>45078</v>
       </c>
@@ -21055,7 +21055,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="76">
         <v>45108</v>
       </c>
@@ -21063,7 +21063,7 @@
         <v>1.1067</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="76">
         <v>45139</v>
       </c>
@@ -21071,7 +21071,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="76">
         <v>45170</v>
       </c>
@@ -21079,7 +21079,7 @@
         <v>1.0671999999999999</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="76">
         <v>45200</v>
       </c>
@@ -21087,7 +21087,7 @@
         <v>1.0565</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="76">
         <v>45231</v>
       </c>
@@ -21095,7 +21095,7 @@
         <v>1.0819000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="76">
         <v>45261</v>
       </c>
@@ -21103,7 +21103,7 @@
         <v>1.0909</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="76">
         <v>45292</v>
       </c>
@@ -21111,7 +21111,7 @@
         <v>1.0899000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="76">
         <v>45323</v>
       </c>
@@ -21119,7 +21119,7 @@
         <v>1.0792999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="76">
         <v>45352</v>
       </c>
@@ -21127,7 +21127,7 @@
         <v>1.087</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="76">
         <v>45383</v>
       </c>
@@ -21135,7 +21135,7 @@
         <v>1.0724</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="76">
         <v>45413</v>
       </c>
@@ -21143,7 +21143,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="76">
         <v>45444</v>
       </c>
@@ -21151,7 +21151,7 @@
         <v>1.0763</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="76">
         <v>45474</v>
       </c>
@@ -21159,7 +21159,7 @@
         <v>1.0847</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="76">
         <v>45505</v>
       </c>
@@ -21176,7 +21176,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21188,7 +21188,7 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
@@ -21196,7 +21196,7 @@
     <col min="4" max="4" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -21210,7 +21210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -21224,12 +21224,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="8" customFormat="1">
+    <row r="3" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -21246,7 +21246,7 @@
         <v>2.453282945060923E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -21254,7 +21254,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -21263,12 +21263,12 @@
         <v>0.81870109796004231</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="8" customFormat="1">
+    <row r="8" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>15</v>
       </c>
@@ -21286,7 +21286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
         <v>15</v>
       </c>
@@ -21303,7 +21303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="105" t="s">
         <v>19</v>
       </c>
@@ -21320,7 +21320,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="105" t="s">
         <v>19</v>
       </c>
@@ -21337,7 +21337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="105" t="s">
         <v>19</v>
       </c>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="E13" s="94"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="105" t="s">
         <v>19</v>
       </c>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E14" s="94"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="105" t="s">
         <v>22</v>
       </c>
@@ -21386,7 +21386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="105" t="s">
         <v>22</v>
       </c>
@@ -21403,7 +21403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="105" t="s">
         <v>22</v>
       </c>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="E17" s="94"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="105" t="s">
         <v>22</v>
       </c>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="E18" s="94"/>
     </row>
-    <row r="19" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="19" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="94" t="s">
         <v>23</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="20" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="94" t="s">
         <v>25</v>
       </c>
@@ -21463,7 +21463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="94" customFormat="1" ht="14.45">
+    <row r="21" spans="1:5" s="94" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="94" t="s">
         <v>26</v>
       </c>
@@ -21478,12 +21478,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="8" customFormat="1">
+    <row r="22" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -21500,7 +21500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -21517,12 +21517,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="8" customFormat="1">
+    <row r="25" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>32</v>
       </c>
@@ -21539,7 +21539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>32</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="108" customFormat="1" ht="14.45">
+    <row r="29" spans="1:5" s="108" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="108" t="s">
         <v>33</v>
       </c>
@@ -21584,7 +21584,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
     <col min="2" max="2" width="20.125" customWidth="1"/>
@@ -21594,7 +21594,7 @@
     <col min="37" max="37" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>35</v>
       </c>
@@ -21710,7 +21710,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>43</v>
       </c>
@@ -21827,7 +21827,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
         <v>51</v>
       </c>
@@ -21934,7 +21934,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>53</v>
       </c>
@@ -22041,7 +22041,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
         <v>55</v>
       </c>
@@ -22148,7 +22148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
         <v>56</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="40" t="s">
         <v>57</v>
       </c>
@@ -22362,7 +22362,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
         <v>58</v>
       </c>
@@ -22469,7 +22469,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="s">
         <v>59</v>
       </c>
@@ -22576,7 +22576,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>60</v>
       </c>
@@ -22683,7 +22683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
         <v>61</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>62</v>
       </c>
@@ -22897,7 +22897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:38">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>63</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:38">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>43</v>
       </c>
@@ -23121,7 +23121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:38">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="40" t="s">
         <v>64</v>
       </c>
@@ -23228,7 +23228,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:38">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>65</v>
       </c>
@@ -23335,7 +23335,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:38">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
         <v>66</v>
       </c>
@@ -23442,7 +23442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:38">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
         <v>67</v>
       </c>
@@ -23549,7 +23549,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:38">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
         <v>68</v>
       </c>
@@ -23666,7 +23666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
         <v>51</v>
       </c>
@@ -23773,7 +23773,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
         <v>53</v>
       </c>
@@ -23880,7 +23880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>55</v>
       </c>
@@ -23987,7 +23987,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="40" t="s">
         <v>56</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:38">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
         <v>57</v>
       </c>
@@ -24201,7 +24201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="40" t="s">
         <v>58</v>
       </c>
@@ -24308,7 +24308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:38">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
         <v>59</v>
       </c>
@@ -24415,7 +24415,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:38">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
         <v>60</v>
       </c>
@@ -24522,7 +24522,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:38">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="40" t="s">
         <v>61</v>
       </c>
@@ -24629,7 +24629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:38">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="40" t="s">
         <v>62</v>
       </c>
@@ -24736,7 +24736,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:38">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="40" t="s">
         <v>63</v>
       </c>
@@ -24843,7 +24843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="2" customFormat="1">
+    <row r="31" spans="1:38" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>43</v>
       </c>
@@ -24960,7 +24960,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>64</v>
       </c>
@@ -25067,7 +25067,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
         <v>65</v>
       </c>
@@ -25174,7 +25174,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="40" t="s">
         <v>66</v>
       </c>
@@ -25281,7 +25281,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="40" t="s">
         <v>67</v>
       </c>
@@ -25388,7 +25388,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
         <v>68</v>
       </c>
@@ -25505,7 +25505,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="40" t="s">
         <v>72</v>
       </c>
@@ -25532,7 +25532,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="40" t="s">
         <v>72</v>
       </c>
@@ -25556,7 +25556,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="40" t="s">
         <v>75</v>
       </c>
@@ -25589,7 +25589,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>75</v>
       </c>
@@ -25610,14 +25610,14 @@
         <v>1.89E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="AI42"/>
       <c r="AJ42"/>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="97"/>
       <c r="B43" s="98" t="s">
         <v>80</v>
@@ -25643,7 +25643,7 @@
       <c r="AI43"/>
       <c r="AJ43"/>
     </row>
-    <row r="44" spans="1:40" s="1" customFormat="1">
+    <row r="44" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="99" t="s">
         <v>87</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="97"/>
       <c r="B45" s="100" t="s">
         <v>88</v>
@@ -25701,7 +25701,7 @@
       <c r="AI45"/>
       <c r="AJ45"/>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="97"/>
       <c r="B46" s="100" t="s">
         <v>88</v>
@@ -25730,7 +25730,7 @@
       <c r="AI46"/>
       <c r="AJ46"/>
     </row>
-    <row r="47" spans="1:40" s="1" customFormat="1">
+    <row r="47" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="99" t="s">
         <v>94</v>
       </c>
@@ -25761,44 +25761,44 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
       <c r="AI48"/>
       <c r="AJ48"/>
     </row>
-    <row r="49" spans="1:36">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>99</v>
       </c>
       <c r="AI49"/>
       <c r="AJ49"/>
     </row>
-    <row r="50" spans="1:36">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>100</v>
       </c>
       <c r="AI50"/>
       <c r="AJ50"/>
     </row>
-    <row r="51" spans="1:36">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI51"/>
       <c r="AJ51"/>
     </row>
-    <row r="52" spans="1:36">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI52"/>
       <c r="AJ52"/>
     </row>
-    <row r="53" spans="1:36">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI53"/>
       <c r="AJ53"/>
     </row>
-    <row r="54" spans="1:36">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI54"/>
       <c r="AJ54"/>
     </row>
-    <row r="55" spans="1:36">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="AI55"/>
       <c r="AJ55"/>
     </row>
@@ -25820,7 +25820,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="10"/>
     <col min="2" max="2" width="69.625" style="10" bestFit="1" customWidth="1"/>
@@ -25830,7 +25830,7 @@
     <col min="6" max="16384" width="10.625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -25876,7 +25876,7 @@
       <c r="AQ1" s="9"/>
       <c r="AR1" s="9"/>
     </row>
-    <row r="2" spans="1:44" ht="20.45" thickBot="1">
+    <row r="2" spans="1:44" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="11" t="s">
         <v>101</v>
@@ -25924,7 +25924,7 @@
       <c r="AQ2" s="9"/>
       <c r="AR2" s="9"/>
     </row>
-    <row r="3" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="3" spans="1:44" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -25970,7 +25970,7 @@
       <c r="AQ3" s="9"/>
       <c r="AR3" s="9"/>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>102</v>
@@ -26020,7 +26020,7 @@
       <c r="AQ4" s="9"/>
       <c r="AR4" s="9"/>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>6</v>
@@ -26128,7 +26128,7 @@
       <c r="AQ5" s="15"/>
       <c r="AR5" s="15"/>
     </row>
-    <row r="6" spans="1:44">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="16" t="s">
         <v>105</v>
@@ -26234,7 +26234,7 @@
       <c r="AQ6" s="19"/>
       <c r="AR6" s="19"/>
     </row>
-    <row r="7" spans="1:44">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="20" t="s">
         <v>106</v>
@@ -26340,7 +26340,7 @@
       <c r="AQ7" s="24"/>
       <c r="AR7" s="24"/>
     </row>
-    <row r="8" spans="1:44">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="25"/>
@@ -26386,7 +26386,7 @@
       <c r="AQ8" s="25"/>
       <c r="AR8" s="25"/>
     </row>
-    <row r="9" spans="1:44">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="12" t="s">
         <v>107</v>
@@ -26434,7 +26434,7 @@
       <c r="AQ9" s="25"/>
       <c r="AR9" s="25"/>
     </row>
-    <row r="10" spans="1:44">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="12" t="s">
         <v>108</v>
@@ -26482,7 +26482,7 @@
       <c r="AQ10" s="25"/>
       <c r="AR10" s="25"/>
     </row>
-    <row r="11" spans="1:44">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12" t="s">
         <v>109</v>
@@ -26588,7 +26588,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
     </row>
-    <row r="12" spans="1:44">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12" t="s">
         <v>110</v>
@@ -26636,7 +26636,7 @@
       <c r="AQ12" s="25"/>
       <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:44">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="12" t="s">
         <v>109</v>
@@ -26742,7 +26742,7 @@
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
     </row>
-    <row r="14" spans="1:44">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="12" t="s">
         <v>111</v>
@@ -26790,7 +26790,7 @@
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
     </row>
-    <row r="15" spans="1:44">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="12" t="s">
         <v>109</v>
@@ -26896,7 +26896,7 @@
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
     </row>
-    <row r="16" spans="1:44">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="25"/>
@@ -26942,7 +26942,7 @@
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
     </row>
-    <row r="17" spans="1:44">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -26988,7 +26988,7 @@
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
     </row>
-    <row r="18" spans="1:44" ht="20.45" thickBot="1">
+    <row r="18" spans="1:44" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="11" t="s">
         <v>112</v>
@@ -27036,7 +27036,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
     </row>
-    <row r="19" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="19" spans="1:44" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -27082,7 +27082,7 @@
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
     </row>
-    <row r="20" spans="1:44">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -27129,7 +27129,7 @@
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
     </row>
-    <row r="21" spans="1:44">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
         <v>112</v>
@@ -27180,7 +27180,7 @@
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
     </row>
-    <row r="22" spans="1:44">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -27226,7 +27226,7 @@
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
     </row>
-    <row r="23" spans="1:44">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -27272,7 +27272,7 @@
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
     </row>
-    <row r="24" spans="1:44">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -27314,7 +27314,7 @@
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
     </row>
-    <row r="25" spans="1:44">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -27360,7 +27360,7 @@
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
     </row>
-    <row r="26" spans="1:44">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -27406,7 +27406,7 @@
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
     </row>
-    <row r="27" spans="1:44">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -27460,20 +27460,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="144" t="s">
         <v>114</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -27481,7 +27481,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>406</v>
       </c>
@@ -27489,7 +27489,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>358</v>
       </c>
@@ -27497,7 +27497,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -27509,13 +27509,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="144" t="s">
         <v>119</v>
       </c>
       <c r="B9" s="144"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -27523,7 +27523,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -27537,7 +27537,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>121</v>
       </c>
@@ -27548,13 +27548,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="144" t="s">
         <v>122</v>
       </c>
       <c r="B14" s="144"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -27562,7 +27562,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -27601,13 +27601,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -27626,7 +27626,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA419E9D-493B-4DCE-A933-2A9A9AF40246}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" outlineLevelCol="2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.125" customWidth="1" outlineLevel="1"/>
@@ -27650,7 +27650,7 @@
     <col min="24" max="30" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -27734,7 +27734,7 @@
       <c r="AC1" s="82"/>
       <c r="AD1" s="82"/>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>150</v>
       </c>
@@ -27790,7 +27790,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -27846,7 +27846,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>150</v>
       </c>
@@ -27900,7 +27900,7 @@
       </c>
       <c r="W4" s="60"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -27954,7 +27954,7 @@
       </c>
       <c r="W5" s="60"/>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -28008,7 +28008,7 @@
       </c>
       <c r="W6" s="60"/>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>150</v>
       </c>
@@ -28062,7 +28062,7 @@
       </c>
       <c r="W7" s="60"/>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -28116,7 +28116,7 @@
       </c>
       <c r="W8" s="60"/>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -28170,7 +28170,7 @@
       </c>
       <c r="W9" s="60"/>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="W10" s="60"/>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -28278,7 +28278,7 @@
       </c>
       <c r="W11" s="60"/>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -28332,7 +28332,7 @@
       </c>
       <c r="W12" s="60"/>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>150</v>
       </c>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="W13" s="60"/>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -28440,7 +28440,7 @@
       </c>
       <c r="W14" s="60"/>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -28494,7 +28494,7 @@
       </c>
       <c r="W15" s="60"/>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -28551,7 +28551,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>150</v>
       </c>
@@ -28608,7 +28608,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -28650,7 +28650,7 @@
       </c>
       <c r="W18" s="60"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>150</v>
       </c>
@@ -28692,7 +28692,7 @@
       </c>
       <c r="W19" s="60"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>150</v>
       </c>
@@ -28764,7 +28764,7 @@
       </c>
       <c r="W21" s="60"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -28800,7 +28800,7 @@
       </c>
       <c r="W22" s="60"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -28836,7 +28836,7 @@
       </c>
       <c r="W23" s="60"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -28878,7 +28878,7 @@
       </c>
       <c r="W24" s="60"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -28929,7 +28929,7 @@
       </c>
       <c r="W25" s="60"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -28965,7 +28965,7 @@
       </c>
       <c r="W26" s="60"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>150</v>
       </c>
@@ -29001,7 +29001,7 @@
       </c>
       <c r="W27" s="60"/>
     </row>
-    <row r="28" spans="1:26" s="48" customFormat="1">
+    <row r="28" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
         <v>150</v>
       </c>
@@ -29031,7 +29031,7 @@
       </c>
       <c r="W28" s="90"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -29067,7 +29067,7 @@
       </c>
       <c r="W29" s="60"/>
     </row>
-    <row r="30" spans="1:26" s="48" customFormat="1">
+    <row r="30" spans="1:26" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="48" t="s">
         <v>260</v>
       </c>
@@ -29100,7 +29100,7 @@
       </c>
       <c r="W30" s="90"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -29136,7 +29136,7 @@
       </c>
       <c r="W31" s="60"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="W32" s="60"/>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="W33" s="60"/>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -29244,7 +29244,7 @@
       </c>
       <c r="W34" s="60"/>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -29295,7 +29295,7 @@
       </c>
       <c r="W35" s="60"/>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -29331,7 +29331,7 @@
       </c>
       <c r="W36" s="60"/>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -29367,7 +29367,7 @@
       </c>
       <c r="W37" s="60"/>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -29403,7 +29403,7 @@
       </c>
       <c r="W38" s="60"/>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -29439,7 +29439,7 @@
       </c>
       <c r="W39" s="60"/>
     </row>
-    <row r="40" spans="1:23" s="48" customFormat="1">
+    <row r="40" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="48" t="s">
         <v>150</v>
       </c>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="W40" s="90"/>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -29505,7 +29505,7 @@
       </c>
       <c r="W41" s="60"/>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -29547,7 +29547,7 @@
       </c>
       <c r="W42" s="60"/>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -29580,7 +29580,7 @@
       </c>
       <c r="W43" s="60"/>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>150</v>
       </c>
@@ -29613,7 +29613,7 @@
       </c>
       <c r="W44" s="60"/>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="W45" s="60"/>
     </row>
-    <row r="46" spans="1:23" s="48" customFormat="1">
+    <row r="46" spans="1:23" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="48" t="s">
         <v>150</v>
       </c>
@@ -29673,7 +29673,7 @@
       </c>
       <c r="W46" s="90"/>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -29707,7 +29707,7 @@
       </c>
       <c r="W47" s="60"/>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>260</v>
       </c>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="W48" s="60"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -29789,7 +29789,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>150</v>
       </c>
@@ -29837,7 +29837,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -29885,7 +29885,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -29933,7 +29933,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -29975,7 +29975,7 @@
       </c>
       <c r="W53" s="60"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -30011,7 +30011,7 @@
       </c>
       <c r="W54" s="60"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>150</v>
       </c>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="W55" s="60"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>150</v>
       </c>
@@ -30083,7 +30083,7 @@
       </c>
       <c r="W56" s="60"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>150</v>
       </c>
@@ -30140,7 +30140,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99968075-C79E-496E-8470-A0201C505FA7}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AL54"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -30167,7 +30167,7 @@
     <col min="36" max="36" width="33.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="51" customFormat="1">
+    <row r="1" spans="1:38" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -30227,7 +30227,7 @@
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
     </row>
-    <row r="2" spans="1:38" s="117" customFormat="1">
+    <row r="2" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117" t="s">
         <v>151</v>
       </c>
@@ -30258,7 +30258,7 @@
       <c r="R2" s="118"/>
       <c r="AI2" s="119"/>
     </row>
-    <row r="3" spans="1:38" s="117" customFormat="1">
+    <row r="3" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="117" t="s">
         <v>151</v>
       </c>
@@ -30290,7 +30290,7 @@
       <c r="R3" s="118"/>
       <c r="AI3" s="119"/>
     </row>
-    <row r="4" spans="1:38" s="117" customFormat="1">
+    <row r="4" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="117" t="s">
         <v>151</v>
       </c>
@@ -30322,7 +30322,7 @@
       <c r="R4" s="118"/>
       <c r="AI4" s="119"/>
     </row>
-    <row r="5" spans="1:38" s="117" customFormat="1">
+    <row r="5" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="117" t="s">
         <v>151</v>
       </c>
@@ -30355,7 +30355,7 @@
       <c r="AD5" s="120"/>
       <c r="AI5" s="119"/>
     </row>
-    <row r="6" spans="1:38" s="117" customFormat="1">
+    <row r="6" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="117" t="s">
         <v>185</v>
       </c>
@@ -30386,7 +30386,7 @@
       </c>
       <c r="R6" s="121"/>
     </row>
-    <row r="7" spans="1:38" s="117" customFormat="1">
+    <row r="7" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="117" t="s">
         <v>185</v>
       </c>
@@ -30418,7 +30418,7 @@
       <c r="O7" s="122"/>
       <c r="R7" s="121"/>
     </row>
-    <row r="8" spans="1:38" s="117" customFormat="1">
+    <row r="8" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="117" t="s">
         <v>185</v>
       </c>
@@ -30450,7 +30450,7 @@
       <c r="R8" s="121"/>
       <c r="AD8" s="120"/>
     </row>
-    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="9" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -30485,7 +30485,7 @@
       <c r="W9" s="114"/>
       <c r="AF9" s="115"/>
     </row>
-    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="10" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>208</v>
       </c>
@@ -30522,7 +30522,7 @@
       <c r="R10" s="113"/>
       <c r="AI10" s="116"/>
     </row>
-    <row r="11" spans="1:38" s="117" customFormat="1">
+    <row r="11" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="117" t="s">
         <v>214</v>
       </c>
@@ -30553,7 +30553,7 @@
       <c r="R11" s="121"/>
       <c r="AI11" s="119"/>
     </row>
-    <row r="12" spans="1:38" s="117" customFormat="1">
+    <row r="12" spans="1:38" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="117" t="s">
         <v>214</v>
       </c>
@@ -30584,7 +30584,7 @@
       <c r="R12" s="121"/>
       <c r="AI12" s="119"/>
     </row>
-    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="13" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>223</v>
       </c>
@@ -30619,7 +30619,7 @@
       <c r="AA13" s="124"/>
       <c r="AB13" s="124"/>
     </row>
-    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="14" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>227</v>
       </c>
@@ -30656,7 +30656,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="15" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
@@ -30688,7 +30688,7 @@
       <c r="AI15" s="116"/>
       <c r="AL15" s="127"/>
     </row>
-    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1">
+    <row r="16" spans="1:38" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>230</v>
       </c>
@@ -30720,7 +30720,7 @@
       <c r="AI16" s="116"/>
       <c r="AL16" s="127"/>
     </row>
-    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="17" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>234</v>
       </c>
@@ -30751,7 +30751,7 @@
       <c r="R17" s="123"/>
       <c r="AI17" s="116"/>
     </row>
-    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1">
+    <row r="18" spans="1:36" s="128" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="128" t="s">
         <v>240</v>
       </c>
@@ -30779,7 +30779,7 @@
       <c r="R18" s="129"/>
       <c r="W18" s="130"/>
     </row>
-    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="19" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>247</v>
       </c>
@@ -30814,7 +30814,7 @@
       <c r="R19" s="123"/>
       <c r="X19" s="123"/>
     </row>
-    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="20" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>247</v>
       </c>
@@ -30846,7 +30846,7 @@
       <c r="R20" s="123"/>
       <c r="X20" s="123"/>
     </row>
-    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1">
+    <row r="21" spans="1:36" s="127" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="127" t="s">
         <v>251</v>
       </c>
@@ -30865,7 +30865,7 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="22" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>255</v>
       </c>
@@ -30907,7 +30907,7 @@
       <c r="AB22" s="124"/>
       <c r="AF22" s="115"/>
     </row>
-    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="23" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>267</v>
       </c>
@@ -30941,7 +30941,7 @@
       <c r="X23" s="123"/>
       <c r="AI23" s="116"/>
     </row>
-    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="24" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
@@ -30975,7 +30975,7 @@
       <c r="X24" s="123"/>
       <c r="AI24" s="116"/>
     </row>
-    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1">
+    <row r="25" spans="1:36" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
         <v>271</v>
       </c>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="AI25" s="93"/>
     </row>
-    <row r="26" spans="1:36" s="117" customFormat="1">
+    <row r="26" spans="1:36" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="117" t="s">
         <v>275</v>
       </c>
@@ -31029,7 +31029,7 @@
       </c>
       <c r="X26" s="138"/>
     </row>
-    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1">
+    <row r="27" spans="1:36" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
@@ -31063,7 +31063,7 @@
       <c r="R27" s="126"/>
       <c r="X27" s="123"/>
     </row>
-    <row r="28" spans="1:36" hidden="1">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="88" t="s">
         <v>285</v>
       </c>
@@ -31091,7 +31091,7 @@
       <c r="AI28" s="53"/>
       <c r="AJ28" s="48"/>
     </row>
-    <row r="29" spans="1:36" hidden="1">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="88" t="s">
         <v>285</v>
       </c>
@@ -31119,7 +31119,7 @@
       <c r="AI29" s="53"/>
       <c r="AJ29" s="48"/>
     </row>
-    <row r="30" spans="1:36" hidden="1">
+    <row r="30" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="88" t="s">
         <v>285</v>
       </c>
@@ -31147,7 +31147,7 @@
       <c r="AI30" s="53"/>
       <c r="AJ30" s="48"/>
     </row>
-    <row r="31" spans="1:36" ht="25.9" hidden="1" customHeight="1">
+    <row r="31" spans="1:36" ht="25.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="88" t="s">
         <v>285</v>
       </c>
@@ -31176,7 +31176,7 @@
       <c r="AI31" s="53"/>
       <c r="AJ31" s="48"/>
     </row>
-    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1">
+    <row r="32" spans="1:36" s="48" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>290</v>
       </c>
@@ -31193,7 +31193,7 @@
       <c r="AH32"/>
       <c r="AI32" s="87"/>
     </row>
-    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1">
+    <row r="33" spans="1:35" s="112" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="112" t="s">
         <v>294</v>
       </c>
@@ -31227,7 +31227,7 @@
       <c r="L33" s="41"/>
       <c r="X33" s="132"/>
     </row>
-    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="34" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>301</v>
       </c>
@@ -31258,7 +31258,7 @@
       <c r="Q34" s="127"/>
       <c r="AI34" s="116"/>
     </row>
-    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="35" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>307</v>
       </c>
@@ -31287,7 +31287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="36" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>311</v>
       </c>
@@ -31319,7 +31319,7 @@
       <c r="X36" s="133"/>
       <c r="AA36" s="134"/>
     </row>
-    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="37" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
@@ -31346,7 +31346,7 @@
       </c>
       <c r="R37" s="126"/>
     </row>
-    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="38" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="127" t="s">
         <v>319</v>
       </c>
@@ -31362,7 +31362,7 @@
       </c>
       <c r="F38" s="127"/>
     </row>
-    <row r="39" spans="1:35" s="117" customFormat="1">
+    <row r="39" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="122" t="s">
         <v>329</v>
       </c>
@@ -31394,7 +31394,7 @@
       <c r="R39" s="141"/>
       <c r="X39" s="141"/>
     </row>
-    <row r="40" spans="1:35" s="117" customFormat="1">
+    <row r="40" spans="1:35" s="117" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="122" t="s">
         <v>329</v>
       </c>
@@ -31428,7 +31428,7 @@
       <c r="AE40" s="120"/>
       <c r="AF40" s="142"/>
     </row>
-    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="41" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="124" t="s">
         <v>336</v>
       </c>
@@ -31460,7 +31460,7 @@
       <c r="AD41" s="135"/>
       <c r="AE41" s="43"/>
     </row>
-    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="42" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="124" t="s">
         <v>342</v>
       </c>
@@ -31491,7 +31491,7 @@
       <c r="X42" s="123"/>
       <c r="AE42" s="43"/>
     </row>
-    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1">
+    <row r="43" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="124" t="s">
         <v>345</v>
       </c>
@@ -31539,7 +31539,7 @@
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
     </row>
-    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1">
+    <row r="44" spans="1:35" s="137" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="124" t="s">
         <v>345</v>
       </c>
@@ -31587,7 +31587,7 @@
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
     </row>
-    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1">
+    <row r="45" spans="1:35" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>348</v>
       </c>
@@ -31615,10 +31615,10 @@
       <c r="R45" s="123"/>
       <c r="X45" s="123"/>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="48"/>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="143" t="s">
         <v>35</v>
       </c>
@@ -31653,7 +31653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:12">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="143" t="s">
         <v>402</v>
       </c>
@@ -31672,7 +31672,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:12">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="143"/>
       <c r="C52" s="143" t="s">
         <v>404</v>
@@ -31689,7 +31689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="143" t="s">
         <v>405</v>
       </c>
@@ -31708,7 +31708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:12">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="143"/>
       <c r="C54" s="143" t="s">
         <v>404</v>
@@ -31763,5 +31763,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>